--- a/work-breakdown-structure-template.xlsx
+++ b/work-breakdown-structure-template.xlsx
@@ -3993,11 +3993,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DF127"/>
+  <dimension ref="A1:BS127"/>
   <sheetFormatPr defaultColWidth="8.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="3" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.14"/>
@@ -4008,7 +4008,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="10.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="110" min="11" style="0" width="2.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="11" style="0" width="2.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4114,346 +4114,190 @@
       <c r="BQ6" s="26"/>
       <c r="BR6" s="26"/>
       <c r="BS6" s="26"/>
-      <c r="BT6" s="26"/>
-      <c r="BU6" s="26"/>
-      <c r="BV6" s="26"/>
-      <c r="BW6" s="26"/>
-      <c r="BX6" s="26"/>
-      <c r="BY6" s="26"/>
-      <c r="BZ6" s="26"/>
-      <c r="CA6" s="26"/>
-      <c r="CB6" s="26"/>
-      <c r="CC6" s="26"/>
-      <c r="CD6" s="26"/>
-      <c r="CE6" s="26"/>
-      <c r="CF6" s="26"/>
-      <c r="CG6" s="26"/>
-      <c r="CH6" s="26"/>
-      <c r="CI6" s="26"/>
-      <c r="CJ6" s="26"/>
-      <c r="CK6" s="26"/>
-      <c r="CL6" s="26"/>
-      <c r="CM6" s="26"/>
-      <c r="CN6" s="26"/>
-      <c r="CO6" s="26"/>
-      <c r="CP6" s="26"/>
-      <c r="CQ6" s="26"/>
-      <c r="CR6" s="26"/>
-      <c r="CS6" s="26"/>
-      <c r="CT6" s="26"/>
-      <c r="CU6" s="26"/>
-      <c r="CV6" s="26"/>
-      <c r="CW6" s="26"/>
-      <c r="CX6" s="26"/>
-      <c r="CY6" s="26"/>
-      <c r="CZ6" s="26"/>
-      <c r="DA6" s="26"/>
-      <c r="DB6" s="26"/>
-      <c r="DC6" s="26"/>
-      <c r="DD6" s="26"/>
-      <c r="DE6" s="26"/>
-      <c r="DF6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K7" s="27" t="n">
-        <v>46027</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>46028</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>46029</v>
-      </c>
-      <c r="N7" s="27" t="n">
-        <v>46030</v>
-      </c>
-      <c r="O7" s="27" t="n">
-        <v>46031</v>
-      </c>
-      <c r="P7" s="27" t="n">
-        <v>46032</v>
-      </c>
-      <c r="Q7" s="27" t="n">
-        <v>46033</v>
-      </c>
-      <c r="R7" s="27" t="n">
-        <v>46034</v>
-      </c>
-      <c r="S7" s="27" t="n">
-        <v>46035</v>
-      </c>
-      <c r="T7" s="27" t="n">
-        <v>46036</v>
-      </c>
-      <c r="U7" s="27" t="n">
-        <v>46037</v>
-      </c>
-      <c r="V7" s="27" t="n">
-        <v>46038</v>
-      </c>
-      <c r="W7" s="27" t="n">
-        <v>46039</v>
-      </c>
-      <c r="X7" s="27" t="n">
-        <v>46040</v>
-      </c>
-      <c r="Y7" s="27" t="n">
-        <v>46041</v>
-      </c>
-      <c r="Z7" s="27" t="n">
-        <v>46042</v>
-      </c>
-      <c r="AA7" s="27" t="n">
-        <v>46043</v>
-      </c>
-      <c r="AB7" s="27" t="n">
-        <v>46044</v>
-      </c>
-      <c r="AC7" s="27" t="n">
-        <v>46045</v>
-      </c>
-      <c r="AD7" s="27" t="n">
-        <v>46046</v>
-      </c>
-      <c r="AE7" s="27" t="n">
-        <v>46047</v>
-      </c>
-      <c r="AF7" s="27" t="n">
-        <v>46048</v>
-      </c>
-      <c r="AG7" s="27" t="n">
-        <v>46049</v>
-      </c>
-      <c r="AH7" s="27" t="n">
-        <v>46050</v>
-      </c>
-      <c r="AI7" s="27" t="n">
-        <v>46051</v>
-      </c>
-      <c r="AJ7" s="27" t="n">
-        <v>46052</v>
-      </c>
-      <c r="AK7" s="27" t="n">
-        <v>46053</v>
-      </c>
-      <c r="AL7" s="27" t="n">
-        <v>46054</v>
-      </c>
-      <c r="AM7" s="27" t="n">
-        <v>46055</v>
-      </c>
-      <c r="AN7" s="27" t="n">
-        <v>46056</v>
-      </c>
-      <c r="AO7" s="27" t="n">
-        <v>46057</v>
-      </c>
-      <c r="AP7" s="27" t="n">
-        <v>46058</v>
-      </c>
-      <c r="AQ7" s="27" t="n">
-        <v>46059</v>
-      </c>
-      <c r="AR7" s="27" t="n">
-        <v>46060</v>
-      </c>
-      <c r="AS7" s="27" t="n">
-        <v>46061</v>
-      </c>
-      <c r="AT7" s="27" t="n">
-        <v>46062</v>
-      </c>
-      <c r="AU7" s="27" t="n">
-        <v>46063</v>
-      </c>
-      <c r="AV7" s="27" t="n">
-        <v>46064</v>
-      </c>
-      <c r="AW7" s="27" t="n">
-        <v>46065</v>
-      </c>
-      <c r="AX7" s="27" t="n">
-        <v>46066</v>
-      </c>
-      <c r="AY7" s="27" t="n">
-        <v>46067</v>
-      </c>
-      <c r="AZ7" s="27" t="n">
-        <v>46068</v>
-      </c>
-      <c r="BA7" s="27" t="n">
-        <v>46069</v>
-      </c>
-      <c r="BB7" s="27" t="n">
-        <v>46070</v>
-      </c>
-      <c r="BC7" s="27" t="n">
-        <v>46071</v>
-      </c>
-      <c r="BD7" s="27" t="n">
-        <v>46072</v>
-      </c>
-      <c r="BE7" s="27" t="n">
-        <v>46073</v>
-      </c>
-      <c r="BF7" s="27" t="n">
-        <v>46074</v>
-      </c>
-      <c r="BG7" s="27" t="n">
-        <v>46075</v>
-      </c>
-      <c r="BH7" s="27" t="n">
-        <v>46076</v>
-      </c>
-      <c r="BI7" s="27" t="n">
-        <v>46077</v>
-      </c>
-      <c r="BJ7" s="27" t="n">
-        <v>46078</v>
-      </c>
-      <c r="BK7" s="27" t="n">
-        <v>46079</v>
-      </c>
-      <c r="BL7" s="27" t="n">
-        <v>46080</v>
-      </c>
-      <c r="BM7" s="27" t="n">
-        <v>46081</v>
-      </c>
-      <c r="BN7" s="27" t="n">
-        <v>46082</v>
-      </c>
-      <c r="BO7" s="27" t="n">
-        <v>46083</v>
-      </c>
-      <c r="BP7" s="27" t="n">
-        <v>46084</v>
-      </c>
-      <c r="BQ7" s="27" t="n">
-        <v>46085</v>
-      </c>
-      <c r="BR7" s="27" t="n">
-        <v>46086</v>
-      </c>
-      <c r="BS7" s="27" t="n">
-        <v>46087</v>
-      </c>
-      <c r="BT7" s="27" t="n">
-        <v>46088</v>
-      </c>
-      <c r="BU7" s="27" t="n">
-        <v>46089</v>
-      </c>
-      <c r="BV7" s="27" t="n">
-        <v>46090</v>
-      </c>
-      <c r="BW7" s="27" t="n">
-        <v>46091</v>
-      </c>
-      <c r="BX7" s="27" t="n">
-        <v>46092</v>
-      </c>
-      <c r="BY7" s="27" t="n">
-        <v>46093</v>
-      </c>
-      <c r="BZ7" s="27" t="n">
-        <v>46094</v>
-      </c>
-      <c r="CA7" s="27" t="n">
-        <v>46095</v>
-      </c>
-      <c r="CB7" s="27" t="n">
-        <v>46096</v>
-      </c>
-      <c r="CC7" s="27" t="n">
-        <v>46097</v>
-      </c>
-      <c r="CD7" s="27" t="n">
-        <v>46098</v>
-      </c>
-      <c r="CE7" s="27" t="n">
-        <v>46099</v>
-      </c>
-      <c r="CF7" s="27" t="n">
-        <v>46100</v>
-      </c>
-      <c r="CG7" s="27" t="n">
-        <v>46101</v>
-      </c>
-      <c r="CH7" s="27" t="n">
-        <v>46102</v>
-      </c>
-      <c r="CI7" s="27" t="n">
-        <v>46103</v>
-      </c>
-      <c r="CJ7" s="27" t="n">
-        <v>46104</v>
-      </c>
-      <c r="CK7" s="27" t="n">
-        <v>46105</v>
-      </c>
-      <c r="CL7" s="27" t="n">
-        <v>46106</v>
-      </c>
-      <c r="CM7" s="27" t="n">
-        <v>46107</v>
-      </c>
-      <c r="CN7" s="27" t="n">
-        <v>46108</v>
-      </c>
-      <c r="CO7" s="27" t="n">
-        <v>46109</v>
-      </c>
-      <c r="CP7" s="27" t="n">
-        <v>46110</v>
-      </c>
-      <c r="CQ7" s="27" t="n">
-        <v>46111</v>
-      </c>
-      <c r="CR7" s="27" t="n">
-        <v>46112</v>
-      </c>
-      <c r="CS7" s="27" t="n">
-        <v>46113</v>
-      </c>
-      <c r="CT7" s="27" t="n">
-        <v>46114</v>
-      </c>
-      <c r="CU7" s="27" t="n">
-        <v>46115</v>
-      </c>
-      <c r="CV7" s="27" t="n">
-        <v>46116</v>
-      </c>
-      <c r="CW7" s="27" t="n">
-        <v>46117</v>
-      </c>
-      <c r="CX7" s="27" t="n">
-        <v>46118</v>
-      </c>
-      <c r="CY7" s="27" t="n">
-        <v>46119</v>
-      </c>
-      <c r="CZ7" s="27" t="n">
-        <v>46120</v>
-      </c>
-      <c r="DA7" s="27" t="n">
-        <v>46121</v>
-      </c>
-      <c r="DB7" s="27" t="n">
-        <v>46122</v>
-      </c>
-      <c r="DC7" s="27" t="n">
-        <v>46123</v>
-      </c>
-      <c r="DD7" s="27" t="n">
-        <v>46124</v>
-      </c>
-      <c r="DE7" s="27" t="n">
-        <v>46125</v>
-      </c>
-      <c r="DF7" s="27" t="n">
-        <v>46126</v>
+      <c r="K7" s="27">
+        <v>46296</v>
+      </c>
+      <c r="L7" s="27">
+        <v>46297</v>
+      </c>
+      <c r="M7" s="27">
+        <v>46298</v>
+      </c>
+      <c r="N7" s="27">
+        <v>46299</v>
+      </c>
+      <c r="O7" s="27">
+        <v>46300</v>
+      </c>
+      <c r="P7" s="27">
+        <v>46301</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>46302</v>
+      </c>
+      <c r="R7" s="27">
+        <v>46303</v>
+      </c>
+      <c r="S7" s="27">
+        <v>46304</v>
+      </c>
+      <c r="T7" s="27">
+        <v>46305</v>
+      </c>
+      <c r="U7" s="27">
+        <v>46306</v>
+      </c>
+      <c r="V7" s="27">
+        <v>46307</v>
+      </c>
+      <c r="W7" s="27">
+        <v>46308</v>
+      </c>
+      <c r="X7" s="27">
+        <v>46309</v>
+      </c>
+      <c r="Y7" s="27">
+        <v>46310</v>
+      </c>
+      <c r="Z7" s="27">
+        <v>46311</v>
+      </c>
+      <c r="AA7" s="27">
+        <v>46312</v>
+      </c>
+      <c r="AB7" s="27">
+        <v>46313</v>
+      </c>
+      <c r="AC7" s="27">
+        <v>46314</v>
+      </c>
+      <c r="AD7" s="27">
+        <v>46315</v>
+      </c>
+      <c r="AE7" s="27">
+        <v>46316</v>
+      </c>
+      <c r="AF7" s="27">
+        <v>46317</v>
+      </c>
+      <c r="AG7" s="27">
+        <v>46318</v>
+      </c>
+      <c r="AH7" s="27">
+        <v>46319</v>
+      </c>
+      <c r="AI7" s="27">
+        <v>46320</v>
+      </c>
+      <c r="AJ7" s="27">
+        <v>46321</v>
+      </c>
+      <c r="AK7" s="27">
+        <v>46322</v>
+      </c>
+      <c r="AL7" s="27">
+        <v>46323</v>
+      </c>
+      <c r="AM7" s="27">
+        <v>46324</v>
+      </c>
+      <c r="AN7" s="27">
+        <v>46325</v>
+      </c>
+      <c r="AO7" s="27">
+        <v>46326</v>
+      </c>
+      <c r="AP7" s="27">
+        <v>46327</v>
+      </c>
+      <c r="AQ7" s="27">
+        <v>46328</v>
+      </c>
+      <c r="AR7" s="27">
+        <v>46329</v>
+      </c>
+      <c r="AS7" s="27">
+        <v>46330</v>
+      </c>
+      <c r="AT7" s="27">
+        <v>46331</v>
+      </c>
+      <c r="AU7" s="27">
+        <v>46332</v>
+      </c>
+      <c r="AV7" s="27">
+        <v>46333</v>
+      </c>
+      <c r="AW7" s="27">
+        <v>46334</v>
+      </c>
+      <c r="AX7" s="27">
+        <v>46335</v>
+      </c>
+      <c r="AY7" s="27">
+        <v>46336</v>
+      </c>
+      <c r="AZ7" s="27">
+        <v>46337</v>
+      </c>
+      <c r="BA7" s="27">
+        <v>46338</v>
+      </c>
+      <c r="BB7" s="27">
+        <v>46339</v>
+      </c>
+      <c r="BC7" s="27">
+        <v>46340</v>
+      </c>
+      <c r="BD7" s="27">
+        <v>46341</v>
+      </c>
+      <c r="BE7" s="27">
+        <v>46342</v>
+      </c>
+      <c r="BF7" s="27">
+        <v>46343</v>
+      </c>
+      <c r="BG7" s="27">
+        <v>46344</v>
+      </c>
+      <c r="BH7" s="27">
+        <v>46345</v>
+      </c>
+      <c r="BI7" s="27">
+        <v>46346</v>
+      </c>
+      <c r="BJ7" s="27">
+        <v>46347</v>
+      </c>
+      <c r="BK7" s="27">
+        <v>46348</v>
+      </c>
+      <c r="BL7" s="27">
+        <v>46349</v>
+      </c>
+      <c r="BM7" s="27">
+        <v>46350</v>
+      </c>
+      <c r="BN7" s="27">
+        <v>46351</v>
+      </c>
+      <c r="BO7" s="27">
+        <v>46352</v>
+      </c>
+      <c r="BP7" s="27">
+        <v>46353</v>
+      </c>
+      <c r="BQ7" s="27">
+        <v>46354</v>
+      </c>
+      <c r="BR7" s="27">
+        <v>46355</v>
+      </c>
+      <c r="BS7" s="27">
+        <v>46356</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4469,7 +4313,11 @@
       <c r="H8" s="28"/>
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
-      <c r="K8" s="29"/>
+      <c r="K8" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026년 10월</t>
+        </is>
+      </c>
       <c r="L8" s="29"/>
       <c r="M8" s="29"/>
       <c r="N8" s="29"/>
@@ -4500,7 +4348,11 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="30"/>
       <c r="AO8" s="30"/>
-      <c r="AP8" s="30"/>
+      <c r="AP8" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026년 11월</t>
+        </is>
+      </c>
       <c r="AQ8" s="30"/>
       <c r="AR8" s="30"/>
       <c r="AS8" s="30"/>
@@ -4530,45 +4382,6 @@
       <c r="BQ8" s="29"/>
       <c r="BR8" s="29"/>
       <c r="BS8" s="29"/>
-      <c r="BT8" s="29"/>
-      <c r="BU8" s="29"/>
-      <c r="BV8" s="29"/>
-      <c r="BW8" s="29"/>
-      <c r="BX8" s="29"/>
-      <c r="BY8" s="29"/>
-      <c r="BZ8" s="29"/>
-      <c r="CA8" s="29"/>
-      <c r="CB8" s="29"/>
-      <c r="CC8" s="29"/>
-      <c r="CD8" s="29"/>
-      <c r="CE8" s="29"/>
-      <c r="CF8" s="29"/>
-      <c r="CG8" s="29"/>
-      <c r="CH8" s="29"/>
-      <c r="CI8" s="29"/>
-      <c r="CJ8" s="29"/>
-      <c r="CK8" s="29"/>
-      <c r="CL8" s="29"/>
-      <c r="CM8" s="29"/>
-      <c r="CN8" s="29"/>
-      <c r="CO8" s="29"/>
-      <c r="CP8" s="29"/>
-      <c r="CQ8" s="29"/>
-      <c r="CR8" s="29"/>
-      <c r="CS8" s="29"/>
-      <c r="CT8" s="29"/>
-      <c r="CU8" s="29"/>
-      <c r="CV8" s="29"/>
-      <c r="CW8" s="29"/>
-      <c r="CX8" s="29"/>
-      <c r="CY8" s="29"/>
-      <c r="CZ8" s="29"/>
-      <c r="DA8" s="29"/>
-      <c r="DB8" s="29"/>
-      <c r="DC8" s="29"/>
-      <c r="DD8" s="29"/>
-      <c r="DE8" s="29"/>
-      <c r="DF8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
@@ -4583,136 +4396,117 @@
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
-      <c r="K9" s="32" t="s">
-        <v>30</v>
+      <c r="K9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W1
+10/01</t>
+        </is>
       </c>
       <c r="L9" s="32"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W2
+10/05</t>
+        </is>
+      </c>
       <c r="P9" s="32"/>
       <c r="Q9" s="32"/>
-      <c r="R9" s="32" t="s">
-        <v>31</v>
-      </c>
+      <c r="R9" s="32"/>
       <c r="S9" s="32"/>
       <c r="T9" s="32"/>
       <c r="U9" s="32"/>
-      <c r="V9" s="32"/>
+      <c r="V9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W3
+10/12</t>
+        </is>
+      </c>
       <c r="W9" s="32"/>
       <c r="X9" s="32"/>
-      <c r="Y9" s="32" t="s">
-        <v>32</v>
-      </c>
+      <c r="Y9" s="32"/>
       <c r="Z9" s="32"/>
       <c r="AA9" s="32"/>
       <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
+      <c r="AC9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W4
+10/19</t>
+        </is>
+      </c>
       <c r="AD9" s="32"/>
       <c r="AE9" s="32"/>
-      <c r="AF9" s="33" t="s">
-        <v>33</v>
-      </c>
+      <c r="AF9" s="33"/>
       <c r="AG9" s="33"/>
       <c r="AH9" s="33"/>
       <c r="AI9" s="33"/>
-      <c r="AJ9" s="33"/>
+      <c r="AJ9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W5
+10/26</t>
+        </is>
+      </c>
       <c r="AK9" s="33"/>
       <c r="AL9" s="33"/>
-      <c r="AM9" s="32" t="s">
-        <v>34</v>
-      </c>
+      <c r="AM9" s="32"/>
       <c r="AN9" s="32"/>
       <c r="AO9" s="32"/>
       <c r="AP9" s="32"/>
-      <c r="AQ9" s="32"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W6
+11/02</t>
+        </is>
+      </c>
       <c r="AR9" s="32"/>
       <c r="AS9" s="32"/>
-      <c r="AT9" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="AT9" s="32"/>
       <c r="AU9" s="32"/>
       <c r="AV9" s="32"/>
       <c r="AW9" s="32"/>
-      <c r="AX9" s="32"/>
+      <c r="AX9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W7
+11/09</t>
+        </is>
+      </c>
       <c r="AY9" s="32"/>
       <c r="AZ9" s="32"/>
-      <c r="BA9" s="32" t="s">
-        <v>36</v>
-      </c>
+      <c r="BA9" s="32"/>
       <c r="BB9" s="32"/>
       <c r="BC9" s="32"/>
       <c r="BD9" s="32"/>
-      <c r="BE9" s="32"/>
+      <c r="BE9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W8
+11/16</t>
+        </is>
+      </c>
       <c r="BF9" s="32"/>
       <c r="BG9" s="32"/>
-      <c r="BH9" s="33" t="s">
-        <v>37</v>
-      </c>
+      <c r="BH9" s="33"/>
       <c r="BI9" s="33"/>
       <c r="BJ9" s="33"/>
       <c r="BK9" s="33"/>
-      <c r="BL9" s="33"/>
+      <c r="BL9" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W9
+11/23</t>
+        </is>
+      </c>
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
-      <c r="BO9" s="32" t="s">
-        <v>38</v>
-      </c>
+      <c r="BO9" s="32"/>
       <c r="BP9" s="32"/>
       <c r="BQ9" s="32"/>
       <c r="BR9" s="32"/>
-      <c r="BS9" s="32"/>
-      <c r="BT9" s="32"/>
-      <c r="BU9" s="32"/>
-      <c r="BV9" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="BW9" s="32"/>
-      <c r="BX9" s="32"/>
-      <c r="BY9" s="32"/>
-      <c r="BZ9" s="32"/>
-      <c r="CA9" s="32"/>
-      <c r="CB9" s="32"/>
-      <c r="CC9" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="CD9" s="32"/>
-      <c r="CE9" s="32"/>
-      <c r="CF9" s="32"/>
-      <c r="CG9" s="32"/>
-      <c r="CH9" s="32"/>
-      <c r="CI9" s="32"/>
-      <c r="CJ9" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="CK9" s="33"/>
-      <c r="CL9" s="33"/>
-      <c r="CM9" s="33"/>
-      <c r="CN9" s="33"/>
-      <c r="CO9" s="33"/>
-      <c r="CP9" s="33"/>
-      <c r="CQ9" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="CR9" s="32"/>
-      <c r="CS9" s="32"/>
-      <c r="CT9" s="32"/>
-      <c r="CU9" s="32"/>
-      <c r="CV9" s="32"/>
-      <c r="CW9" s="32"/>
-      <c r="CX9" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="CY9" s="32"/>
-      <c r="CZ9" s="32"/>
-      <c r="DA9" s="32"/>
-      <c r="DB9" s="32"/>
-      <c r="DC9" s="32"/>
-      <c r="DD9" s="32"/>
-      <c r="DE9" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="DF9" s="32"/>
+      <c r="BS9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W10
+11/30</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
@@ -4745,305 +4539,371 @@
       <c r="J10" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="O10" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="P10" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q10" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="R10" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="S10" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="T10" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="U10" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="V10" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="X10" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y10" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z10" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA10" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB10" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC10" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD10" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE10" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF10" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG10" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH10" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI10" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ10" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK10" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL10" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM10" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN10" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO10" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP10" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ10" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR10" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS10" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT10" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU10" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW10" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX10" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY10" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ10" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA10" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB10" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="BC10" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD10" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE10" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="BF10" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="BG10" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="BH10" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="BI10" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ10" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="BK10" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL10" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM10" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN10" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO10" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="BP10" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="BQ10" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="BR10" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="BS10" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="BT10" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="BU10" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV10" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="BW10" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="BX10" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="BY10" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="BZ10" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="CA10" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="CB10" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="CC10" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="CD10" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="CE10" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF10" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="CG10" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="CH10" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="CI10" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="CJ10" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="CK10" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="CL10" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="CM10" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="CN10" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="CO10" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="CP10" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="CQ10" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="CR10" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="CS10" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="CT10" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU10" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="CV10" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="CW10" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="CX10" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="CY10" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="CZ10" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="DA10" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="DB10" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="DC10" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="DD10" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="DE10" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="DF10" s="37" t="s">
-        <v>129</v>
+      <c r="K10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+목</t>
+        </is>
+      </c>
+      <c r="L10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+금</t>
+        </is>
+      </c>
+      <c r="M10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+토</t>
+        </is>
+      </c>
+      <c r="N10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+일</t>
+        </is>
+      </c>
+      <c r="O10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+월</t>
+        </is>
+      </c>
+      <c r="P10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+화</t>
+        </is>
+      </c>
+      <c r="Q10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+수</t>
+        </is>
+      </c>
+      <c r="R10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+목</t>
+        </is>
+      </c>
+      <c r="S10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+금</t>
+        </is>
+      </c>
+      <c r="T10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+토</t>
+        </is>
+      </c>
+      <c r="U10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+일</t>
+        </is>
+      </c>
+      <c r="V10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+월</t>
+        </is>
+      </c>
+      <c r="W10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+화</t>
+        </is>
+      </c>
+      <c r="X10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+수</t>
+        </is>
+      </c>
+      <c r="Y10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+목</t>
+        </is>
+      </c>
+      <c r="Z10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+금</t>
+        </is>
+      </c>
+      <c r="AA10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+토</t>
+        </is>
+      </c>
+      <c r="AB10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+일</t>
+        </is>
+      </c>
+      <c r="AC10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+월</t>
+        </is>
+      </c>
+      <c r="AD10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+화</t>
+        </is>
+      </c>
+      <c r="AE10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+수</t>
+        </is>
+      </c>
+      <c r="AF10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+목</t>
+        </is>
+      </c>
+      <c r="AG10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+금</t>
+        </is>
+      </c>
+      <c r="AH10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+토</t>
+        </is>
+      </c>
+      <c r="AI10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+일</t>
+        </is>
+      </c>
+      <c r="AJ10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+월</t>
+        </is>
+      </c>
+      <c r="AK10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+화</t>
+        </is>
+      </c>
+      <c r="AL10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+수</t>
+        </is>
+      </c>
+      <c r="AM10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+목</t>
+        </is>
+      </c>
+      <c r="AN10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+금</t>
+        </is>
+      </c>
+      <c r="AO10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+토</t>
+        </is>
+      </c>
+      <c r="AP10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+일</t>
+        </is>
+      </c>
+      <c r="AQ10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+월</t>
+        </is>
+      </c>
+      <c r="AR10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+화</t>
+        </is>
+      </c>
+      <c r="AS10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+수</t>
+        </is>
+      </c>
+      <c r="AT10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+목</t>
+        </is>
+      </c>
+      <c r="AU10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+금</t>
+        </is>
+      </c>
+      <c r="AV10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+토</t>
+        </is>
+      </c>
+      <c r="AW10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+일</t>
+        </is>
+      </c>
+      <c r="AX10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+월</t>
+        </is>
+      </c>
+      <c r="AY10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+화</t>
+        </is>
+      </c>
+      <c r="AZ10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+수</t>
+        </is>
+      </c>
+      <c r="BA10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+목</t>
+        </is>
+      </c>
+      <c r="BB10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+금</t>
+        </is>
+      </c>
+      <c r="BC10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+토</t>
+        </is>
+      </c>
+      <c r="BD10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+일</t>
+        </is>
+      </c>
+      <c r="BE10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+월</t>
+        </is>
+      </c>
+      <c r="BF10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+화</t>
+        </is>
+      </c>
+      <c r="BG10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+수</t>
+        </is>
+      </c>
+      <c r="BH10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+목</t>
+        </is>
+      </c>
+      <c r="BI10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+금</t>
+        </is>
+      </c>
+      <c r="BJ10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+토</t>
+        </is>
+      </c>
+      <c r="BK10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+일</t>
+        </is>
+      </c>
+      <c r="BL10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+월</t>
+        </is>
+      </c>
+      <c r="BM10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+화</t>
+        </is>
+      </c>
+      <c r="BN10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+수</t>
+        </is>
+      </c>
+      <c r="BO10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+목</t>
+        </is>
+      </c>
+      <c r="BP10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+금</t>
+        </is>
+      </c>
+      <c r="BQ10" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+토</t>
+        </is>
+      </c>
+      <c r="BR10" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+일</t>
+        </is>
+      </c>
+      <c r="BS10" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+월</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5118,45 +4978,6 @@
       <c r="BQ11" s="57"/>
       <c r="BR11" s="57"/>
       <c r="BS11" s="58"/>
-      <c r="BT11" s="52"/>
-      <c r="BU11" s="53"/>
-      <c r="BV11" s="60"/>
-      <c r="BW11" s="57"/>
-      <c r="BX11" s="57"/>
-      <c r="BY11" s="57"/>
-      <c r="BZ11" s="57"/>
-      <c r="CA11" s="52"/>
-      <c r="CB11" s="53"/>
-      <c r="CC11" s="60"/>
-      <c r="CD11" s="57"/>
-      <c r="CE11" s="57"/>
-      <c r="CF11" s="57"/>
-      <c r="CG11" s="57"/>
-      <c r="CH11" s="52"/>
-      <c r="CI11" s="55"/>
-      <c r="CJ11" s="59"/>
-      <c r="CK11" s="57"/>
-      <c r="CL11" s="57"/>
-      <c r="CM11" s="57"/>
-      <c r="CN11" s="57"/>
-      <c r="CO11" s="52"/>
-      <c r="CP11" s="53"/>
-      <c r="CQ11" s="60"/>
-      <c r="CR11" s="57"/>
-      <c r="CS11" s="57"/>
-      <c r="CT11" s="57"/>
-      <c r="CU11" s="57"/>
-      <c r="CV11" s="52"/>
-      <c r="CW11" s="53"/>
-      <c r="CX11" s="60"/>
-      <c r="CY11" s="57"/>
-      <c r="CZ11" s="57"/>
-      <c r="DA11" s="57"/>
-      <c r="DB11" s="57"/>
-      <c r="DC11" s="52"/>
-      <c r="DD11" s="53"/>
-      <c r="DE11" s="60"/>
-      <c r="DF11" s="57"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="61"/>
@@ -5230,45 +5051,6 @@
       <c r="BQ12" s="57"/>
       <c r="BR12" s="57"/>
       <c r="BS12" s="58"/>
-      <c r="BT12" s="52"/>
-      <c r="BU12" s="53"/>
-      <c r="BV12" s="60"/>
-      <c r="BW12" s="57"/>
-      <c r="BX12" s="57"/>
-      <c r="BY12" s="57"/>
-      <c r="BZ12" s="57"/>
-      <c r="CA12" s="52"/>
-      <c r="CB12" s="53"/>
-      <c r="CC12" s="60"/>
-      <c r="CD12" s="57"/>
-      <c r="CE12" s="57"/>
-      <c r="CF12" s="57"/>
-      <c r="CG12" s="57"/>
-      <c r="CH12" s="52"/>
-      <c r="CI12" s="55"/>
-      <c r="CJ12" s="59"/>
-      <c r="CK12" s="57"/>
-      <c r="CL12" s="57"/>
-      <c r="CM12" s="57"/>
-      <c r="CN12" s="57"/>
-      <c r="CO12" s="52"/>
-      <c r="CP12" s="53"/>
-      <c r="CQ12" s="60"/>
-      <c r="CR12" s="57"/>
-      <c r="CS12" s="57"/>
-      <c r="CT12" s="57"/>
-      <c r="CU12" s="57"/>
-      <c r="CV12" s="52"/>
-      <c r="CW12" s="53"/>
-      <c r="CX12" s="60"/>
-      <c r="CY12" s="57"/>
-      <c r="CZ12" s="57"/>
-      <c r="DA12" s="57"/>
-      <c r="DB12" s="57"/>
-      <c r="DC12" s="52"/>
-      <c r="DD12" s="53"/>
-      <c r="DE12" s="60"/>
-      <c r="DF12" s="57"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A13" s="67"/>
@@ -5342,45 +5124,6 @@
       <c r="BQ13" s="57"/>
       <c r="BR13" s="57"/>
       <c r="BS13" s="58"/>
-      <c r="BT13" s="52"/>
-      <c r="BU13" s="53"/>
-      <c r="BV13" s="60"/>
-      <c r="BW13" s="57"/>
-      <c r="BX13" s="57"/>
-      <c r="BY13" s="57"/>
-      <c r="BZ13" s="57"/>
-      <c r="CA13" s="52"/>
-      <c r="CB13" s="53"/>
-      <c r="CC13" s="60"/>
-      <c r="CD13" s="57"/>
-      <c r="CE13" s="57"/>
-      <c r="CF13" s="57"/>
-      <c r="CG13" s="57"/>
-      <c r="CH13" s="52"/>
-      <c r="CI13" s="55"/>
-      <c r="CJ13" s="59"/>
-      <c r="CK13" s="57"/>
-      <c r="CL13" s="57"/>
-      <c r="CM13" s="57"/>
-      <c r="CN13" s="57"/>
-      <c r="CO13" s="52"/>
-      <c r="CP13" s="53"/>
-      <c r="CQ13" s="60"/>
-      <c r="CR13" s="57"/>
-      <c r="CS13" s="57"/>
-      <c r="CT13" s="57"/>
-      <c r="CU13" s="57"/>
-      <c r="CV13" s="52"/>
-      <c r="CW13" s="53"/>
-      <c r="CX13" s="60"/>
-      <c r="CY13" s="57"/>
-      <c r="CZ13" s="57"/>
-      <c r="DA13" s="57"/>
-      <c r="DB13" s="57"/>
-      <c r="DC13" s="52"/>
-      <c r="DD13" s="53"/>
-      <c r="DE13" s="60"/>
-      <c r="DF13" s="57"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A14" s="67"/>
@@ -5454,45 +5197,6 @@
       <c r="BQ14" s="57"/>
       <c r="BR14" s="57"/>
       <c r="BS14" s="58"/>
-      <c r="BT14" s="52"/>
-      <c r="BU14" s="53"/>
-      <c r="BV14" s="60"/>
-      <c r="BW14" s="57"/>
-      <c r="BX14" s="57"/>
-      <c r="BY14" s="57"/>
-      <c r="BZ14" s="57"/>
-      <c r="CA14" s="52"/>
-      <c r="CB14" s="53"/>
-      <c r="CC14" s="60"/>
-      <c r="CD14" s="57"/>
-      <c r="CE14" s="57"/>
-      <c r="CF14" s="57"/>
-      <c r="CG14" s="57"/>
-      <c r="CH14" s="52"/>
-      <c r="CI14" s="55"/>
-      <c r="CJ14" s="59"/>
-      <c r="CK14" s="57"/>
-      <c r="CL14" s="57"/>
-      <c r="CM14" s="57"/>
-      <c r="CN14" s="57"/>
-      <c r="CO14" s="52"/>
-      <c r="CP14" s="53"/>
-      <c r="CQ14" s="60"/>
-      <c r="CR14" s="57"/>
-      <c r="CS14" s="57"/>
-      <c r="CT14" s="57"/>
-      <c r="CU14" s="57"/>
-      <c r="CV14" s="52"/>
-      <c r="CW14" s="53"/>
-      <c r="CX14" s="60"/>
-      <c r="CY14" s="57"/>
-      <c r="CZ14" s="57"/>
-      <c r="DA14" s="57"/>
-      <c r="DB14" s="57"/>
-      <c r="DC14" s="52"/>
-      <c r="DD14" s="53"/>
-      <c r="DE14" s="60"/>
-      <c r="DF14" s="57"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A15" s="67"/>
@@ -5566,45 +5270,6 @@
       <c r="BQ15" s="57"/>
       <c r="BR15" s="57"/>
       <c r="BS15" s="58"/>
-      <c r="BT15" s="52"/>
-      <c r="BU15" s="53"/>
-      <c r="BV15" s="60"/>
-      <c r="BW15" s="57"/>
-      <c r="BX15" s="57"/>
-      <c r="BY15" s="57"/>
-      <c r="BZ15" s="57"/>
-      <c r="CA15" s="52"/>
-      <c r="CB15" s="53"/>
-      <c r="CC15" s="60"/>
-      <c r="CD15" s="57"/>
-      <c r="CE15" s="57"/>
-      <c r="CF15" s="57"/>
-      <c r="CG15" s="57"/>
-      <c r="CH15" s="52"/>
-      <c r="CI15" s="55"/>
-      <c r="CJ15" s="59"/>
-      <c r="CK15" s="57"/>
-      <c r="CL15" s="57"/>
-      <c r="CM15" s="57"/>
-      <c r="CN15" s="57"/>
-      <c r="CO15" s="52"/>
-      <c r="CP15" s="53"/>
-      <c r="CQ15" s="60"/>
-      <c r="CR15" s="57"/>
-      <c r="CS15" s="57"/>
-      <c r="CT15" s="57"/>
-      <c r="CU15" s="57"/>
-      <c r="CV15" s="52"/>
-      <c r="CW15" s="53"/>
-      <c r="CX15" s="60"/>
-      <c r="CY15" s="57"/>
-      <c r="CZ15" s="57"/>
-      <c r="DA15" s="57"/>
-      <c r="DB15" s="57"/>
-      <c r="DC15" s="52"/>
-      <c r="DD15" s="53"/>
-      <c r="DE15" s="60"/>
-      <c r="DF15" s="57"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A16" s="61"/>
@@ -5678,45 +5343,6 @@
       <c r="BQ16" s="57"/>
       <c r="BR16" s="57"/>
       <c r="BS16" s="58"/>
-      <c r="BT16" s="52"/>
-      <c r="BU16" s="53"/>
-      <c r="BV16" s="60"/>
-      <c r="BW16" s="57"/>
-      <c r="BX16" s="57"/>
-      <c r="BY16" s="57"/>
-      <c r="BZ16" s="57"/>
-      <c r="CA16" s="52"/>
-      <c r="CB16" s="53"/>
-      <c r="CC16" s="60"/>
-      <c r="CD16" s="57"/>
-      <c r="CE16" s="57"/>
-      <c r="CF16" s="57"/>
-      <c r="CG16" s="57"/>
-      <c r="CH16" s="52"/>
-      <c r="CI16" s="55"/>
-      <c r="CJ16" s="59"/>
-      <c r="CK16" s="57"/>
-      <c r="CL16" s="57"/>
-      <c r="CM16" s="57"/>
-      <c r="CN16" s="57"/>
-      <c r="CO16" s="52"/>
-      <c r="CP16" s="53"/>
-      <c r="CQ16" s="60"/>
-      <c r="CR16" s="57"/>
-      <c r="CS16" s="57"/>
-      <c r="CT16" s="57"/>
-      <c r="CU16" s="57"/>
-      <c r="CV16" s="52"/>
-      <c r="CW16" s="53"/>
-      <c r="CX16" s="60"/>
-      <c r="CY16" s="57"/>
-      <c r="CZ16" s="57"/>
-      <c r="DA16" s="57"/>
-      <c r="DB16" s="57"/>
-      <c r="DC16" s="52"/>
-      <c r="DD16" s="53"/>
-      <c r="DE16" s="60"/>
-      <c r="DF16" s="57"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A17" s="76"/>
@@ -5790,45 +5416,6 @@
       <c r="BQ17" s="57"/>
       <c r="BR17" s="57"/>
       <c r="BS17" s="58"/>
-      <c r="BT17" s="52"/>
-      <c r="BU17" s="53"/>
-      <c r="BV17" s="60"/>
-      <c r="BW17" s="57"/>
-      <c r="BX17" s="57"/>
-      <c r="BY17" s="57"/>
-      <c r="BZ17" s="57"/>
-      <c r="CA17" s="52"/>
-      <c r="CB17" s="53"/>
-      <c r="CC17" s="60"/>
-      <c r="CD17" s="57"/>
-      <c r="CE17" s="57"/>
-      <c r="CF17" s="57"/>
-      <c r="CG17" s="57"/>
-      <c r="CH17" s="52"/>
-      <c r="CI17" s="55"/>
-      <c r="CJ17" s="59"/>
-      <c r="CK17" s="57"/>
-      <c r="CL17" s="57"/>
-      <c r="CM17" s="57"/>
-      <c r="CN17" s="57"/>
-      <c r="CO17" s="52"/>
-      <c r="CP17" s="53"/>
-      <c r="CQ17" s="60"/>
-      <c r="CR17" s="57"/>
-      <c r="CS17" s="57"/>
-      <c r="CT17" s="57"/>
-      <c r="CU17" s="57"/>
-      <c r="CV17" s="52"/>
-      <c r="CW17" s="53"/>
-      <c r="CX17" s="60"/>
-      <c r="CY17" s="57"/>
-      <c r="CZ17" s="57"/>
-      <c r="DA17" s="57"/>
-      <c r="DB17" s="57"/>
-      <c r="DC17" s="52"/>
-      <c r="DD17" s="53"/>
-      <c r="DE17" s="60"/>
-      <c r="DF17" s="57"/>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A18" s="67"/>
@@ -5902,45 +5489,6 @@
       <c r="BQ18" s="57"/>
       <c r="BR18" s="57"/>
       <c r="BS18" s="58"/>
-      <c r="BT18" s="52"/>
-      <c r="BU18" s="53"/>
-      <c r="BV18" s="60"/>
-      <c r="BW18" s="57"/>
-      <c r="BX18" s="57"/>
-      <c r="BY18" s="57"/>
-      <c r="BZ18" s="57"/>
-      <c r="CA18" s="52"/>
-      <c r="CB18" s="53"/>
-      <c r="CC18" s="60"/>
-      <c r="CD18" s="57"/>
-      <c r="CE18" s="57"/>
-      <c r="CF18" s="57"/>
-      <c r="CG18" s="57"/>
-      <c r="CH18" s="52"/>
-      <c r="CI18" s="55"/>
-      <c r="CJ18" s="59"/>
-      <c r="CK18" s="57"/>
-      <c r="CL18" s="57"/>
-      <c r="CM18" s="57"/>
-      <c r="CN18" s="57"/>
-      <c r="CO18" s="52"/>
-      <c r="CP18" s="53"/>
-      <c r="CQ18" s="60"/>
-      <c r="CR18" s="57"/>
-      <c r="CS18" s="57"/>
-      <c r="CT18" s="57"/>
-      <c r="CU18" s="57"/>
-      <c r="CV18" s="52"/>
-      <c r="CW18" s="53"/>
-      <c r="CX18" s="60"/>
-      <c r="CY18" s="57"/>
-      <c r="CZ18" s="57"/>
-      <c r="DA18" s="57"/>
-      <c r="DB18" s="57"/>
-      <c r="DC18" s="52"/>
-      <c r="DD18" s="53"/>
-      <c r="DE18" s="60"/>
-      <c r="DF18" s="57"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A19" s="67"/>
@@ -6014,45 +5562,6 @@
       <c r="BQ19" s="57"/>
       <c r="BR19" s="57"/>
       <c r="BS19" s="58"/>
-      <c r="BT19" s="52"/>
-      <c r="BU19" s="53"/>
-      <c r="BV19" s="60"/>
-      <c r="BW19" s="57"/>
-      <c r="BX19" s="57"/>
-      <c r="BY19" s="57"/>
-      <c r="BZ19" s="57"/>
-      <c r="CA19" s="52"/>
-      <c r="CB19" s="53"/>
-      <c r="CC19" s="60"/>
-      <c r="CD19" s="57"/>
-      <c r="CE19" s="57"/>
-      <c r="CF19" s="57"/>
-      <c r="CG19" s="57"/>
-      <c r="CH19" s="52"/>
-      <c r="CI19" s="55"/>
-      <c r="CJ19" s="59"/>
-      <c r="CK19" s="57"/>
-      <c r="CL19" s="57"/>
-      <c r="CM19" s="57"/>
-      <c r="CN19" s="57"/>
-      <c r="CO19" s="52"/>
-      <c r="CP19" s="53"/>
-      <c r="CQ19" s="60"/>
-      <c r="CR19" s="57"/>
-      <c r="CS19" s="57"/>
-      <c r="CT19" s="57"/>
-      <c r="CU19" s="57"/>
-      <c r="CV19" s="52"/>
-      <c r="CW19" s="53"/>
-      <c r="CX19" s="60"/>
-      <c r="CY19" s="57"/>
-      <c r="CZ19" s="57"/>
-      <c r="DA19" s="57"/>
-      <c r="DB19" s="57"/>
-      <c r="DC19" s="52"/>
-      <c r="DD19" s="53"/>
-      <c r="DE19" s="60"/>
-      <c r="DF19" s="57"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A20" s="67"/>
@@ -6126,45 +5635,6 @@
       <c r="BQ20" s="57"/>
       <c r="BR20" s="57"/>
       <c r="BS20" s="58"/>
-      <c r="BT20" s="52"/>
-      <c r="BU20" s="53"/>
-      <c r="BV20" s="60"/>
-      <c r="BW20" s="57"/>
-      <c r="BX20" s="57"/>
-      <c r="BY20" s="57"/>
-      <c r="BZ20" s="57"/>
-      <c r="CA20" s="52"/>
-      <c r="CB20" s="53"/>
-      <c r="CC20" s="60"/>
-      <c r="CD20" s="57"/>
-      <c r="CE20" s="57"/>
-      <c r="CF20" s="57"/>
-      <c r="CG20" s="57"/>
-      <c r="CH20" s="52"/>
-      <c r="CI20" s="55"/>
-      <c r="CJ20" s="59"/>
-      <c r="CK20" s="57"/>
-      <c r="CL20" s="57"/>
-      <c r="CM20" s="57"/>
-      <c r="CN20" s="57"/>
-      <c r="CO20" s="52"/>
-      <c r="CP20" s="53"/>
-      <c r="CQ20" s="60"/>
-      <c r="CR20" s="57"/>
-      <c r="CS20" s="57"/>
-      <c r="CT20" s="57"/>
-      <c r="CU20" s="57"/>
-      <c r="CV20" s="52"/>
-      <c r="CW20" s="53"/>
-      <c r="CX20" s="60"/>
-      <c r="CY20" s="57"/>
-      <c r="CZ20" s="57"/>
-      <c r="DA20" s="57"/>
-      <c r="DB20" s="57"/>
-      <c r="DC20" s="52"/>
-      <c r="DD20" s="53"/>
-      <c r="DE20" s="60"/>
-      <c r="DF20" s="57"/>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A21" s="67"/>
@@ -6238,45 +5708,6 @@
       <c r="BQ21" s="57"/>
       <c r="BR21" s="57"/>
       <c r="BS21" s="58"/>
-      <c r="BT21" s="52"/>
-      <c r="BU21" s="53"/>
-      <c r="BV21" s="60"/>
-      <c r="BW21" s="57"/>
-      <c r="BX21" s="57"/>
-      <c r="BY21" s="57"/>
-      <c r="BZ21" s="57"/>
-      <c r="CA21" s="52"/>
-      <c r="CB21" s="53"/>
-      <c r="CC21" s="60"/>
-      <c r="CD21" s="57"/>
-      <c r="CE21" s="57"/>
-      <c r="CF21" s="57"/>
-      <c r="CG21" s="57"/>
-      <c r="CH21" s="52"/>
-      <c r="CI21" s="55"/>
-      <c r="CJ21" s="59"/>
-      <c r="CK21" s="57"/>
-      <c r="CL21" s="57"/>
-      <c r="CM21" s="57"/>
-      <c r="CN21" s="57"/>
-      <c r="CO21" s="52"/>
-      <c r="CP21" s="53"/>
-      <c r="CQ21" s="60"/>
-      <c r="CR21" s="57"/>
-      <c r="CS21" s="57"/>
-      <c r="CT21" s="57"/>
-      <c r="CU21" s="57"/>
-      <c r="CV21" s="52"/>
-      <c r="CW21" s="53"/>
-      <c r="CX21" s="60"/>
-      <c r="CY21" s="57"/>
-      <c r="CZ21" s="57"/>
-      <c r="DA21" s="57"/>
-      <c r="DB21" s="57"/>
-      <c r="DC21" s="52"/>
-      <c r="DD21" s="53"/>
-      <c r="DE21" s="60"/>
-      <c r="DF21" s="57"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A22" s="76"/>
@@ -6350,45 +5781,6 @@
       <c r="BQ22" s="57"/>
       <c r="BR22" s="57"/>
       <c r="BS22" s="58"/>
-      <c r="BT22" s="52"/>
-      <c r="BU22" s="53"/>
-      <c r="BV22" s="60"/>
-      <c r="BW22" s="57"/>
-      <c r="BX22" s="57"/>
-      <c r="BY22" s="57"/>
-      <c r="BZ22" s="57"/>
-      <c r="CA22" s="52"/>
-      <c r="CB22" s="53"/>
-      <c r="CC22" s="60"/>
-      <c r="CD22" s="57"/>
-      <c r="CE22" s="57"/>
-      <c r="CF22" s="57"/>
-      <c r="CG22" s="57"/>
-      <c r="CH22" s="52"/>
-      <c r="CI22" s="55"/>
-      <c r="CJ22" s="59"/>
-      <c r="CK22" s="57"/>
-      <c r="CL22" s="57"/>
-      <c r="CM22" s="57"/>
-      <c r="CN22" s="57"/>
-      <c r="CO22" s="52"/>
-      <c r="CP22" s="53"/>
-      <c r="CQ22" s="60"/>
-      <c r="CR22" s="57"/>
-      <c r="CS22" s="57"/>
-      <c r="CT22" s="57"/>
-      <c r="CU22" s="57"/>
-      <c r="CV22" s="52"/>
-      <c r="CW22" s="53"/>
-      <c r="CX22" s="60"/>
-      <c r="CY22" s="57"/>
-      <c r="CZ22" s="57"/>
-      <c r="DA22" s="57"/>
-      <c r="DB22" s="57"/>
-      <c r="DC22" s="52"/>
-      <c r="DD22" s="53"/>
-      <c r="DE22" s="60"/>
-      <c r="DF22" s="57"/>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A23" s="67"/>
@@ -6462,45 +5854,6 @@
       <c r="BQ23" s="57"/>
       <c r="BR23" s="57"/>
       <c r="BS23" s="58"/>
-      <c r="BT23" s="52"/>
-      <c r="BU23" s="53"/>
-      <c r="BV23" s="60"/>
-      <c r="BW23" s="57"/>
-      <c r="BX23" s="57"/>
-      <c r="BY23" s="57"/>
-      <c r="BZ23" s="57"/>
-      <c r="CA23" s="52"/>
-      <c r="CB23" s="53"/>
-      <c r="CC23" s="60"/>
-      <c r="CD23" s="57"/>
-      <c r="CE23" s="57"/>
-      <c r="CF23" s="57"/>
-      <c r="CG23" s="57"/>
-      <c r="CH23" s="52"/>
-      <c r="CI23" s="55"/>
-      <c r="CJ23" s="59"/>
-      <c r="CK23" s="57"/>
-      <c r="CL23" s="57"/>
-      <c r="CM23" s="57"/>
-      <c r="CN23" s="57"/>
-      <c r="CO23" s="52"/>
-      <c r="CP23" s="53"/>
-      <c r="CQ23" s="60"/>
-      <c r="CR23" s="57"/>
-      <c r="CS23" s="57"/>
-      <c r="CT23" s="57"/>
-      <c r="CU23" s="57"/>
-      <c r="CV23" s="52"/>
-      <c r="CW23" s="53"/>
-      <c r="CX23" s="60"/>
-      <c r="CY23" s="57"/>
-      <c r="CZ23" s="57"/>
-      <c r="DA23" s="57"/>
-      <c r="DB23" s="57"/>
-      <c r="DC23" s="52"/>
-      <c r="DD23" s="53"/>
-      <c r="DE23" s="60"/>
-      <c r="DF23" s="57"/>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A24" s="67"/>
@@ -6574,45 +5927,6 @@
       <c r="BQ24" s="57"/>
       <c r="BR24" s="57"/>
       <c r="BS24" s="58"/>
-      <c r="BT24" s="52"/>
-      <c r="BU24" s="53"/>
-      <c r="BV24" s="60"/>
-      <c r="BW24" s="57"/>
-      <c r="BX24" s="57"/>
-      <c r="BY24" s="57"/>
-      <c r="BZ24" s="57"/>
-      <c r="CA24" s="52"/>
-      <c r="CB24" s="53"/>
-      <c r="CC24" s="60"/>
-      <c r="CD24" s="57"/>
-      <c r="CE24" s="57"/>
-      <c r="CF24" s="57"/>
-      <c r="CG24" s="57"/>
-      <c r="CH24" s="52"/>
-      <c r="CI24" s="55"/>
-      <c r="CJ24" s="59"/>
-      <c r="CK24" s="57"/>
-      <c r="CL24" s="57"/>
-      <c r="CM24" s="57"/>
-      <c r="CN24" s="57"/>
-      <c r="CO24" s="52"/>
-      <c r="CP24" s="53"/>
-      <c r="CQ24" s="60"/>
-      <c r="CR24" s="57"/>
-      <c r="CS24" s="57"/>
-      <c r="CT24" s="57"/>
-      <c r="CU24" s="57"/>
-      <c r="CV24" s="52"/>
-      <c r="CW24" s="53"/>
-      <c r="CX24" s="60"/>
-      <c r="CY24" s="57"/>
-      <c r="CZ24" s="57"/>
-      <c r="DA24" s="57"/>
-      <c r="DB24" s="57"/>
-      <c r="DC24" s="52"/>
-      <c r="DD24" s="53"/>
-      <c r="DE24" s="60"/>
-      <c r="DF24" s="57"/>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A25" s="67"/>
@@ -6686,45 +6000,6 @@
       <c r="BQ25" s="57"/>
       <c r="BR25" s="57"/>
       <c r="BS25" s="58"/>
-      <c r="BT25" s="52"/>
-      <c r="BU25" s="53"/>
-      <c r="BV25" s="60"/>
-      <c r="BW25" s="57"/>
-      <c r="BX25" s="57"/>
-      <c r="BY25" s="57"/>
-      <c r="BZ25" s="57"/>
-      <c r="CA25" s="52"/>
-      <c r="CB25" s="53"/>
-      <c r="CC25" s="60"/>
-      <c r="CD25" s="57"/>
-      <c r="CE25" s="57"/>
-      <c r="CF25" s="57"/>
-      <c r="CG25" s="57"/>
-      <c r="CH25" s="52"/>
-      <c r="CI25" s="55"/>
-      <c r="CJ25" s="59"/>
-      <c r="CK25" s="57"/>
-      <c r="CL25" s="57"/>
-      <c r="CM25" s="57"/>
-      <c r="CN25" s="57"/>
-      <c r="CO25" s="52"/>
-      <c r="CP25" s="53"/>
-      <c r="CQ25" s="60"/>
-      <c r="CR25" s="57"/>
-      <c r="CS25" s="57"/>
-      <c r="CT25" s="57"/>
-      <c r="CU25" s="57"/>
-      <c r="CV25" s="52"/>
-      <c r="CW25" s="53"/>
-      <c r="CX25" s="60"/>
-      <c r="CY25" s="57"/>
-      <c r="CZ25" s="57"/>
-      <c r="DA25" s="57"/>
-      <c r="DB25" s="57"/>
-      <c r="DC25" s="52"/>
-      <c r="DD25" s="53"/>
-      <c r="DE25" s="60"/>
-      <c r="DF25" s="57"/>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A26" s="67"/>
@@ -6798,45 +6073,6 @@
       <c r="BQ26" s="57"/>
       <c r="BR26" s="57"/>
       <c r="BS26" s="58"/>
-      <c r="BT26" s="52"/>
-      <c r="BU26" s="53"/>
-      <c r="BV26" s="60"/>
-      <c r="BW26" s="57"/>
-      <c r="BX26" s="57"/>
-      <c r="BY26" s="57"/>
-      <c r="BZ26" s="57"/>
-      <c r="CA26" s="52"/>
-      <c r="CB26" s="53"/>
-      <c r="CC26" s="60"/>
-      <c r="CD26" s="57"/>
-      <c r="CE26" s="57"/>
-      <c r="CF26" s="57"/>
-      <c r="CG26" s="57"/>
-      <c r="CH26" s="52"/>
-      <c r="CI26" s="55"/>
-      <c r="CJ26" s="59"/>
-      <c r="CK26" s="57"/>
-      <c r="CL26" s="57"/>
-      <c r="CM26" s="57"/>
-      <c r="CN26" s="57"/>
-      <c r="CO26" s="52"/>
-      <c r="CP26" s="53"/>
-      <c r="CQ26" s="60"/>
-      <c r="CR26" s="57"/>
-      <c r="CS26" s="57"/>
-      <c r="CT26" s="57"/>
-      <c r="CU26" s="57"/>
-      <c r="CV26" s="52"/>
-      <c r="CW26" s="53"/>
-      <c r="CX26" s="60"/>
-      <c r="CY26" s="57"/>
-      <c r="CZ26" s="57"/>
-      <c r="DA26" s="57"/>
-      <c r="DB26" s="57"/>
-      <c r="DC26" s="52"/>
-      <c r="DD26" s="53"/>
-      <c r="DE26" s="60"/>
-      <c r="DF26" s="57"/>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="3" collapsed="false">
       <c r="A27" s="67"/>
@@ -6910,45 +6146,6 @@
       <c r="BQ27" s="57"/>
       <c r="BR27" s="57"/>
       <c r="BS27" s="58"/>
-      <c r="BT27" s="52"/>
-      <c r="BU27" s="53"/>
-      <c r="BV27" s="60"/>
-      <c r="BW27" s="57"/>
-      <c r="BX27" s="57"/>
-      <c r="BY27" s="57"/>
-      <c r="BZ27" s="57"/>
-      <c r="CA27" s="52"/>
-      <c r="CB27" s="53"/>
-      <c r="CC27" s="60"/>
-      <c r="CD27" s="57"/>
-      <c r="CE27" s="57"/>
-      <c r="CF27" s="57"/>
-      <c r="CG27" s="57"/>
-      <c r="CH27" s="52"/>
-      <c r="CI27" s="55"/>
-      <c r="CJ27" s="59"/>
-      <c r="CK27" s="57"/>
-      <c r="CL27" s="57"/>
-      <c r="CM27" s="57"/>
-      <c r="CN27" s="57"/>
-      <c r="CO27" s="52"/>
-      <c r="CP27" s="53"/>
-      <c r="CQ27" s="60"/>
-      <c r="CR27" s="57"/>
-      <c r="CS27" s="57"/>
-      <c r="CT27" s="57"/>
-      <c r="CU27" s="57"/>
-      <c r="CV27" s="52"/>
-      <c r="CW27" s="53"/>
-      <c r="CX27" s="60"/>
-      <c r="CY27" s="57"/>
-      <c r="CZ27" s="57"/>
-      <c r="DA27" s="57"/>
-      <c r="DB27" s="57"/>
-      <c r="DC27" s="52"/>
-      <c r="DD27" s="53"/>
-      <c r="DE27" s="60"/>
-      <c r="DF27" s="57"/>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A28" s="61"/>
@@ -7022,45 +6219,6 @@
       <c r="BQ28" s="57"/>
       <c r="BR28" s="57"/>
       <c r="BS28" s="58"/>
-      <c r="BT28" s="52"/>
-      <c r="BU28" s="53"/>
-      <c r="BV28" s="60"/>
-      <c r="BW28" s="57"/>
-      <c r="BX28" s="57"/>
-      <c r="BY28" s="57"/>
-      <c r="BZ28" s="57"/>
-      <c r="CA28" s="52"/>
-      <c r="CB28" s="53"/>
-      <c r="CC28" s="60"/>
-      <c r="CD28" s="57"/>
-      <c r="CE28" s="57"/>
-      <c r="CF28" s="57"/>
-      <c r="CG28" s="57"/>
-      <c r="CH28" s="52"/>
-      <c r="CI28" s="55"/>
-      <c r="CJ28" s="59"/>
-      <c r="CK28" s="57"/>
-      <c r="CL28" s="57"/>
-      <c r="CM28" s="57"/>
-      <c r="CN28" s="57"/>
-      <c r="CO28" s="52"/>
-      <c r="CP28" s="53"/>
-      <c r="CQ28" s="60"/>
-      <c r="CR28" s="57"/>
-      <c r="CS28" s="57"/>
-      <c r="CT28" s="57"/>
-      <c r="CU28" s="57"/>
-      <c r="CV28" s="52"/>
-      <c r="CW28" s="53"/>
-      <c r="CX28" s="60"/>
-      <c r="CY28" s="57"/>
-      <c r="CZ28" s="57"/>
-      <c r="DA28" s="57"/>
-      <c r="DB28" s="57"/>
-      <c r="DC28" s="52"/>
-      <c r="DD28" s="53"/>
-      <c r="DE28" s="60"/>
-      <c r="DF28" s="57"/>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A29" s="67"/>
@@ -7134,45 +6292,6 @@
       <c r="BQ29" s="57"/>
       <c r="BR29" s="57"/>
       <c r="BS29" s="58"/>
-      <c r="BT29" s="52"/>
-      <c r="BU29" s="53"/>
-      <c r="BV29" s="60"/>
-      <c r="BW29" s="57"/>
-      <c r="BX29" s="57"/>
-      <c r="BY29" s="57"/>
-      <c r="BZ29" s="57"/>
-      <c r="CA29" s="52"/>
-      <c r="CB29" s="53"/>
-      <c r="CC29" s="60"/>
-      <c r="CD29" s="57"/>
-      <c r="CE29" s="57"/>
-      <c r="CF29" s="57"/>
-      <c r="CG29" s="57"/>
-      <c r="CH29" s="52"/>
-      <c r="CI29" s="55"/>
-      <c r="CJ29" s="59"/>
-      <c r="CK29" s="57"/>
-      <c r="CL29" s="57"/>
-      <c r="CM29" s="57"/>
-      <c r="CN29" s="57"/>
-      <c r="CO29" s="52"/>
-      <c r="CP29" s="53"/>
-      <c r="CQ29" s="60"/>
-      <c r="CR29" s="57"/>
-      <c r="CS29" s="57"/>
-      <c r="CT29" s="57"/>
-      <c r="CU29" s="57"/>
-      <c r="CV29" s="52"/>
-      <c r="CW29" s="53"/>
-      <c r="CX29" s="60"/>
-      <c r="CY29" s="57"/>
-      <c r="CZ29" s="57"/>
-      <c r="DA29" s="57"/>
-      <c r="DB29" s="57"/>
-      <c r="DC29" s="52"/>
-      <c r="DD29" s="53"/>
-      <c r="DE29" s="60"/>
-      <c r="DF29" s="57"/>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A30" s="67"/>
@@ -7246,45 +6365,6 @@
       <c r="BQ30" s="57"/>
       <c r="BR30" s="57"/>
       <c r="BS30" s="58"/>
-      <c r="BT30" s="52"/>
-      <c r="BU30" s="53"/>
-      <c r="BV30" s="60"/>
-      <c r="BW30" s="57"/>
-      <c r="BX30" s="57"/>
-      <c r="BY30" s="57"/>
-      <c r="BZ30" s="57"/>
-      <c r="CA30" s="52"/>
-      <c r="CB30" s="53"/>
-      <c r="CC30" s="60"/>
-      <c r="CD30" s="57"/>
-      <c r="CE30" s="57"/>
-      <c r="CF30" s="57"/>
-      <c r="CG30" s="57"/>
-      <c r="CH30" s="52"/>
-      <c r="CI30" s="55"/>
-      <c r="CJ30" s="59"/>
-      <c r="CK30" s="57"/>
-      <c r="CL30" s="57"/>
-      <c r="CM30" s="57"/>
-      <c r="CN30" s="57"/>
-      <c r="CO30" s="52"/>
-      <c r="CP30" s="53"/>
-      <c r="CQ30" s="60"/>
-      <c r="CR30" s="57"/>
-      <c r="CS30" s="57"/>
-      <c r="CT30" s="57"/>
-      <c r="CU30" s="57"/>
-      <c r="CV30" s="52"/>
-      <c r="CW30" s="53"/>
-      <c r="CX30" s="60"/>
-      <c r="CY30" s="57"/>
-      <c r="CZ30" s="57"/>
-      <c r="DA30" s="57"/>
-      <c r="DB30" s="57"/>
-      <c r="DC30" s="52"/>
-      <c r="DD30" s="53"/>
-      <c r="DE30" s="60"/>
-      <c r="DF30" s="57"/>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="2" collapsed="false">
       <c r="A31" s="67"/>
@@ -7358,45 +6438,6 @@
       <c r="BQ31" s="57"/>
       <c r="BR31" s="57"/>
       <c r="BS31" s="58"/>
-      <c r="BT31" s="52"/>
-      <c r="BU31" s="53"/>
-      <c r="BV31" s="60"/>
-      <c r="BW31" s="57"/>
-      <c r="BX31" s="57"/>
-      <c r="BY31" s="57"/>
-      <c r="BZ31" s="57"/>
-      <c r="CA31" s="52"/>
-      <c r="CB31" s="53"/>
-      <c r="CC31" s="60"/>
-      <c r="CD31" s="57"/>
-      <c r="CE31" s="57"/>
-      <c r="CF31" s="57"/>
-      <c r="CG31" s="57"/>
-      <c r="CH31" s="52"/>
-      <c r="CI31" s="55"/>
-      <c r="CJ31" s="59"/>
-      <c r="CK31" s="57"/>
-      <c r="CL31" s="57"/>
-      <c r="CM31" s="57"/>
-      <c r="CN31" s="57"/>
-      <c r="CO31" s="52"/>
-      <c r="CP31" s="53"/>
-      <c r="CQ31" s="60"/>
-      <c r="CR31" s="57"/>
-      <c r="CS31" s="57"/>
-      <c r="CT31" s="57"/>
-      <c r="CU31" s="57"/>
-      <c r="CV31" s="52"/>
-      <c r="CW31" s="53"/>
-      <c r="CX31" s="60"/>
-      <c r="CY31" s="57"/>
-      <c r="CZ31" s="57"/>
-      <c r="DA31" s="57"/>
-      <c r="DB31" s="57"/>
-      <c r="DC31" s="52"/>
-      <c r="DD31" s="53"/>
-      <c r="DE31" s="60"/>
-      <c r="DF31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="83"/>
@@ -7470,45 +6511,6 @@
       <c r="BQ32" s="91"/>
       <c r="BR32" s="91"/>
       <c r="BS32" s="91"/>
-      <c r="BT32" s="92"/>
-      <c r="BU32" s="93"/>
-      <c r="BV32" s="90"/>
-      <c r="BW32" s="91"/>
-      <c r="BX32" s="91"/>
-      <c r="BY32" s="91"/>
-      <c r="BZ32" s="91"/>
-      <c r="CA32" s="92"/>
-      <c r="CB32" s="93"/>
-      <c r="CC32" s="90"/>
-      <c r="CD32" s="91"/>
-      <c r="CE32" s="91"/>
-      <c r="CF32" s="91"/>
-      <c r="CG32" s="91"/>
-      <c r="CH32" s="92"/>
-      <c r="CI32" s="94"/>
-      <c r="CJ32" s="95"/>
-      <c r="CK32" s="91"/>
-      <c r="CL32" s="91"/>
-      <c r="CM32" s="91"/>
-      <c r="CN32" s="91"/>
-      <c r="CO32" s="92"/>
-      <c r="CP32" s="93"/>
-      <c r="CQ32" s="90"/>
-      <c r="CR32" s="91"/>
-      <c r="CS32" s="91"/>
-      <c r="CT32" s="91"/>
-      <c r="CU32" s="91"/>
-      <c r="CV32" s="92"/>
-      <c r="CW32" s="93"/>
-      <c r="CX32" s="90"/>
-      <c r="CY32" s="91"/>
-      <c r="CZ32" s="91"/>
-      <c r="DA32" s="91"/>
-      <c r="DB32" s="91"/>
-      <c r="DC32" s="92"/>
-      <c r="DD32" s="93"/>
-      <c r="DE32" s="90"/>
-      <c r="DF32" s="91"/>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96"/>
@@ -7582,45 +6584,6 @@
       <c r="BQ33" s="91"/>
       <c r="BR33" s="91"/>
       <c r="BS33" s="91"/>
-      <c r="BT33" s="92"/>
-      <c r="BU33" s="93"/>
-      <c r="BV33" s="90"/>
-      <c r="BW33" s="91"/>
-      <c r="BX33" s="91"/>
-      <c r="BY33" s="91"/>
-      <c r="BZ33" s="91"/>
-      <c r="CA33" s="92"/>
-      <c r="CB33" s="93"/>
-      <c r="CC33" s="90"/>
-      <c r="CD33" s="91"/>
-      <c r="CE33" s="91"/>
-      <c r="CF33" s="91"/>
-      <c r="CG33" s="91"/>
-      <c r="CH33" s="92"/>
-      <c r="CI33" s="94"/>
-      <c r="CJ33" s="95"/>
-      <c r="CK33" s="91"/>
-      <c r="CL33" s="91"/>
-      <c r="CM33" s="91"/>
-      <c r="CN33" s="91"/>
-      <c r="CO33" s="92"/>
-      <c r="CP33" s="93"/>
-      <c r="CQ33" s="90"/>
-      <c r="CR33" s="91"/>
-      <c r="CS33" s="91"/>
-      <c r="CT33" s="91"/>
-      <c r="CU33" s="91"/>
-      <c r="CV33" s="92"/>
-      <c r="CW33" s="93"/>
-      <c r="CX33" s="90"/>
-      <c r="CY33" s="91"/>
-      <c r="CZ33" s="91"/>
-      <c r="DA33" s="91"/>
-      <c r="DB33" s="91"/>
-      <c r="DC33" s="92"/>
-      <c r="DD33" s="93"/>
-      <c r="DE33" s="90"/>
-      <c r="DF33" s="91"/>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="96"/>
@@ -7694,45 +6657,6 @@
       <c r="BQ34" s="91"/>
       <c r="BR34" s="91"/>
       <c r="BS34" s="91"/>
-      <c r="BT34" s="92"/>
-      <c r="BU34" s="93"/>
-      <c r="BV34" s="90"/>
-      <c r="BW34" s="91"/>
-      <c r="BX34" s="91"/>
-      <c r="BY34" s="91"/>
-      <c r="BZ34" s="91"/>
-      <c r="CA34" s="92"/>
-      <c r="CB34" s="93"/>
-      <c r="CC34" s="90"/>
-      <c r="CD34" s="91"/>
-      <c r="CE34" s="91"/>
-      <c r="CF34" s="91"/>
-      <c r="CG34" s="91"/>
-      <c r="CH34" s="92"/>
-      <c r="CI34" s="94"/>
-      <c r="CJ34" s="95"/>
-      <c r="CK34" s="91"/>
-      <c r="CL34" s="91"/>
-      <c r="CM34" s="91"/>
-      <c r="CN34" s="91"/>
-      <c r="CO34" s="92"/>
-      <c r="CP34" s="93"/>
-      <c r="CQ34" s="90"/>
-      <c r="CR34" s="91"/>
-      <c r="CS34" s="91"/>
-      <c r="CT34" s="91"/>
-      <c r="CU34" s="91"/>
-      <c r="CV34" s="92"/>
-      <c r="CW34" s="93"/>
-      <c r="CX34" s="90"/>
-      <c r="CY34" s="91"/>
-      <c r="CZ34" s="91"/>
-      <c r="DA34" s="91"/>
-      <c r="DB34" s="91"/>
-      <c r="DC34" s="92"/>
-      <c r="DD34" s="93"/>
-      <c r="DE34" s="90"/>
-      <c r="DF34" s="91"/>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="96"/>
@@ -7806,45 +6730,6 @@
       <c r="BQ35" s="91"/>
       <c r="BR35" s="91"/>
       <c r="BS35" s="91"/>
-      <c r="BT35" s="92"/>
-      <c r="BU35" s="93"/>
-      <c r="BV35" s="90"/>
-      <c r="BW35" s="91"/>
-      <c r="BX35" s="91"/>
-      <c r="BY35" s="91"/>
-      <c r="BZ35" s="91"/>
-      <c r="CA35" s="92"/>
-      <c r="CB35" s="93"/>
-      <c r="CC35" s="90"/>
-      <c r="CD35" s="91"/>
-      <c r="CE35" s="91"/>
-      <c r="CF35" s="91"/>
-      <c r="CG35" s="91"/>
-      <c r="CH35" s="92"/>
-      <c r="CI35" s="94"/>
-      <c r="CJ35" s="95"/>
-      <c r="CK35" s="91"/>
-      <c r="CL35" s="91"/>
-      <c r="CM35" s="91"/>
-      <c r="CN35" s="91"/>
-      <c r="CO35" s="92"/>
-      <c r="CP35" s="93"/>
-      <c r="CQ35" s="90"/>
-      <c r="CR35" s="91"/>
-      <c r="CS35" s="91"/>
-      <c r="CT35" s="91"/>
-      <c r="CU35" s="91"/>
-      <c r="CV35" s="92"/>
-      <c r="CW35" s="93"/>
-      <c r="CX35" s="90"/>
-      <c r="CY35" s="91"/>
-      <c r="CZ35" s="91"/>
-      <c r="DA35" s="91"/>
-      <c r="DB35" s="91"/>
-      <c r="DC35" s="92"/>
-      <c r="DD35" s="93"/>
-      <c r="DE35" s="90"/>
-      <c r="DF35" s="91"/>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="96"/>
@@ -7918,45 +6803,6 @@
       <c r="BQ36" s="91"/>
       <c r="BR36" s="91"/>
       <c r="BS36" s="91"/>
-      <c r="BT36" s="92"/>
-      <c r="BU36" s="93"/>
-      <c r="BV36" s="90"/>
-      <c r="BW36" s="91"/>
-      <c r="BX36" s="91"/>
-      <c r="BY36" s="91"/>
-      <c r="BZ36" s="91"/>
-      <c r="CA36" s="92"/>
-      <c r="CB36" s="93"/>
-      <c r="CC36" s="90"/>
-      <c r="CD36" s="91"/>
-      <c r="CE36" s="91"/>
-      <c r="CF36" s="91"/>
-      <c r="CG36" s="91"/>
-      <c r="CH36" s="92"/>
-      <c r="CI36" s="94"/>
-      <c r="CJ36" s="95"/>
-      <c r="CK36" s="91"/>
-      <c r="CL36" s="91"/>
-      <c r="CM36" s="91"/>
-      <c r="CN36" s="91"/>
-      <c r="CO36" s="92"/>
-      <c r="CP36" s="93"/>
-      <c r="CQ36" s="90"/>
-      <c r="CR36" s="91"/>
-      <c r="CS36" s="91"/>
-      <c r="CT36" s="91"/>
-      <c r="CU36" s="91"/>
-      <c r="CV36" s="92"/>
-      <c r="CW36" s="93"/>
-      <c r="CX36" s="90"/>
-      <c r="CY36" s="91"/>
-      <c r="CZ36" s="91"/>
-      <c r="DA36" s="91"/>
-      <c r="DB36" s="91"/>
-      <c r="DC36" s="92"/>
-      <c r="DD36" s="93"/>
-      <c r="DE36" s="90"/>
-      <c r="DF36" s="91"/>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="83"/>
@@ -8030,45 +6876,6 @@
       <c r="BQ37" s="91"/>
       <c r="BR37" s="91"/>
       <c r="BS37" s="91"/>
-      <c r="BT37" s="92"/>
-      <c r="BU37" s="93"/>
-      <c r="BV37" s="90"/>
-      <c r="BW37" s="91"/>
-      <c r="BX37" s="91"/>
-      <c r="BY37" s="91"/>
-      <c r="BZ37" s="91"/>
-      <c r="CA37" s="92"/>
-      <c r="CB37" s="93"/>
-      <c r="CC37" s="90"/>
-      <c r="CD37" s="91"/>
-      <c r="CE37" s="91"/>
-      <c r="CF37" s="91"/>
-      <c r="CG37" s="91"/>
-      <c r="CH37" s="92"/>
-      <c r="CI37" s="94"/>
-      <c r="CJ37" s="95"/>
-      <c r="CK37" s="91"/>
-      <c r="CL37" s="91"/>
-      <c r="CM37" s="91"/>
-      <c r="CN37" s="91"/>
-      <c r="CO37" s="92"/>
-      <c r="CP37" s="93"/>
-      <c r="CQ37" s="90"/>
-      <c r="CR37" s="91"/>
-      <c r="CS37" s="91"/>
-      <c r="CT37" s="91"/>
-      <c r="CU37" s="91"/>
-      <c r="CV37" s="92"/>
-      <c r="CW37" s="93"/>
-      <c r="CX37" s="90"/>
-      <c r="CY37" s="91"/>
-      <c r="CZ37" s="91"/>
-      <c r="DA37" s="91"/>
-      <c r="DB37" s="91"/>
-      <c r="DC37" s="92"/>
-      <c r="DD37" s="93"/>
-      <c r="DE37" s="90"/>
-      <c r="DF37" s="91"/>
     </row>
     <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="96"/>
@@ -8142,45 +6949,6 @@
       <c r="BQ38" s="91"/>
       <c r="BR38" s="91"/>
       <c r="BS38" s="91"/>
-      <c r="BT38" s="92"/>
-      <c r="BU38" s="93"/>
-      <c r="BV38" s="90"/>
-      <c r="BW38" s="91"/>
-      <c r="BX38" s="91"/>
-      <c r="BY38" s="91"/>
-      <c r="BZ38" s="91"/>
-      <c r="CA38" s="92"/>
-      <c r="CB38" s="93"/>
-      <c r="CC38" s="90"/>
-      <c r="CD38" s="91"/>
-      <c r="CE38" s="91"/>
-      <c r="CF38" s="91"/>
-      <c r="CG38" s="91"/>
-      <c r="CH38" s="92"/>
-      <c r="CI38" s="94"/>
-      <c r="CJ38" s="95"/>
-      <c r="CK38" s="91"/>
-      <c r="CL38" s="91"/>
-      <c r="CM38" s="91"/>
-      <c r="CN38" s="91"/>
-      <c r="CO38" s="92"/>
-      <c r="CP38" s="93"/>
-      <c r="CQ38" s="90"/>
-      <c r="CR38" s="91"/>
-      <c r="CS38" s="91"/>
-      <c r="CT38" s="91"/>
-      <c r="CU38" s="91"/>
-      <c r="CV38" s="92"/>
-      <c r="CW38" s="93"/>
-      <c r="CX38" s="90"/>
-      <c r="CY38" s="91"/>
-      <c r="CZ38" s="91"/>
-      <c r="DA38" s="91"/>
-      <c r="DB38" s="91"/>
-      <c r="DC38" s="92"/>
-      <c r="DD38" s="93"/>
-      <c r="DE38" s="90"/>
-      <c r="DF38" s="91"/>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="102"/>
@@ -8254,45 +7022,6 @@
       <c r="BQ39" s="110"/>
       <c r="BR39" s="110"/>
       <c r="BS39" s="110"/>
-      <c r="BT39" s="111"/>
-      <c r="BU39" s="112"/>
-      <c r="BV39" s="109"/>
-      <c r="BW39" s="110"/>
-      <c r="BX39" s="110"/>
-      <c r="BY39" s="110"/>
-      <c r="BZ39" s="110"/>
-      <c r="CA39" s="111"/>
-      <c r="CB39" s="112"/>
-      <c r="CC39" s="109"/>
-      <c r="CD39" s="110"/>
-      <c r="CE39" s="110"/>
-      <c r="CF39" s="110"/>
-      <c r="CG39" s="110"/>
-      <c r="CH39" s="111"/>
-      <c r="CI39" s="113"/>
-      <c r="CJ39" s="114"/>
-      <c r="CK39" s="110"/>
-      <c r="CL39" s="110"/>
-      <c r="CM39" s="110"/>
-      <c r="CN39" s="110"/>
-      <c r="CO39" s="111"/>
-      <c r="CP39" s="112"/>
-      <c r="CQ39" s="109"/>
-      <c r="CR39" s="110"/>
-      <c r="CS39" s="110"/>
-      <c r="CT39" s="110"/>
-      <c r="CU39" s="110"/>
-      <c r="CV39" s="111"/>
-      <c r="CW39" s="112"/>
-      <c r="CX39" s="109"/>
-      <c r="CY39" s="110"/>
-      <c r="CZ39" s="110"/>
-      <c r="DA39" s="110"/>
-      <c r="DB39" s="110"/>
-      <c r="DC39" s="111"/>
-      <c r="DD39" s="112"/>
-      <c r="DE39" s="109"/>
-      <c r="DF39" s="110"/>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="83"/>
@@ -8366,45 +7095,6 @@
       <c r="BQ40" s="91"/>
       <c r="BR40" s="91"/>
       <c r="BS40" s="91"/>
-      <c r="BT40" s="92"/>
-      <c r="BU40" s="93"/>
-      <c r="BV40" s="90"/>
-      <c r="BW40" s="91"/>
-      <c r="BX40" s="91"/>
-      <c r="BY40" s="91"/>
-      <c r="BZ40" s="91"/>
-      <c r="CA40" s="92"/>
-      <c r="CB40" s="93"/>
-      <c r="CC40" s="90"/>
-      <c r="CD40" s="91"/>
-      <c r="CE40" s="91"/>
-      <c r="CF40" s="91"/>
-      <c r="CG40" s="91"/>
-      <c r="CH40" s="92"/>
-      <c r="CI40" s="94"/>
-      <c r="CJ40" s="95"/>
-      <c r="CK40" s="91"/>
-      <c r="CL40" s="91"/>
-      <c r="CM40" s="91"/>
-      <c r="CN40" s="91"/>
-      <c r="CO40" s="92"/>
-      <c r="CP40" s="93"/>
-      <c r="CQ40" s="90"/>
-      <c r="CR40" s="91"/>
-      <c r="CS40" s="91"/>
-      <c r="CT40" s="91"/>
-      <c r="CU40" s="91"/>
-      <c r="CV40" s="92"/>
-      <c r="CW40" s="93"/>
-      <c r="CX40" s="90"/>
-      <c r="CY40" s="91"/>
-      <c r="CZ40" s="91"/>
-      <c r="DA40" s="91"/>
-      <c r="DB40" s="91"/>
-      <c r="DC40" s="92"/>
-      <c r="DD40" s="93"/>
-      <c r="DE40" s="90"/>
-      <c r="DF40" s="91"/>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="83"/>
@@ -8478,45 +7168,6 @@
       <c r="BQ41" s="91"/>
       <c r="BR41" s="91"/>
       <c r="BS41" s="91"/>
-      <c r="BT41" s="92"/>
-      <c r="BU41" s="93"/>
-      <c r="BV41" s="90"/>
-      <c r="BW41" s="91"/>
-      <c r="BX41" s="91"/>
-      <c r="BY41" s="91"/>
-      <c r="BZ41" s="91"/>
-      <c r="CA41" s="92"/>
-      <c r="CB41" s="93"/>
-      <c r="CC41" s="90"/>
-      <c r="CD41" s="91"/>
-      <c r="CE41" s="91"/>
-      <c r="CF41" s="91"/>
-      <c r="CG41" s="91"/>
-      <c r="CH41" s="92"/>
-      <c r="CI41" s="94"/>
-      <c r="CJ41" s="95"/>
-      <c r="CK41" s="91"/>
-      <c r="CL41" s="91"/>
-      <c r="CM41" s="91"/>
-      <c r="CN41" s="91"/>
-      <c r="CO41" s="92"/>
-      <c r="CP41" s="93"/>
-      <c r="CQ41" s="90"/>
-      <c r="CR41" s="91"/>
-      <c r="CS41" s="91"/>
-      <c r="CT41" s="91"/>
-      <c r="CU41" s="91"/>
-      <c r="CV41" s="92"/>
-      <c r="CW41" s="93"/>
-      <c r="CX41" s="90"/>
-      <c r="CY41" s="91"/>
-      <c r="CZ41" s="91"/>
-      <c r="DA41" s="91"/>
-      <c r="DB41" s="91"/>
-      <c r="DC41" s="92"/>
-      <c r="DD41" s="93"/>
-      <c r="DE41" s="90"/>
-      <c r="DF41" s="91"/>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="96"/>
@@ -8590,45 +7241,6 @@
       <c r="BQ42" s="91"/>
       <c r="BR42" s="91"/>
       <c r="BS42" s="91"/>
-      <c r="BT42" s="92"/>
-      <c r="BU42" s="93"/>
-      <c r="BV42" s="90"/>
-      <c r="BW42" s="91"/>
-      <c r="BX42" s="91"/>
-      <c r="BY42" s="91"/>
-      <c r="BZ42" s="91"/>
-      <c r="CA42" s="92"/>
-      <c r="CB42" s="93"/>
-      <c r="CC42" s="90"/>
-      <c r="CD42" s="91"/>
-      <c r="CE42" s="91"/>
-      <c r="CF42" s="91"/>
-      <c r="CG42" s="91"/>
-      <c r="CH42" s="92"/>
-      <c r="CI42" s="94"/>
-      <c r="CJ42" s="95"/>
-      <c r="CK42" s="91"/>
-      <c r="CL42" s="91"/>
-      <c r="CM42" s="91"/>
-      <c r="CN42" s="91"/>
-      <c r="CO42" s="92"/>
-      <c r="CP42" s="93"/>
-      <c r="CQ42" s="90"/>
-      <c r="CR42" s="91"/>
-      <c r="CS42" s="91"/>
-      <c r="CT42" s="91"/>
-      <c r="CU42" s="91"/>
-      <c r="CV42" s="92"/>
-      <c r="CW42" s="93"/>
-      <c r="CX42" s="90"/>
-      <c r="CY42" s="91"/>
-      <c r="CZ42" s="91"/>
-      <c r="DA42" s="91"/>
-      <c r="DB42" s="91"/>
-      <c r="DC42" s="92"/>
-      <c r="DD42" s="93"/>
-      <c r="DE42" s="90"/>
-      <c r="DF42" s="91"/>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="96"/>
@@ -8702,45 +7314,6 @@
       <c r="BQ43" s="91"/>
       <c r="BR43" s="91"/>
       <c r="BS43" s="91"/>
-      <c r="BT43" s="92"/>
-      <c r="BU43" s="93"/>
-      <c r="BV43" s="90"/>
-      <c r="BW43" s="91"/>
-      <c r="BX43" s="91"/>
-      <c r="BY43" s="91"/>
-      <c r="BZ43" s="91"/>
-      <c r="CA43" s="92"/>
-      <c r="CB43" s="93"/>
-      <c r="CC43" s="90"/>
-      <c r="CD43" s="91"/>
-      <c r="CE43" s="91"/>
-      <c r="CF43" s="91"/>
-      <c r="CG43" s="91"/>
-      <c r="CH43" s="92"/>
-      <c r="CI43" s="94"/>
-      <c r="CJ43" s="95"/>
-      <c r="CK43" s="91"/>
-      <c r="CL43" s="91"/>
-      <c r="CM43" s="91"/>
-      <c r="CN43" s="91"/>
-      <c r="CO43" s="92"/>
-      <c r="CP43" s="93"/>
-      <c r="CQ43" s="90"/>
-      <c r="CR43" s="91"/>
-      <c r="CS43" s="91"/>
-      <c r="CT43" s="91"/>
-      <c r="CU43" s="91"/>
-      <c r="CV43" s="92"/>
-      <c r="CW43" s="93"/>
-      <c r="CX43" s="90"/>
-      <c r="CY43" s="91"/>
-      <c r="CZ43" s="91"/>
-      <c r="DA43" s="91"/>
-      <c r="DB43" s="91"/>
-      <c r="DC43" s="92"/>
-      <c r="DD43" s="93"/>
-      <c r="DE43" s="90"/>
-      <c r="DF43" s="91"/>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="96"/>
@@ -8814,45 +7387,6 @@
       <c r="BQ44" s="91"/>
       <c r="BR44" s="91"/>
       <c r="BS44" s="91"/>
-      <c r="BT44" s="92"/>
-      <c r="BU44" s="93"/>
-      <c r="BV44" s="90"/>
-      <c r="BW44" s="91"/>
-      <c r="BX44" s="91"/>
-      <c r="BY44" s="91"/>
-      <c r="BZ44" s="91"/>
-      <c r="CA44" s="92"/>
-      <c r="CB44" s="93"/>
-      <c r="CC44" s="90"/>
-      <c r="CD44" s="91"/>
-      <c r="CE44" s="91"/>
-      <c r="CF44" s="91"/>
-      <c r="CG44" s="91"/>
-      <c r="CH44" s="92"/>
-      <c r="CI44" s="94"/>
-      <c r="CJ44" s="95"/>
-      <c r="CK44" s="91"/>
-      <c r="CL44" s="91"/>
-      <c r="CM44" s="91"/>
-      <c r="CN44" s="91"/>
-      <c r="CO44" s="92"/>
-      <c r="CP44" s="93"/>
-      <c r="CQ44" s="90"/>
-      <c r="CR44" s="91"/>
-      <c r="CS44" s="91"/>
-      <c r="CT44" s="91"/>
-      <c r="CU44" s="91"/>
-      <c r="CV44" s="92"/>
-      <c r="CW44" s="93"/>
-      <c r="CX44" s="90"/>
-      <c r="CY44" s="91"/>
-      <c r="CZ44" s="91"/>
-      <c r="DA44" s="91"/>
-      <c r="DB44" s="91"/>
-      <c r="DC44" s="92"/>
-      <c r="DD44" s="93"/>
-      <c r="DE44" s="90"/>
-      <c r="DF44" s="91"/>
     </row>
     <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="96"/>
@@ -8926,45 +7460,6 @@
       <c r="BQ45" s="91"/>
       <c r="BR45" s="91"/>
       <c r="BS45" s="91"/>
-      <c r="BT45" s="92"/>
-      <c r="BU45" s="93"/>
-      <c r="BV45" s="90"/>
-      <c r="BW45" s="91"/>
-      <c r="BX45" s="91"/>
-      <c r="BY45" s="91"/>
-      <c r="BZ45" s="91"/>
-      <c r="CA45" s="92"/>
-      <c r="CB45" s="93"/>
-      <c r="CC45" s="90"/>
-      <c r="CD45" s="91"/>
-      <c r="CE45" s="91"/>
-      <c r="CF45" s="91"/>
-      <c r="CG45" s="91"/>
-      <c r="CH45" s="92"/>
-      <c r="CI45" s="94"/>
-      <c r="CJ45" s="95"/>
-      <c r="CK45" s="91"/>
-      <c r="CL45" s="91"/>
-      <c r="CM45" s="91"/>
-      <c r="CN45" s="91"/>
-      <c r="CO45" s="92"/>
-      <c r="CP45" s="93"/>
-      <c r="CQ45" s="90"/>
-      <c r="CR45" s="91"/>
-      <c r="CS45" s="91"/>
-      <c r="CT45" s="91"/>
-      <c r="CU45" s="91"/>
-      <c r="CV45" s="92"/>
-      <c r="CW45" s="93"/>
-      <c r="CX45" s="90"/>
-      <c r="CY45" s="91"/>
-      <c r="CZ45" s="91"/>
-      <c r="DA45" s="91"/>
-      <c r="DB45" s="91"/>
-      <c r="DC45" s="92"/>
-      <c r="DD45" s="93"/>
-      <c r="DE45" s="90"/>
-      <c r="DF45" s="91"/>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="83"/>
@@ -9038,45 +7533,6 @@
       <c r="BQ46" s="91"/>
       <c r="BR46" s="91"/>
       <c r="BS46" s="91"/>
-      <c r="BT46" s="92"/>
-      <c r="BU46" s="93"/>
-      <c r="BV46" s="90"/>
-      <c r="BW46" s="91"/>
-      <c r="BX46" s="91"/>
-      <c r="BY46" s="91"/>
-      <c r="BZ46" s="91"/>
-      <c r="CA46" s="92"/>
-      <c r="CB46" s="93"/>
-      <c r="CC46" s="90"/>
-      <c r="CD46" s="91"/>
-      <c r="CE46" s="91"/>
-      <c r="CF46" s="91"/>
-      <c r="CG46" s="91"/>
-      <c r="CH46" s="92"/>
-      <c r="CI46" s="94"/>
-      <c r="CJ46" s="95"/>
-      <c r="CK46" s="91"/>
-      <c r="CL46" s="91"/>
-      <c r="CM46" s="91"/>
-      <c r="CN46" s="91"/>
-      <c r="CO46" s="92"/>
-      <c r="CP46" s="93"/>
-      <c r="CQ46" s="90"/>
-      <c r="CR46" s="91"/>
-      <c r="CS46" s="91"/>
-      <c r="CT46" s="91"/>
-      <c r="CU46" s="91"/>
-      <c r="CV46" s="92"/>
-      <c r="CW46" s="93"/>
-      <c r="CX46" s="90"/>
-      <c r="CY46" s="91"/>
-      <c r="CZ46" s="91"/>
-      <c r="DA46" s="91"/>
-      <c r="DB46" s="91"/>
-      <c r="DC46" s="92"/>
-      <c r="DD46" s="93"/>
-      <c r="DE46" s="90"/>
-      <c r="DF46" s="91"/>
     </row>
     <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="96"/>
@@ -9150,45 +7606,6 @@
       <c r="BQ47" s="91"/>
       <c r="BR47" s="91"/>
       <c r="BS47" s="91"/>
-      <c r="BT47" s="92"/>
-      <c r="BU47" s="93"/>
-      <c r="BV47" s="90"/>
-      <c r="BW47" s="91"/>
-      <c r="BX47" s="91"/>
-      <c r="BY47" s="91"/>
-      <c r="BZ47" s="91"/>
-      <c r="CA47" s="92"/>
-      <c r="CB47" s="93"/>
-      <c r="CC47" s="90"/>
-      <c r="CD47" s="91"/>
-      <c r="CE47" s="91"/>
-      <c r="CF47" s="91"/>
-      <c r="CG47" s="91"/>
-      <c r="CH47" s="92"/>
-      <c r="CI47" s="94"/>
-      <c r="CJ47" s="95"/>
-      <c r="CK47" s="91"/>
-      <c r="CL47" s="91"/>
-      <c r="CM47" s="91"/>
-      <c r="CN47" s="91"/>
-      <c r="CO47" s="92"/>
-      <c r="CP47" s="93"/>
-      <c r="CQ47" s="90"/>
-      <c r="CR47" s="91"/>
-      <c r="CS47" s="91"/>
-      <c r="CT47" s="91"/>
-      <c r="CU47" s="91"/>
-      <c r="CV47" s="92"/>
-      <c r="CW47" s="93"/>
-      <c r="CX47" s="90"/>
-      <c r="CY47" s="91"/>
-      <c r="CZ47" s="91"/>
-      <c r="DA47" s="91"/>
-      <c r="DB47" s="91"/>
-      <c r="DC47" s="92"/>
-      <c r="DD47" s="93"/>
-      <c r="DE47" s="90"/>
-      <c r="DF47" s="91"/>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="96"/>
@@ -9262,45 +7679,6 @@
       <c r="BQ48" s="91"/>
       <c r="BR48" s="91"/>
       <c r="BS48" s="91"/>
-      <c r="BT48" s="92"/>
-      <c r="BU48" s="93"/>
-      <c r="BV48" s="90"/>
-      <c r="BW48" s="91"/>
-      <c r="BX48" s="91"/>
-      <c r="BY48" s="91"/>
-      <c r="BZ48" s="91"/>
-      <c r="CA48" s="92"/>
-      <c r="CB48" s="93"/>
-      <c r="CC48" s="90"/>
-      <c r="CD48" s="91"/>
-      <c r="CE48" s="91"/>
-      <c r="CF48" s="91"/>
-      <c r="CG48" s="91"/>
-      <c r="CH48" s="92"/>
-      <c r="CI48" s="94"/>
-      <c r="CJ48" s="95"/>
-      <c r="CK48" s="91"/>
-      <c r="CL48" s="91"/>
-      <c r="CM48" s="91"/>
-      <c r="CN48" s="91"/>
-      <c r="CO48" s="92"/>
-      <c r="CP48" s="93"/>
-      <c r="CQ48" s="90"/>
-      <c r="CR48" s="91"/>
-      <c r="CS48" s="91"/>
-      <c r="CT48" s="91"/>
-      <c r="CU48" s="91"/>
-      <c r="CV48" s="92"/>
-      <c r="CW48" s="93"/>
-      <c r="CX48" s="90"/>
-      <c r="CY48" s="91"/>
-      <c r="CZ48" s="91"/>
-      <c r="DA48" s="91"/>
-      <c r="DB48" s="91"/>
-      <c r="DC48" s="92"/>
-      <c r="DD48" s="93"/>
-      <c r="DE48" s="90"/>
-      <c r="DF48" s="91"/>
     </row>
     <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="96"/>
@@ -9374,45 +7752,6 @@
       <c r="BQ49" s="91"/>
       <c r="BR49" s="91"/>
       <c r="BS49" s="91"/>
-      <c r="BT49" s="92"/>
-      <c r="BU49" s="93"/>
-      <c r="BV49" s="90"/>
-      <c r="BW49" s="91"/>
-      <c r="BX49" s="91"/>
-      <c r="BY49" s="91"/>
-      <c r="BZ49" s="91"/>
-      <c r="CA49" s="92"/>
-      <c r="CB49" s="93"/>
-      <c r="CC49" s="90"/>
-      <c r="CD49" s="91"/>
-      <c r="CE49" s="91"/>
-      <c r="CF49" s="91"/>
-      <c r="CG49" s="91"/>
-      <c r="CH49" s="92"/>
-      <c r="CI49" s="94"/>
-      <c r="CJ49" s="95"/>
-      <c r="CK49" s="91"/>
-      <c r="CL49" s="91"/>
-      <c r="CM49" s="91"/>
-      <c r="CN49" s="91"/>
-      <c r="CO49" s="92"/>
-      <c r="CP49" s="93"/>
-      <c r="CQ49" s="90"/>
-      <c r="CR49" s="91"/>
-      <c r="CS49" s="91"/>
-      <c r="CT49" s="91"/>
-      <c r="CU49" s="91"/>
-      <c r="CV49" s="92"/>
-      <c r="CW49" s="93"/>
-      <c r="CX49" s="90"/>
-      <c r="CY49" s="91"/>
-      <c r="CZ49" s="91"/>
-      <c r="DA49" s="91"/>
-      <c r="DB49" s="91"/>
-      <c r="DC49" s="92"/>
-      <c r="DD49" s="93"/>
-      <c r="DE49" s="90"/>
-      <c r="DF49" s="91"/>
     </row>
     <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="96"/>
@@ -9486,45 +7825,6 @@
       <c r="BQ50" s="91"/>
       <c r="BR50" s="91"/>
       <c r="BS50" s="91"/>
-      <c r="BT50" s="92"/>
-      <c r="BU50" s="93"/>
-      <c r="BV50" s="90"/>
-      <c r="BW50" s="91"/>
-      <c r="BX50" s="91"/>
-      <c r="BY50" s="91"/>
-      <c r="BZ50" s="91"/>
-      <c r="CA50" s="92"/>
-      <c r="CB50" s="93"/>
-      <c r="CC50" s="90"/>
-      <c r="CD50" s="91"/>
-      <c r="CE50" s="91"/>
-      <c r="CF50" s="91"/>
-      <c r="CG50" s="91"/>
-      <c r="CH50" s="92"/>
-      <c r="CI50" s="94"/>
-      <c r="CJ50" s="95"/>
-      <c r="CK50" s="91"/>
-      <c r="CL50" s="91"/>
-      <c r="CM50" s="91"/>
-      <c r="CN50" s="91"/>
-      <c r="CO50" s="92"/>
-      <c r="CP50" s="93"/>
-      <c r="CQ50" s="90"/>
-      <c r="CR50" s="91"/>
-      <c r="CS50" s="91"/>
-      <c r="CT50" s="91"/>
-      <c r="CU50" s="91"/>
-      <c r="CV50" s="92"/>
-      <c r="CW50" s="93"/>
-      <c r="CX50" s="90"/>
-      <c r="CY50" s="91"/>
-      <c r="CZ50" s="91"/>
-      <c r="DA50" s="91"/>
-      <c r="DB50" s="91"/>
-      <c r="DC50" s="92"/>
-      <c r="DD50" s="93"/>
-      <c r="DE50" s="90"/>
-      <c r="DF50" s="91"/>
     </row>
     <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="83"/>
@@ -9598,45 +7898,6 @@
       <c r="BQ51" s="91"/>
       <c r="BR51" s="91"/>
       <c r="BS51" s="91"/>
-      <c r="BT51" s="92"/>
-      <c r="BU51" s="93"/>
-      <c r="BV51" s="90"/>
-      <c r="BW51" s="91"/>
-      <c r="BX51" s="91"/>
-      <c r="BY51" s="91"/>
-      <c r="BZ51" s="91"/>
-      <c r="CA51" s="92"/>
-      <c r="CB51" s="93"/>
-      <c r="CC51" s="90"/>
-      <c r="CD51" s="91"/>
-      <c r="CE51" s="91"/>
-      <c r="CF51" s="91"/>
-      <c r="CG51" s="91"/>
-      <c r="CH51" s="92"/>
-      <c r="CI51" s="94"/>
-      <c r="CJ51" s="95"/>
-      <c r="CK51" s="91"/>
-      <c r="CL51" s="91"/>
-      <c r="CM51" s="91"/>
-      <c r="CN51" s="91"/>
-      <c r="CO51" s="92"/>
-      <c r="CP51" s="93"/>
-      <c r="CQ51" s="90"/>
-      <c r="CR51" s="91"/>
-      <c r="CS51" s="91"/>
-      <c r="CT51" s="91"/>
-      <c r="CU51" s="91"/>
-      <c r="CV51" s="92"/>
-      <c r="CW51" s="93"/>
-      <c r="CX51" s="90"/>
-      <c r="CY51" s="91"/>
-      <c r="CZ51" s="91"/>
-      <c r="DA51" s="91"/>
-      <c r="DB51" s="91"/>
-      <c r="DC51" s="92"/>
-      <c r="DD51" s="93"/>
-      <c r="DE51" s="90"/>
-      <c r="DF51" s="91"/>
     </row>
     <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="96"/>
@@ -9710,45 +7971,6 @@
       <c r="BQ52" s="91"/>
       <c r="BR52" s="91"/>
       <c r="BS52" s="91"/>
-      <c r="BT52" s="92"/>
-      <c r="BU52" s="93"/>
-      <c r="BV52" s="90"/>
-      <c r="BW52" s="91"/>
-      <c r="BX52" s="91"/>
-      <c r="BY52" s="91"/>
-      <c r="BZ52" s="91"/>
-      <c r="CA52" s="92"/>
-      <c r="CB52" s="93"/>
-      <c r="CC52" s="90"/>
-      <c r="CD52" s="91"/>
-      <c r="CE52" s="91"/>
-      <c r="CF52" s="91"/>
-      <c r="CG52" s="91"/>
-      <c r="CH52" s="92"/>
-      <c r="CI52" s="94"/>
-      <c r="CJ52" s="95"/>
-      <c r="CK52" s="91"/>
-      <c r="CL52" s="91"/>
-      <c r="CM52" s="91"/>
-      <c r="CN52" s="91"/>
-      <c r="CO52" s="92"/>
-      <c r="CP52" s="93"/>
-      <c r="CQ52" s="90"/>
-      <c r="CR52" s="91"/>
-      <c r="CS52" s="91"/>
-      <c r="CT52" s="91"/>
-      <c r="CU52" s="91"/>
-      <c r="CV52" s="92"/>
-      <c r="CW52" s="93"/>
-      <c r="CX52" s="90"/>
-      <c r="CY52" s="91"/>
-      <c r="CZ52" s="91"/>
-      <c r="DA52" s="91"/>
-      <c r="DB52" s="91"/>
-      <c r="DC52" s="92"/>
-      <c r="DD52" s="93"/>
-      <c r="DE52" s="90"/>
-      <c r="DF52" s="91"/>
     </row>
     <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="96"/>
@@ -9822,45 +8044,6 @@
       <c r="BQ53" s="91"/>
       <c r="BR53" s="91"/>
       <c r="BS53" s="91"/>
-      <c r="BT53" s="92"/>
-      <c r="BU53" s="93"/>
-      <c r="BV53" s="90"/>
-      <c r="BW53" s="91"/>
-      <c r="BX53" s="91"/>
-      <c r="BY53" s="91"/>
-      <c r="BZ53" s="91"/>
-      <c r="CA53" s="92"/>
-      <c r="CB53" s="93"/>
-      <c r="CC53" s="90"/>
-      <c r="CD53" s="91"/>
-      <c r="CE53" s="91"/>
-      <c r="CF53" s="91"/>
-      <c r="CG53" s="91"/>
-      <c r="CH53" s="92"/>
-      <c r="CI53" s="94"/>
-      <c r="CJ53" s="95"/>
-      <c r="CK53" s="91"/>
-      <c r="CL53" s="91"/>
-      <c r="CM53" s="91"/>
-      <c r="CN53" s="91"/>
-      <c r="CO53" s="92"/>
-      <c r="CP53" s="93"/>
-      <c r="CQ53" s="90"/>
-      <c r="CR53" s="91"/>
-      <c r="CS53" s="91"/>
-      <c r="CT53" s="91"/>
-      <c r="CU53" s="91"/>
-      <c r="CV53" s="92"/>
-      <c r="CW53" s="93"/>
-      <c r="CX53" s="90"/>
-      <c r="CY53" s="91"/>
-      <c r="CZ53" s="91"/>
-      <c r="DA53" s="91"/>
-      <c r="DB53" s="91"/>
-      <c r="DC53" s="92"/>
-      <c r="DD53" s="93"/>
-      <c r="DE53" s="90"/>
-      <c r="DF53" s="91"/>
     </row>
     <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="96"/>
@@ -9934,45 +8117,6 @@
       <c r="BQ54" s="91"/>
       <c r="BR54" s="91"/>
       <c r="BS54" s="91"/>
-      <c r="BT54" s="92"/>
-      <c r="BU54" s="93"/>
-      <c r="BV54" s="90"/>
-      <c r="BW54" s="91"/>
-      <c r="BX54" s="91"/>
-      <c r="BY54" s="91"/>
-      <c r="BZ54" s="91"/>
-      <c r="CA54" s="92"/>
-      <c r="CB54" s="93"/>
-      <c r="CC54" s="90"/>
-      <c r="CD54" s="91"/>
-      <c r="CE54" s="91"/>
-      <c r="CF54" s="91"/>
-      <c r="CG54" s="91"/>
-      <c r="CH54" s="92"/>
-      <c r="CI54" s="94"/>
-      <c r="CJ54" s="95"/>
-      <c r="CK54" s="91"/>
-      <c r="CL54" s="91"/>
-      <c r="CM54" s="91"/>
-      <c r="CN54" s="91"/>
-      <c r="CO54" s="92"/>
-      <c r="CP54" s="93"/>
-      <c r="CQ54" s="90"/>
-      <c r="CR54" s="91"/>
-      <c r="CS54" s="91"/>
-      <c r="CT54" s="91"/>
-      <c r="CU54" s="91"/>
-      <c r="CV54" s="92"/>
-      <c r="CW54" s="93"/>
-      <c r="CX54" s="90"/>
-      <c r="CY54" s="91"/>
-      <c r="CZ54" s="91"/>
-      <c r="DA54" s="91"/>
-      <c r="DB54" s="91"/>
-      <c r="DC54" s="92"/>
-      <c r="DD54" s="93"/>
-      <c r="DE54" s="90"/>
-      <c r="DF54" s="91"/>
     </row>
     <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="96"/>
@@ -10046,45 +8190,6 @@
       <c r="BQ55" s="91"/>
       <c r="BR55" s="91"/>
       <c r="BS55" s="91"/>
-      <c r="BT55" s="92"/>
-      <c r="BU55" s="93"/>
-      <c r="BV55" s="90"/>
-      <c r="BW55" s="91"/>
-      <c r="BX55" s="91"/>
-      <c r="BY55" s="91"/>
-      <c r="BZ55" s="91"/>
-      <c r="CA55" s="92"/>
-      <c r="CB55" s="93"/>
-      <c r="CC55" s="90"/>
-      <c r="CD55" s="91"/>
-      <c r="CE55" s="91"/>
-      <c r="CF55" s="91"/>
-      <c r="CG55" s="91"/>
-      <c r="CH55" s="92"/>
-      <c r="CI55" s="94"/>
-      <c r="CJ55" s="95"/>
-      <c r="CK55" s="91"/>
-      <c r="CL55" s="91"/>
-      <c r="CM55" s="91"/>
-      <c r="CN55" s="91"/>
-      <c r="CO55" s="92"/>
-      <c r="CP55" s="93"/>
-      <c r="CQ55" s="90"/>
-      <c r="CR55" s="91"/>
-      <c r="CS55" s="91"/>
-      <c r="CT55" s="91"/>
-      <c r="CU55" s="91"/>
-      <c r="CV55" s="92"/>
-      <c r="CW55" s="93"/>
-      <c r="CX55" s="90"/>
-      <c r="CY55" s="91"/>
-      <c r="CZ55" s="91"/>
-      <c r="DA55" s="91"/>
-      <c r="DB55" s="91"/>
-      <c r="DC55" s="92"/>
-      <c r="DD55" s="93"/>
-      <c r="DE55" s="90"/>
-      <c r="DF55" s="91"/>
     </row>
     <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="83"/>
@@ -10158,45 +8263,6 @@
       <c r="BQ56" s="91"/>
       <c r="BR56" s="91"/>
       <c r="BS56" s="91"/>
-      <c r="BT56" s="92"/>
-      <c r="BU56" s="93"/>
-      <c r="BV56" s="90"/>
-      <c r="BW56" s="91"/>
-      <c r="BX56" s="91"/>
-      <c r="BY56" s="91"/>
-      <c r="BZ56" s="91"/>
-      <c r="CA56" s="92"/>
-      <c r="CB56" s="93"/>
-      <c r="CC56" s="90"/>
-      <c r="CD56" s="91"/>
-      <c r="CE56" s="91"/>
-      <c r="CF56" s="91"/>
-      <c r="CG56" s="91"/>
-      <c r="CH56" s="92"/>
-      <c r="CI56" s="94"/>
-      <c r="CJ56" s="95"/>
-      <c r="CK56" s="91"/>
-      <c r="CL56" s="91"/>
-      <c r="CM56" s="91"/>
-      <c r="CN56" s="91"/>
-      <c r="CO56" s="92"/>
-      <c r="CP56" s="93"/>
-      <c r="CQ56" s="90"/>
-      <c r="CR56" s="91"/>
-      <c r="CS56" s="91"/>
-      <c r="CT56" s="91"/>
-      <c r="CU56" s="91"/>
-      <c r="CV56" s="92"/>
-      <c r="CW56" s="93"/>
-      <c r="CX56" s="90"/>
-      <c r="CY56" s="91"/>
-      <c r="CZ56" s="91"/>
-      <c r="DA56" s="91"/>
-      <c r="DB56" s="91"/>
-      <c r="DC56" s="92"/>
-      <c r="DD56" s="93"/>
-      <c r="DE56" s="90"/>
-      <c r="DF56" s="91"/>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="96"/>
@@ -10270,45 +8336,6 @@
       <c r="BQ57" s="91"/>
       <c r="BR57" s="91"/>
       <c r="BS57" s="91"/>
-      <c r="BT57" s="92"/>
-      <c r="BU57" s="93"/>
-      <c r="BV57" s="90"/>
-      <c r="BW57" s="91"/>
-      <c r="BX57" s="91"/>
-      <c r="BY57" s="91"/>
-      <c r="BZ57" s="91"/>
-      <c r="CA57" s="92"/>
-      <c r="CB57" s="93"/>
-      <c r="CC57" s="90"/>
-      <c r="CD57" s="91"/>
-      <c r="CE57" s="91"/>
-      <c r="CF57" s="91"/>
-      <c r="CG57" s="91"/>
-      <c r="CH57" s="92"/>
-      <c r="CI57" s="94"/>
-      <c r="CJ57" s="95"/>
-      <c r="CK57" s="91"/>
-      <c r="CL57" s="91"/>
-      <c r="CM57" s="91"/>
-      <c r="CN57" s="91"/>
-      <c r="CO57" s="92"/>
-      <c r="CP57" s="93"/>
-      <c r="CQ57" s="90"/>
-      <c r="CR57" s="91"/>
-      <c r="CS57" s="91"/>
-      <c r="CT57" s="91"/>
-      <c r="CU57" s="91"/>
-      <c r="CV57" s="92"/>
-      <c r="CW57" s="93"/>
-      <c r="CX57" s="90"/>
-      <c r="CY57" s="91"/>
-      <c r="CZ57" s="91"/>
-      <c r="DA57" s="91"/>
-      <c r="DB57" s="91"/>
-      <c r="DC57" s="92"/>
-      <c r="DD57" s="93"/>
-      <c r="DE57" s="90"/>
-      <c r="DF57" s="91"/>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="96"/>
@@ -10382,45 +8409,6 @@
       <c r="BQ58" s="91"/>
       <c r="BR58" s="91"/>
       <c r="BS58" s="91"/>
-      <c r="BT58" s="92"/>
-      <c r="BU58" s="93"/>
-      <c r="BV58" s="90"/>
-      <c r="BW58" s="91"/>
-      <c r="BX58" s="91"/>
-      <c r="BY58" s="91"/>
-      <c r="BZ58" s="91"/>
-      <c r="CA58" s="92"/>
-      <c r="CB58" s="93"/>
-      <c r="CC58" s="90"/>
-      <c r="CD58" s="91"/>
-      <c r="CE58" s="91"/>
-      <c r="CF58" s="91"/>
-      <c r="CG58" s="91"/>
-      <c r="CH58" s="92"/>
-      <c r="CI58" s="94"/>
-      <c r="CJ58" s="95"/>
-      <c r="CK58" s="91"/>
-      <c r="CL58" s="91"/>
-      <c r="CM58" s="91"/>
-      <c r="CN58" s="91"/>
-      <c r="CO58" s="92"/>
-      <c r="CP58" s="93"/>
-      <c r="CQ58" s="90"/>
-      <c r="CR58" s="91"/>
-      <c r="CS58" s="91"/>
-      <c r="CT58" s="91"/>
-      <c r="CU58" s="91"/>
-      <c r="CV58" s="92"/>
-      <c r="CW58" s="93"/>
-      <c r="CX58" s="90"/>
-      <c r="CY58" s="91"/>
-      <c r="CZ58" s="91"/>
-      <c r="DA58" s="91"/>
-      <c r="DB58" s="91"/>
-      <c r="DC58" s="92"/>
-      <c r="DD58" s="93"/>
-      <c r="DE58" s="90"/>
-      <c r="DF58" s="91"/>
     </row>
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="96"/>
@@ -10494,45 +8482,6 @@
       <c r="BQ59" s="91"/>
       <c r="BR59" s="91"/>
       <c r="BS59" s="91"/>
-      <c r="BT59" s="92"/>
-      <c r="BU59" s="93"/>
-      <c r="BV59" s="90"/>
-      <c r="BW59" s="91"/>
-      <c r="BX59" s="91"/>
-      <c r="BY59" s="91"/>
-      <c r="BZ59" s="91"/>
-      <c r="CA59" s="92"/>
-      <c r="CB59" s="93"/>
-      <c r="CC59" s="90"/>
-      <c r="CD59" s="91"/>
-      <c r="CE59" s="91"/>
-      <c r="CF59" s="91"/>
-      <c r="CG59" s="91"/>
-      <c r="CH59" s="92"/>
-      <c r="CI59" s="94"/>
-      <c r="CJ59" s="95"/>
-      <c r="CK59" s="91"/>
-      <c r="CL59" s="91"/>
-      <c r="CM59" s="91"/>
-      <c r="CN59" s="91"/>
-      <c r="CO59" s="92"/>
-      <c r="CP59" s="93"/>
-      <c r="CQ59" s="90"/>
-      <c r="CR59" s="91"/>
-      <c r="CS59" s="91"/>
-      <c r="CT59" s="91"/>
-      <c r="CU59" s="91"/>
-      <c r="CV59" s="92"/>
-      <c r="CW59" s="93"/>
-      <c r="CX59" s="90"/>
-      <c r="CY59" s="91"/>
-      <c r="CZ59" s="91"/>
-      <c r="DA59" s="91"/>
-      <c r="DB59" s="91"/>
-      <c r="DC59" s="92"/>
-      <c r="DD59" s="93"/>
-      <c r="DE59" s="90"/>
-      <c r="DF59" s="91"/>
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="96"/>
@@ -10606,45 +8555,6 @@
       <c r="BQ60" s="91"/>
       <c r="BR60" s="91"/>
       <c r="BS60" s="91"/>
-      <c r="BT60" s="92"/>
-      <c r="BU60" s="93"/>
-      <c r="BV60" s="90"/>
-      <c r="BW60" s="91"/>
-      <c r="BX60" s="91"/>
-      <c r="BY60" s="91"/>
-      <c r="BZ60" s="91"/>
-      <c r="CA60" s="92"/>
-      <c r="CB60" s="93"/>
-      <c r="CC60" s="90"/>
-      <c r="CD60" s="91"/>
-      <c r="CE60" s="91"/>
-      <c r="CF60" s="91"/>
-      <c r="CG60" s="91"/>
-      <c r="CH60" s="92"/>
-      <c r="CI60" s="94"/>
-      <c r="CJ60" s="95"/>
-      <c r="CK60" s="91"/>
-      <c r="CL60" s="91"/>
-      <c r="CM60" s="91"/>
-      <c r="CN60" s="91"/>
-      <c r="CO60" s="92"/>
-      <c r="CP60" s="93"/>
-      <c r="CQ60" s="90"/>
-      <c r="CR60" s="91"/>
-      <c r="CS60" s="91"/>
-      <c r="CT60" s="91"/>
-      <c r="CU60" s="91"/>
-      <c r="CV60" s="92"/>
-      <c r="CW60" s="93"/>
-      <c r="CX60" s="90"/>
-      <c r="CY60" s="91"/>
-      <c r="CZ60" s="91"/>
-      <c r="DA60" s="91"/>
-      <c r="DB60" s="91"/>
-      <c r="DC60" s="92"/>
-      <c r="DD60" s="93"/>
-      <c r="DE60" s="90"/>
-      <c r="DF60" s="91"/>
     </row>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="83"/>
@@ -10718,45 +8628,6 @@
       <c r="BQ61" s="91"/>
       <c r="BR61" s="91"/>
       <c r="BS61" s="91"/>
-      <c r="BT61" s="92"/>
-      <c r="BU61" s="93"/>
-      <c r="BV61" s="90"/>
-      <c r="BW61" s="91"/>
-      <c r="BX61" s="91"/>
-      <c r="BY61" s="91"/>
-      <c r="BZ61" s="91"/>
-      <c r="CA61" s="92"/>
-      <c r="CB61" s="93"/>
-      <c r="CC61" s="90"/>
-      <c r="CD61" s="91"/>
-      <c r="CE61" s="91"/>
-      <c r="CF61" s="91"/>
-      <c r="CG61" s="91"/>
-      <c r="CH61" s="92"/>
-      <c r="CI61" s="94"/>
-      <c r="CJ61" s="95"/>
-      <c r="CK61" s="91"/>
-      <c r="CL61" s="91"/>
-      <c r="CM61" s="91"/>
-      <c r="CN61" s="91"/>
-      <c r="CO61" s="92"/>
-      <c r="CP61" s="93"/>
-      <c r="CQ61" s="90"/>
-      <c r="CR61" s="91"/>
-      <c r="CS61" s="91"/>
-      <c r="CT61" s="91"/>
-      <c r="CU61" s="91"/>
-      <c r="CV61" s="92"/>
-      <c r="CW61" s="93"/>
-      <c r="CX61" s="90"/>
-      <c r="CY61" s="91"/>
-      <c r="CZ61" s="91"/>
-      <c r="DA61" s="91"/>
-      <c r="DB61" s="91"/>
-      <c r="DC61" s="92"/>
-      <c r="DD61" s="93"/>
-      <c r="DE61" s="90"/>
-      <c r="DF61" s="91"/>
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="96"/>
@@ -10830,45 +8701,6 @@
       <c r="BQ62" s="91"/>
       <c r="BR62" s="91"/>
       <c r="BS62" s="91"/>
-      <c r="BT62" s="92"/>
-      <c r="BU62" s="93"/>
-      <c r="BV62" s="90"/>
-      <c r="BW62" s="91"/>
-      <c r="BX62" s="91"/>
-      <c r="BY62" s="91"/>
-      <c r="BZ62" s="91"/>
-      <c r="CA62" s="92"/>
-      <c r="CB62" s="93"/>
-      <c r="CC62" s="90"/>
-      <c r="CD62" s="91"/>
-      <c r="CE62" s="91"/>
-      <c r="CF62" s="91"/>
-      <c r="CG62" s="91"/>
-      <c r="CH62" s="92"/>
-      <c r="CI62" s="94"/>
-      <c r="CJ62" s="95"/>
-      <c r="CK62" s="91"/>
-      <c r="CL62" s="91"/>
-      <c r="CM62" s="91"/>
-      <c r="CN62" s="91"/>
-      <c r="CO62" s="92"/>
-      <c r="CP62" s="93"/>
-      <c r="CQ62" s="90"/>
-      <c r="CR62" s="91"/>
-      <c r="CS62" s="91"/>
-      <c r="CT62" s="91"/>
-      <c r="CU62" s="91"/>
-      <c r="CV62" s="92"/>
-      <c r="CW62" s="93"/>
-      <c r="CX62" s="90"/>
-      <c r="CY62" s="91"/>
-      <c r="CZ62" s="91"/>
-      <c r="DA62" s="91"/>
-      <c r="DB62" s="91"/>
-      <c r="DC62" s="92"/>
-      <c r="DD62" s="93"/>
-      <c r="DE62" s="90"/>
-      <c r="DF62" s="91"/>
     </row>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="96"/>
@@ -10942,45 +8774,6 @@
       <c r="BQ63" s="91"/>
       <c r="BR63" s="91"/>
       <c r="BS63" s="91"/>
-      <c r="BT63" s="92"/>
-      <c r="BU63" s="93"/>
-      <c r="BV63" s="90"/>
-      <c r="BW63" s="91"/>
-      <c r="BX63" s="91"/>
-      <c r="BY63" s="91"/>
-      <c r="BZ63" s="91"/>
-      <c r="CA63" s="92"/>
-      <c r="CB63" s="93"/>
-      <c r="CC63" s="90"/>
-      <c r="CD63" s="91"/>
-      <c r="CE63" s="91"/>
-      <c r="CF63" s="91"/>
-      <c r="CG63" s="91"/>
-      <c r="CH63" s="92"/>
-      <c r="CI63" s="94"/>
-      <c r="CJ63" s="95"/>
-      <c r="CK63" s="91"/>
-      <c r="CL63" s="91"/>
-      <c r="CM63" s="91"/>
-      <c r="CN63" s="91"/>
-      <c r="CO63" s="92"/>
-      <c r="CP63" s="93"/>
-      <c r="CQ63" s="90"/>
-      <c r="CR63" s="91"/>
-      <c r="CS63" s="91"/>
-      <c r="CT63" s="91"/>
-      <c r="CU63" s="91"/>
-      <c r="CV63" s="92"/>
-      <c r="CW63" s="93"/>
-      <c r="CX63" s="90"/>
-      <c r="CY63" s="91"/>
-      <c r="CZ63" s="91"/>
-      <c r="DA63" s="91"/>
-      <c r="DB63" s="91"/>
-      <c r="DC63" s="92"/>
-      <c r="DD63" s="93"/>
-      <c r="DE63" s="90"/>
-      <c r="DF63" s="91"/>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="102"/>
@@ -11054,45 +8847,6 @@
       <c r="BQ64" s="110"/>
       <c r="BR64" s="110"/>
       <c r="BS64" s="110"/>
-      <c r="BT64" s="111"/>
-      <c r="BU64" s="112"/>
-      <c r="BV64" s="109"/>
-      <c r="BW64" s="110"/>
-      <c r="BX64" s="110"/>
-      <c r="BY64" s="110"/>
-      <c r="BZ64" s="110"/>
-      <c r="CA64" s="111"/>
-      <c r="CB64" s="112"/>
-      <c r="CC64" s="109"/>
-      <c r="CD64" s="110"/>
-      <c r="CE64" s="110"/>
-      <c r="CF64" s="110"/>
-      <c r="CG64" s="110"/>
-      <c r="CH64" s="111"/>
-      <c r="CI64" s="113"/>
-      <c r="CJ64" s="114"/>
-      <c r="CK64" s="110"/>
-      <c r="CL64" s="110"/>
-      <c r="CM64" s="110"/>
-      <c r="CN64" s="110"/>
-      <c r="CO64" s="111"/>
-      <c r="CP64" s="112"/>
-      <c r="CQ64" s="109"/>
-      <c r="CR64" s="110"/>
-      <c r="CS64" s="110"/>
-      <c r="CT64" s="110"/>
-      <c r="CU64" s="110"/>
-      <c r="CV64" s="111"/>
-      <c r="CW64" s="112"/>
-      <c r="CX64" s="109"/>
-      <c r="CY64" s="110"/>
-      <c r="CZ64" s="110"/>
-      <c r="DA64" s="110"/>
-      <c r="DB64" s="110"/>
-      <c r="DC64" s="111"/>
-      <c r="DD64" s="112"/>
-      <c r="DE64" s="109"/>
-      <c r="DF64" s="110"/>
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="83"/>
@@ -11166,45 +8920,6 @@
       <c r="BQ65" s="91"/>
       <c r="BR65" s="91"/>
       <c r="BS65" s="91"/>
-      <c r="BT65" s="92"/>
-      <c r="BU65" s="93"/>
-      <c r="BV65" s="90"/>
-      <c r="BW65" s="91"/>
-      <c r="BX65" s="91"/>
-      <c r="BY65" s="91"/>
-      <c r="BZ65" s="91"/>
-      <c r="CA65" s="92"/>
-      <c r="CB65" s="93"/>
-      <c r="CC65" s="90"/>
-      <c r="CD65" s="91"/>
-      <c r="CE65" s="91"/>
-      <c r="CF65" s="91"/>
-      <c r="CG65" s="91"/>
-      <c r="CH65" s="92"/>
-      <c r="CI65" s="94"/>
-      <c r="CJ65" s="95"/>
-      <c r="CK65" s="91"/>
-      <c r="CL65" s="91"/>
-      <c r="CM65" s="91"/>
-      <c r="CN65" s="91"/>
-      <c r="CO65" s="92"/>
-      <c r="CP65" s="93"/>
-      <c r="CQ65" s="90"/>
-      <c r="CR65" s="91"/>
-      <c r="CS65" s="91"/>
-      <c r="CT65" s="91"/>
-      <c r="CU65" s="91"/>
-      <c r="CV65" s="92"/>
-      <c r="CW65" s="93"/>
-      <c r="CX65" s="90"/>
-      <c r="CY65" s="91"/>
-      <c r="CZ65" s="91"/>
-      <c r="DA65" s="91"/>
-      <c r="DB65" s="91"/>
-      <c r="DC65" s="92"/>
-      <c r="DD65" s="93"/>
-      <c r="DE65" s="90"/>
-      <c r="DF65" s="91"/>
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="83"/>
@@ -11278,45 +8993,6 @@
       <c r="BQ66" s="91"/>
       <c r="BR66" s="91"/>
       <c r="BS66" s="91"/>
-      <c r="BT66" s="92"/>
-      <c r="BU66" s="93"/>
-      <c r="BV66" s="90"/>
-      <c r="BW66" s="91"/>
-      <c r="BX66" s="91"/>
-      <c r="BY66" s="91"/>
-      <c r="BZ66" s="91"/>
-      <c r="CA66" s="92"/>
-      <c r="CB66" s="93"/>
-      <c r="CC66" s="90"/>
-      <c r="CD66" s="91"/>
-      <c r="CE66" s="91"/>
-      <c r="CF66" s="91"/>
-      <c r="CG66" s="91"/>
-      <c r="CH66" s="92"/>
-      <c r="CI66" s="94"/>
-      <c r="CJ66" s="95"/>
-      <c r="CK66" s="91"/>
-      <c r="CL66" s="91"/>
-      <c r="CM66" s="91"/>
-      <c r="CN66" s="91"/>
-      <c r="CO66" s="92"/>
-      <c r="CP66" s="93"/>
-      <c r="CQ66" s="90"/>
-      <c r="CR66" s="91"/>
-      <c r="CS66" s="91"/>
-      <c r="CT66" s="91"/>
-      <c r="CU66" s="91"/>
-      <c r="CV66" s="92"/>
-      <c r="CW66" s="93"/>
-      <c r="CX66" s="90"/>
-      <c r="CY66" s="91"/>
-      <c r="CZ66" s="91"/>
-      <c r="DA66" s="91"/>
-      <c r="DB66" s="91"/>
-      <c r="DC66" s="92"/>
-      <c r="DD66" s="93"/>
-      <c r="DE66" s="90"/>
-      <c r="DF66" s="91"/>
     </row>
     <row r="67" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="117"/>
@@ -11390,45 +9066,6 @@
       <c r="BQ67" s="91"/>
       <c r="BR67" s="91"/>
       <c r="BS67" s="91"/>
-      <c r="BT67" s="92"/>
-      <c r="BU67" s="93"/>
-      <c r="BV67" s="90"/>
-      <c r="BW67" s="91"/>
-      <c r="BX67" s="91"/>
-      <c r="BY67" s="91"/>
-      <c r="BZ67" s="91"/>
-      <c r="CA67" s="92"/>
-      <c r="CB67" s="93"/>
-      <c r="CC67" s="90"/>
-      <c r="CD67" s="91"/>
-      <c r="CE67" s="91"/>
-      <c r="CF67" s="91"/>
-      <c r="CG67" s="91"/>
-      <c r="CH67" s="92"/>
-      <c r="CI67" s="94"/>
-      <c r="CJ67" s="95"/>
-      <c r="CK67" s="91"/>
-      <c r="CL67" s="91"/>
-      <c r="CM67" s="91"/>
-      <c r="CN67" s="91"/>
-      <c r="CO67" s="92"/>
-      <c r="CP67" s="93"/>
-      <c r="CQ67" s="90"/>
-      <c r="CR67" s="91"/>
-      <c r="CS67" s="91"/>
-      <c r="CT67" s="91"/>
-      <c r="CU67" s="91"/>
-      <c r="CV67" s="92"/>
-      <c r="CW67" s="93"/>
-      <c r="CX67" s="90"/>
-      <c r="CY67" s="91"/>
-      <c r="CZ67" s="91"/>
-      <c r="DA67" s="91"/>
-      <c r="DB67" s="91"/>
-      <c r="DC67" s="92"/>
-      <c r="DD67" s="93"/>
-      <c r="DE67" s="90"/>
-      <c r="DF67" s="91"/>
     </row>
     <row r="68" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="96"/>
@@ -11502,45 +9139,6 @@
       <c r="BQ68" s="91"/>
       <c r="BR68" s="91"/>
       <c r="BS68" s="91"/>
-      <c r="BT68" s="92"/>
-      <c r="BU68" s="93"/>
-      <c r="BV68" s="90"/>
-      <c r="BW68" s="91"/>
-      <c r="BX68" s="91"/>
-      <c r="BY68" s="91"/>
-      <c r="BZ68" s="91"/>
-      <c r="CA68" s="92"/>
-      <c r="CB68" s="93"/>
-      <c r="CC68" s="90"/>
-      <c r="CD68" s="91"/>
-      <c r="CE68" s="91"/>
-      <c r="CF68" s="91"/>
-      <c r="CG68" s="91"/>
-      <c r="CH68" s="92"/>
-      <c r="CI68" s="94"/>
-      <c r="CJ68" s="95"/>
-      <c r="CK68" s="91"/>
-      <c r="CL68" s="91"/>
-      <c r="CM68" s="91"/>
-      <c r="CN68" s="91"/>
-      <c r="CO68" s="92"/>
-      <c r="CP68" s="93"/>
-      <c r="CQ68" s="90"/>
-      <c r="CR68" s="91"/>
-      <c r="CS68" s="91"/>
-      <c r="CT68" s="91"/>
-      <c r="CU68" s="91"/>
-      <c r="CV68" s="92"/>
-      <c r="CW68" s="93"/>
-      <c r="CX68" s="90"/>
-      <c r="CY68" s="91"/>
-      <c r="CZ68" s="91"/>
-      <c r="DA68" s="91"/>
-      <c r="DB68" s="91"/>
-      <c r="DC68" s="92"/>
-      <c r="DD68" s="93"/>
-      <c r="DE68" s="90"/>
-      <c r="DF68" s="91"/>
     </row>
     <row r="69" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="96"/>
@@ -11614,45 +9212,6 @@
       <c r="BQ69" s="91"/>
       <c r="BR69" s="91"/>
       <c r="BS69" s="91"/>
-      <c r="BT69" s="92"/>
-      <c r="BU69" s="93"/>
-      <c r="BV69" s="90"/>
-      <c r="BW69" s="91"/>
-      <c r="BX69" s="91"/>
-      <c r="BY69" s="91"/>
-      <c r="BZ69" s="91"/>
-      <c r="CA69" s="92"/>
-      <c r="CB69" s="93"/>
-      <c r="CC69" s="90"/>
-      <c r="CD69" s="91"/>
-      <c r="CE69" s="91"/>
-      <c r="CF69" s="91"/>
-      <c r="CG69" s="91"/>
-      <c r="CH69" s="92"/>
-      <c r="CI69" s="94"/>
-      <c r="CJ69" s="95"/>
-      <c r="CK69" s="91"/>
-      <c r="CL69" s="91"/>
-      <c r="CM69" s="91"/>
-      <c r="CN69" s="91"/>
-      <c r="CO69" s="92"/>
-      <c r="CP69" s="93"/>
-      <c r="CQ69" s="90"/>
-      <c r="CR69" s="91"/>
-      <c r="CS69" s="91"/>
-      <c r="CT69" s="91"/>
-      <c r="CU69" s="91"/>
-      <c r="CV69" s="92"/>
-      <c r="CW69" s="93"/>
-      <c r="CX69" s="90"/>
-      <c r="CY69" s="91"/>
-      <c r="CZ69" s="91"/>
-      <c r="DA69" s="91"/>
-      <c r="DB69" s="91"/>
-      <c r="DC69" s="92"/>
-      <c r="DD69" s="93"/>
-      <c r="DE69" s="90"/>
-      <c r="DF69" s="91"/>
     </row>
     <row r="70" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="96"/>
@@ -11726,45 +9285,6 @@
       <c r="BQ70" s="91"/>
       <c r="BR70" s="91"/>
       <c r="BS70" s="91"/>
-      <c r="BT70" s="92"/>
-      <c r="BU70" s="93"/>
-      <c r="BV70" s="90"/>
-      <c r="BW70" s="91"/>
-      <c r="BX70" s="91"/>
-      <c r="BY70" s="91"/>
-      <c r="BZ70" s="91"/>
-      <c r="CA70" s="92"/>
-      <c r="CB70" s="93"/>
-      <c r="CC70" s="90"/>
-      <c r="CD70" s="91"/>
-      <c r="CE70" s="91"/>
-      <c r="CF70" s="91"/>
-      <c r="CG70" s="91"/>
-      <c r="CH70" s="92"/>
-      <c r="CI70" s="94"/>
-      <c r="CJ70" s="95"/>
-      <c r="CK70" s="91"/>
-      <c r="CL70" s="91"/>
-      <c r="CM70" s="91"/>
-      <c r="CN70" s="91"/>
-      <c r="CO70" s="92"/>
-      <c r="CP70" s="93"/>
-      <c r="CQ70" s="90"/>
-      <c r="CR70" s="91"/>
-      <c r="CS70" s="91"/>
-      <c r="CT70" s="91"/>
-      <c r="CU70" s="91"/>
-      <c r="CV70" s="92"/>
-      <c r="CW70" s="93"/>
-      <c r="CX70" s="90"/>
-      <c r="CY70" s="91"/>
-      <c r="CZ70" s="91"/>
-      <c r="DA70" s="91"/>
-      <c r="DB70" s="91"/>
-      <c r="DC70" s="92"/>
-      <c r="DD70" s="93"/>
-      <c r="DE70" s="90"/>
-      <c r="DF70" s="91"/>
     </row>
     <row r="71" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="96"/>
@@ -11838,45 +9358,6 @@
       <c r="BQ71" s="91"/>
       <c r="BR71" s="91"/>
       <c r="BS71" s="91"/>
-      <c r="BT71" s="92"/>
-      <c r="BU71" s="93"/>
-      <c r="BV71" s="90"/>
-      <c r="BW71" s="91"/>
-      <c r="BX71" s="91"/>
-      <c r="BY71" s="91"/>
-      <c r="BZ71" s="91"/>
-      <c r="CA71" s="92"/>
-      <c r="CB71" s="93"/>
-      <c r="CC71" s="90"/>
-      <c r="CD71" s="91"/>
-      <c r="CE71" s="91"/>
-      <c r="CF71" s="91"/>
-      <c r="CG71" s="91"/>
-      <c r="CH71" s="92"/>
-      <c r="CI71" s="94"/>
-      <c r="CJ71" s="95"/>
-      <c r="CK71" s="91"/>
-      <c r="CL71" s="91"/>
-      <c r="CM71" s="91"/>
-      <c r="CN71" s="91"/>
-      <c r="CO71" s="92"/>
-      <c r="CP71" s="93"/>
-      <c r="CQ71" s="90"/>
-      <c r="CR71" s="91"/>
-      <c r="CS71" s="91"/>
-      <c r="CT71" s="91"/>
-      <c r="CU71" s="91"/>
-      <c r="CV71" s="92"/>
-      <c r="CW71" s="93"/>
-      <c r="CX71" s="90"/>
-      <c r="CY71" s="91"/>
-      <c r="CZ71" s="91"/>
-      <c r="DA71" s="91"/>
-      <c r="DB71" s="91"/>
-      <c r="DC71" s="92"/>
-      <c r="DD71" s="93"/>
-      <c r="DE71" s="90"/>
-      <c r="DF71" s="91"/>
     </row>
     <row r="72" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="117"/>
@@ -11950,45 +9431,6 @@
       <c r="BQ72" s="91"/>
       <c r="BR72" s="91"/>
       <c r="BS72" s="91"/>
-      <c r="BT72" s="92"/>
-      <c r="BU72" s="93"/>
-      <c r="BV72" s="90"/>
-      <c r="BW72" s="91"/>
-      <c r="BX72" s="91"/>
-      <c r="BY72" s="91"/>
-      <c r="BZ72" s="91"/>
-      <c r="CA72" s="92"/>
-      <c r="CB72" s="93"/>
-      <c r="CC72" s="90"/>
-      <c r="CD72" s="91"/>
-      <c r="CE72" s="91"/>
-      <c r="CF72" s="91"/>
-      <c r="CG72" s="91"/>
-      <c r="CH72" s="92"/>
-      <c r="CI72" s="94"/>
-      <c r="CJ72" s="95"/>
-      <c r="CK72" s="91"/>
-      <c r="CL72" s="91"/>
-      <c r="CM72" s="91"/>
-      <c r="CN72" s="91"/>
-      <c r="CO72" s="92"/>
-      <c r="CP72" s="93"/>
-      <c r="CQ72" s="90"/>
-      <c r="CR72" s="91"/>
-      <c r="CS72" s="91"/>
-      <c r="CT72" s="91"/>
-      <c r="CU72" s="91"/>
-      <c r="CV72" s="92"/>
-      <c r="CW72" s="93"/>
-      <c r="CX72" s="90"/>
-      <c r="CY72" s="91"/>
-      <c r="CZ72" s="91"/>
-      <c r="DA72" s="91"/>
-      <c r="DB72" s="91"/>
-      <c r="DC72" s="92"/>
-      <c r="DD72" s="93"/>
-      <c r="DE72" s="90"/>
-      <c r="DF72" s="91"/>
     </row>
     <row r="73" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="96"/>
@@ -12062,45 +9504,6 @@
       <c r="BQ73" s="91"/>
       <c r="BR73" s="91"/>
       <c r="BS73" s="91"/>
-      <c r="BT73" s="92"/>
-      <c r="BU73" s="93"/>
-      <c r="BV73" s="90"/>
-      <c r="BW73" s="91"/>
-      <c r="BX73" s="91"/>
-      <c r="BY73" s="91"/>
-      <c r="BZ73" s="91"/>
-      <c r="CA73" s="92"/>
-      <c r="CB73" s="93"/>
-      <c r="CC73" s="90"/>
-      <c r="CD73" s="91"/>
-      <c r="CE73" s="91"/>
-      <c r="CF73" s="91"/>
-      <c r="CG73" s="91"/>
-      <c r="CH73" s="92"/>
-      <c r="CI73" s="94"/>
-      <c r="CJ73" s="95"/>
-      <c r="CK73" s="91"/>
-      <c r="CL73" s="91"/>
-      <c r="CM73" s="91"/>
-      <c r="CN73" s="91"/>
-      <c r="CO73" s="92"/>
-      <c r="CP73" s="93"/>
-      <c r="CQ73" s="90"/>
-      <c r="CR73" s="91"/>
-      <c r="CS73" s="91"/>
-      <c r="CT73" s="91"/>
-      <c r="CU73" s="91"/>
-      <c r="CV73" s="92"/>
-      <c r="CW73" s="93"/>
-      <c r="CX73" s="90"/>
-      <c r="CY73" s="91"/>
-      <c r="CZ73" s="91"/>
-      <c r="DA73" s="91"/>
-      <c r="DB73" s="91"/>
-      <c r="DC73" s="92"/>
-      <c r="DD73" s="93"/>
-      <c r="DE73" s="90"/>
-      <c r="DF73" s="91"/>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="96"/>
@@ -12174,45 +9577,6 @@
       <c r="BQ74" s="91"/>
       <c r="BR74" s="91"/>
       <c r="BS74" s="91"/>
-      <c r="BT74" s="92"/>
-      <c r="BU74" s="93"/>
-      <c r="BV74" s="90"/>
-      <c r="BW74" s="91"/>
-      <c r="BX74" s="91"/>
-      <c r="BY74" s="91"/>
-      <c r="BZ74" s="91"/>
-      <c r="CA74" s="92"/>
-      <c r="CB74" s="93"/>
-      <c r="CC74" s="90"/>
-      <c r="CD74" s="91"/>
-      <c r="CE74" s="91"/>
-      <c r="CF74" s="91"/>
-      <c r="CG74" s="91"/>
-      <c r="CH74" s="92"/>
-      <c r="CI74" s="94"/>
-      <c r="CJ74" s="95"/>
-      <c r="CK74" s="91"/>
-      <c r="CL74" s="91"/>
-      <c r="CM74" s="91"/>
-      <c r="CN74" s="91"/>
-      <c r="CO74" s="92"/>
-      <c r="CP74" s="93"/>
-      <c r="CQ74" s="90"/>
-      <c r="CR74" s="91"/>
-      <c r="CS74" s="91"/>
-      <c r="CT74" s="91"/>
-      <c r="CU74" s="91"/>
-      <c r="CV74" s="92"/>
-      <c r="CW74" s="93"/>
-      <c r="CX74" s="90"/>
-      <c r="CY74" s="91"/>
-      <c r="CZ74" s="91"/>
-      <c r="DA74" s="91"/>
-      <c r="DB74" s="91"/>
-      <c r="DC74" s="92"/>
-      <c r="DD74" s="93"/>
-      <c r="DE74" s="90"/>
-      <c r="DF74" s="91"/>
     </row>
     <row r="75" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="96"/>
@@ -12286,45 +9650,6 @@
       <c r="BQ75" s="91"/>
       <c r="BR75" s="91"/>
       <c r="BS75" s="91"/>
-      <c r="BT75" s="92"/>
-      <c r="BU75" s="93"/>
-      <c r="BV75" s="90"/>
-      <c r="BW75" s="91"/>
-      <c r="BX75" s="91"/>
-      <c r="BY75" s="91"/>
-      <c r="BZ75" s="91"/>
-      <c r="CA75" s="92"/>
-      <c r="CB75" s="93"/>
-      <c r="CC75" s="90"/>
-      <c r="CD75" s="91"/>
-      <c r="CE75" s="91"/>
-      <c r="CF75" s="91"/>
-      <c r="CG75" s="91"/>
-      <c r="CH75" s="92"/>
-      <c r="CI75" s="94"/>
-      <c r="CJ75" s="95"/>
-      <c r="CK75" s="91"/>
-      <c r="CL75" s="91"/>
-      <c r="CM75" s="91"/>
-      <c r="CN75" s="91"/>
-      <c r="CO75" s="92"/>
-      <c r="CP75" s="93"/>
-      <c r="CQ75" s="90"/>
-      <c r="CR75" s="91"/>
-      <c r="CS75" s="91"/>
-      <c r="CT75" s="91"/>
-      <c r="CU75" s="91"/>
-      <c r="CV75" s="92"/>
-      <c r="CW75" s="93"/>
-      <c r="CX75" s="90"/>
-      <c r="CY75" s="91"/>
-      <c r="CZ75" s="91"/>
-      <c r="DA75" s="91"/>
-      <c r="DB75" s="91"/>
-      <c r="DC75" s="92"/>
-      <c r="DD75" s="93"/>
-      <c r="DE75" s="90"/>
-      <c r="DF75" s="91"/>
     </row>
     <row r="76" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="96"/>
@@ -12398,45 +9723,6 @@
       <c r="BQ76" s="91"/>
       <c r="BR76" s="91"/>
       <c r="BS76" s="91"/>
-      <c r="BT76" s="92"/>
-      <c r="BU76" s="93"/>
-      <c r="BV76" s="90"/>
-      <c r="BW76" s="91"/>
-      <c r="BX76" s="91"/>
-      <c r="BY76" s="91"/>
-      <c r="BZ76" s="91"/>
-      <c r="CA76" s="92"/>
-      <c r="CB76" s="93"/>
-      <c r="CC76" s="90"/>
-      <c r="CD76" s="91"/>
-      <c r="CE76" s="91"/>
-      <c r="CF76" s="91"/>
-      <c r="CG76" s="91"/>
-      <c r="CH76" s="92"/>
-      <c r="CI76" s="94"/>
-      <c r="CJ76" s="95"/>
-      <c r="CK76" s="91"/>
-      <c r="CL76" s="91"/>
-      <c r="CM76" s="91"/>
-      <c r="CN76" s="91"/>
-      <c r="CO76" s="92"/>
-      <c r="CP76" s="93"/>
-      <c r="CQ76" s="90"/>
-      <c r="CR76" s="91"/>
-      <c r="CS76" s="91"/>
-      <c r="CT76" s="91"/>
-      <c r="CU76" s="91"/>
-      <c r="CV76" s="92"/>
-      <c r="CW76" s="93"/>
-      <c r="CX76" s="90"/>
-      <c r="CY76" s="91"/>
-      <c r="CZ76" s="91"/>
-      <c r="DA76" s="91"/>
-      <c r="DB76" s="91"/>
-      <c r="DC76" s="92"/>
-      <c r="DD76" s="93"/>
-      <c r="DE76" s="90"/>
-      <c r="DF76" s="91"/>
     </row>
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="117"/>
@@ -12510,45 +9796,6 @@
       <c r="BQ77" s="91"/>
       <c r="BR77" s="91"/>
       <c r="BS77" s="91"/>
-      <c r="BT77" s="92"/>
-      <c r="BU77" s="93"/>
-      <c r="BV77" s="90"/>
-      <c r="BW77" s="91"/>
-      <c r="BX77" s="91"/>
-      <c r="BY77" s="91"/>
-      <c r="BZ77" s="91"/>
-      <c r="CA77" s="92"/>
-      <c r="CB77" s="93"/>
-      <c r="CC77" s="90"/>
-      <c r="CD77" s="91"/>
-      <c r="CE77" s="91"/>
-      <c r="CF77" s="91"/>
-      <c r="CG77" s="91"/>
-      <c r="CH77" s="92"/>
-      <c r="CI77" s="94"/>
-      <c r="CJ77" s="95"/>
-      <c r="CK77" s="91"/>
-      <c r="CL77" s="91"/>
-      <c r="CM77" s="91"/>
-      <c r="CN77" s="91"/>
-      <c r="CO77" s="92"/>
-      <c r="CP77" s="93"/>
-      <c r="CQ77" s="90"/>
-      <c r="CR77" s="91"/>
-      <c r="CS77" s="91"/>
-      <c r="CT77" s="91"/>
-      <c r="CU77" s="91"/>
-      <c r="CV77" s="92"/>
-      <c r="CW77" s="93"/>
-      <c r="CX77" s="90"/>
-      <c r="CY77" s="91"/>
-      <c r="CZ77" s="91"/>
-      <c r="DA77" s="91"/>
-      <c r="DB77" s="91"/>
-      <c r="DC77" s="92"/>
-      <c r="DD77" s="93"/>
-      <c r="DE77" s="90"/>
-      <c r="DF77" s="91"/>
     </row>
     <row r="78" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="96"/>
@@ -12622,45 +9869,6 @@
       <c r="BQ78" s="91"/>
       <c r="BR78" s="91"/>
       <c r="BS78" s="91"/>
-      <c r="BT78" s="92"/>
-      <c r="BU78" s="93"/>
-      <c r="BV78" s="90"/>
-      <c r="BW78" s="91"/>
-      <c r="BX78" s="91"/>
-      <c r="BY78" s="91"/>
-      <c r="BZ78" s="91"/>
-      <c r="CA78" s="92"/>
-      <c r="CB78" s="93"/>
-      <c r="CC78" s="90"/>
-      <c r="CD78" s="91"/>
-      <c r="CE78" s="91"/>
-      <c r="CF78" s="91"/>
-      <c r="CG78" s="91"/>
-      <c r="CH78" s="92"/>
-      <c r="CI78" s="94"/>
-      <c r="CJ78" s="95"/>
-      <c r="CK78" s="91"/>
-      <c r="CL78" s="91"/>
-      <c r="CM78" s="91"/>
-      <c r="CN78" s="91"/>
-      <c r="CO78" s="92"/>
-      <c r="CP78" s="93"/>
-      <c r="CQ78" s="90"/>
-      <c r="CR78" s="91"/>
-      <c r="CS78" s="91"/>
-      <c r="CT78" s="91"/>
-      <c r="CU78" s="91"/>
-      <c r="CV78" s="92"/>
-      <c r="CW78" s="93"/>
-      <c r="CX78" s="90"/>
-      <c r="CY78" s="91"/>
-      <c r="CZ78" s="91"/>
-      <c r="DA78" s="91"/>
-      <c r="DB78" s="91"/>
-      <c r="DC78" s="92"/>
-      <c r="DD78" s="93"/>
-      <c r="DE78" s="90"/>
-      <c r="DF78" s="91"/>
     </row>
     <row r="79" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="96"/>
@@ -12734,45 +9942,6 @@
       <c r="BQ79" s="91"/>
       <c r="BR79" s="91"/>
       <c r="BS79" s="91"/>
-      <c r="BT79" s="92"/>
-      <c r="BU79" s="93"/>
-      <c r="BV79" s="90"/>
-      <c r="BW79" s="91"/>
-      <c r="BX79" s="91"/>
-      <c r="BY79" s="91"/>
-      <c r="BZ79" s="91"/>
-      <c r="CA79" s="92"/>
-      <c r="CB79" s="93"/>
-      <c r="CC79" s="90"/>
-      <c r="CD79" s="91"/>
-      <c r="CE79" s="91"/>
-      <c r="CF79" s="91"/>
-      <c r="CG79" s="91"/>
-      <c r="CH79" s="92"/>
-      <c r="CI79" s="94"/>
-      <c r="CJ79" s="95"/>
-      <c r="CK79" s="91"/>
-      <c r="CL79" s="91"/>
-      <c r="CM79" s="91"/>
-      <c r="CN79" s="91"/>
-      <c r="CO79" s="92"/>
-      <c r="CP79" s="93"/>
-      <c r="CQ79" s="90"/>
-      <c r="CR79" s="91"/>
-      <c r="CS79" s="91"/>
-      <c r="CT79" s="91"/>
-      <c r="CU79" s="91"/>
-      <c r="CV79" s="92"/>
-      <c r="CW79" s="93"/>
-      <c r="CX79" s="90"/>
-      <c r="CY79" s="91"/>
-      <c r="CZ79" s="91"/>
-      <c r="DA79" s="91"/>
-      <c r="DB79" s="91"/>
-      <c r="DC79" s="92"/>
-      <c r="DD79" s="93"/>
-      <c r="DE79" s="90"/>
-      <c r="DF79" s="91"/>
     </row>
     <row r="80" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="96"/>
@@ -12846,45 +10015,6 @@
       <c r="BQ80" s="91"/>
       <c r="BR80" s="91"/>
       <c r="BS80" s="91"/>
-      <c r="BT80" s="92"/>
-      <c r="BU80" s="93"/>
-      <c r="BV80" s="90"/>
-      <c r="BW80" s="91"/>
-      <c r="BX80" s="91"/>
-      <c r="BY80" s="91"/>
-      <c r="BZ80" s="91"/>
-      <c r="CA80" s="92"/>
-      <c r="CB80" s="93"/>
-      <c r="CC80" s="90"/>
-      <c r="CD80" s="91"/>
-      <c r="CE80" s="91"/>
-      <c r="CF80" s="91"/>
-      <c r="CG80" s="91"/>
-      <c r="CH80" s="92"/>
-      <c r="CI80" s="94"/>
-      <c r="CJ80" s="95"/>
-      <c r="CK80" s="91"/>
-      <c r="CL80" s="91"/>
-      <c r="CM80" s="91"/>
-      <c r="CN80" s="91"/>
-      <c r="CO80" s="92"/>
-      <c r="CP80" s="93"/>
-      <c r="CQ80" s="90"/>
-      <c r="CR80" s="91"/>
-      <c r="CS80" s="91"/>
-      <c r="CT80" s="91"/>
-      <c r="CU80" s="91"/>
-      <c r="CV80" s="92"/>
-      <c r="CW80" s="93"/>
-      <c r="CX80" s="90"/>
-      <c r="CY80" s="91"/>
-      <c r="CZ80" s="91"/>
-      <c r="DA80" s="91"/>
-      <c r="DB80" s="91"/>
-      <c r="DC80" s="92"/>
-      <c r="DD80" s="93"/>
-      <c r="DE80" s="90"/>
-      <c r="DF80" s="91"/>
     </row>
     <row r="81" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="96"/>
@@ -12958,45 +10088,6 @@
       <c r="BQ81" s="91"/>
       <c r="BR81" s="91"/>
       <c r="BS81" s="91"/>
-      <c r="BT81" s="92"/>
-      <c r="BU81" s="93"/>
-      <c r="BV81" s="90"/>
-      <c r="BW81" s="91"/>
-      <c r="BX81" s="91"/>
-      <c r="BY81" s="91"/>
-      <c r="BZ81" s="91"/>
-      <c r="CA81" s="92"/>
-      <c r="CB81" s="93"/>
-      <c r="CC81" s="90"/>
-      <c r="CD81" s="91"/>
-      <c r="CE81" s="91"/>
-      <c r="CF81" s="91"/>
-      <c r="CG81" s="91"/>
-      <c r="CH81" s="92"/>
-      <c r="CI81" s="94"/>
-      <c r="CJ81" s="95"/>
-      <c r="CK81" s="91"/>
-      <c r="CL81" s="91"/>
-      <c r="CM81" s="91"/>
-      <c r="CN81" s="91"/>
-      <c r="CO81" s="92"/>
-      <c r="CP81" s="93"/>
-      <c r="CQ81" s="90"/>
-      <c r="CR81" s="91"/>
-      <c r="CS81" s="91"/>
-      <c r="CT81" s="91"/>
-      <c r="CU81" s="91"/>
-      <c r="CV81" s="92"/>
-      <c r="CW81" s="93"/>
-      <c r="CX81" s="90"/>
-      <c r="CY81" s="91"/>
-      <c r="CZ81" s="91"/>
-      <c r="DA81" s="91"/>
-      <c r="DB81" s="91"/>
-      <c r="DC81" s="92"/>
-      <c r="DD81" s="93"/>
-      <c r="DE81" s="90"/>
-      <c r="DF81" s="91"/>
     </row>
     <row r="82" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="117"/>
@@ -13070,45 +10161,6 @@
       <c r="BQ82" s="91"/>
       <c r="BR82" s="91"/>
       <c r="BS82" s="91"/>
-      <c r="BT82" s="92"/>
-      <c r="BU82" s="93"/>
-      <c r="BV82" s="90"/>
-      <c r="BW82" s="91"/>
-      <c r="BX82" s="91"/>
-      <c r="BY82" s="91"/>
-      <c r="BZ82" s="91"/>
-      <c r="CA82" s="92"/>
-      <c r="CB82" s="93"/>
-      <c r="CC82" s="90"/>
-      <c r="CD82" s="91"/>
-      <c r="CE82" s="91"/>
-      <c r="CF82" s="91"/>
-      <c r="CG82" s="91"/>
-      <c r="CH82" s="92"/>
-      <c r="CI82" s="94"/>
-      <c r="CJ82" s="95"/>
-      <c r="CK82" s="91"/>
-      <c r="CL82" s="91"/>
-      <c r="CM82" s="91"/>
-      <c r="CN82" s="91"/>
-      <c r="CO82" s="92"/>
-      <c r="CP82" s="93"/>
-      <c r="CQ82" s="90"/>
-      <c r="CR82" s="91"/>
-      <c r="CS82" s="91"/>
-      <c r="CT82" s="91"/>
-      <c r="CU82" s="91"/>
-      <c r="CV82" s="92"/>
-      <c r="CW82" s="93"/>
-      <c r="CX82" s="90"/>
-      <c r="CY82" s="91"/>
-      <c r="CZ82" s="91"/>
-      <c r="DA82" s="91"/>
-      <c r="DB82" s="91"/>
-      <c r="DC82" s="92"/>
-      <c r="DD82" s="93"/>
-      <c r="DE82" s="90"/>
-      <c r="DF82" s="91"/>
     </row>
     <row r="83" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="96"/>
@@ -13182,45 +10234,6 @@
       <c r="BQ83" s="91"/>
       <c r="BR83" s="91"/>
       <c r="BS83" s="91"/>
-      <c r="BT83" s="92"/>
-      <c r="BU83" s="93"/>
-      <c r="BV83" s="90"/>
-      <c r="BW83" s="91"/>
-      <c r="BX83" s="91"/>
-      <c r="BY83" s="91"/>
-      <c r="BZ83" s="91"/>
-      <c r="CA83" s="92"/>
-      <c r="CB83" s="93"/>
-      <c r="CC83" s="90"/>
-      <c r="CD83" s="91"/>
-      <c r="CE83" s="91"/>
-      <c r="CF83" s="91"/>
-      <c r="CG83" s="91"/>
-      <c r="CH83" s="92"/>
-      <c r="CI83" s="94"/>
-      <c r="CJ83" s="95"/>
-      <c r="CK83" s="91"/>
-      <c r="CL83" s="91"/>
-      <c r="CM83" s="91"/>
-      <c r="CN83" s="91"/>
-      <c r="CO83" s="92"/>
-      <c r="CP83" s="93"/>
-      <c r="CQ83" s="90"/>
-      <c r="CR83" s="91"/>
-      <c r="CS83" s="91"/>
-      <c r="CT83" s="91"/>
-      <c r="CU83" s="91"/>
-      <c r="CV83" s="92"/>
-      <c r="CW83" s="93"/>
-      <c r="CX83" s="90"/>
-      <c r="CY83" s="91"/>
-      <c r="CZ83" s="91"/>
-      <c r="DA83" s="91"/>
-      <c r="DB83" s="91"/>
-      <c r="DC83" s="92"/>
-      <c r="DD83" s="93"/>
-      <c r="DE83" s="90"/>
-      <c r="DF83" s="91"/>
     </row>
     <row r="84" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="96"/>
@@ -13294,45 +10307,6 @@
       <c r="BQ84" s="91"/>
       <c r="BR84" s="91"/>
       <c r="BS84" s="91"/>
-      <c r="BT84" s="92"/>
-      <c r="BU84" s="93"/>
-      <c r="BV84" s="90"/>
-      <c r="BW84" s="91"/>
-      <c r="BX84" s="91"/>
-      <c r="BY84" s="91"/>
-      <c r="BZ84" s="91"/>
-      <c r="CA84" s="92"/>
-      <c r="CB84" s="93"/>
-      <c r="CC84" s="90"/>
-      <c r="CD84" s="91"/>
-      <c r="CE84" s="91"/>
-      <c r="CF84" s="91"/>
-      <c r="CG84" s="91"/>
-      <c r="CH84" s="92"/>
-      <c r="CI84" s="94"/>
-      <c r="CJ84" s="95"/>
-      <c r="CK84" s="91"/>
-      <c r="CL84" s="91"/>
-      <c r="CM84" s="91"/>
-      <c r="CN84" s="91"/>
-      <c r="CO84" s="92"/>
-      <c r="CP84" s="93"/>
-      <c r="CQ84" s="90"/>
-      <c r="CR84" s="91"/>
-      <c r="CS84" s="91"/>
-      <c r="CT84" s="91"/>
-      <c r="CU84" s="91"/>
-      <c r="CV84" s="92"/>
-      <c r="CW84" s="93"/>
-      <c r="CX84" s="90"/>
-      <c r="CY84" s="91"/>
-      <c r="CZ84" s="91"/>
-      <c r="DA84" s="91"/>
-      <c r="DB84" s="91"/>
-      <c r="DC84" s="92"/>
-      <c r="DD84" s="93"/>
-      <c r="DE84" s="90"/>
-      <c r="DF84" s="91"/>
     </row>
     <row r="85" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="83"/>
@@ -13406,45 +10380,6 @@
       <c r="BQ85" s="91"/>
       <c r="BR85" s="91"/>
       <c r="BS85" s="91"/>
-      <c r="BT85" s="92"/>
-      <c r="BU85" s="93"/>
-      <c r="BV85" s="90"/>
-      <c r="BW85" s="91"/>
-      <c r="BX85" s="91"/>
-      <c r="BY85" s="91"/>
-      <c r="BZ85" s="91"/>
-      <c r="CA85" s="92"/>
-      <c r="CB85" s="93"/>
-      <c r="CC85" s="90"/>
-      <c r="CD85" s="91"/>
-      <c r="CE85" s="91"/>
-      <c r="CF85" s="91"/>
-      <c r="CG85" s="91"/>
-      <c r="CH85" s="92"/>
-      <c r="CI85" s="94"/>
-      <c r="CJ85" s="95"/>
-      <c r="CK85" s="91"/>
-      <c r="CL85" s="91"/>
-      <c r="CM85" s="91"/>
-      <c r="CN85" s="91"/>
-      <c r="CO85" s="92"/>
-      <c r="CP85" s="93"/>
-      <c r="CQ85" s="90"/>
-      <c r="CR85" s="91"/>
-      <c r="CS85" s="91"/>
-      <c r="CT85" s="91"/>
-      <c r="CU85" s="91"/>
-      <c r="CV85" s="92"/>
-      <c r="CW85" s="93"/>
-      <c r="CX85" s="90"/>
-      <c r="CY85" s="91"/>
-      <c r="CZ85" s="91"/>
-      <c r="DA85" s="91"/>
-      <c r="DB85" s="91"/>
-      <c r="DC85" s="92"/>
-      <c r="DD85" s="93"/>
-      <c r="DE85" s="90"/>
-      <c r="DF85" s="91"/>
     </row>
     <row r="86" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="117"/>
@@ -13518,45 +10453,6 @@
       <c r="BQ86" s="91"/>
       <c r="BR86" s="91"/>
       <c r="BS86" s="91"/>
-      <c r="BT86" s="92"/>
-      <c r="BU86" s="93"/>
-      <c r="BV86" s="90"/>
-      <c r="BW86" s="91"/>
-      <c r="BX86" s="91"/>
-      <c r="BY86" s="91"/>
-      <c r="BZ86" s="91"/>
-      <c r="CA86" s="92"/>
-      <c r="CB86" s="93"/>
-      <c r="CC86" s="90"/>
-      <c r="CD86" s="91"/>
-      <c r="CE86" s="91"/>
-      <c r="CF86" s="91"/>
-      <c r="CG86" s="91"/>
-      <c r="CH86" s="92"/>
-      <c r="CI86" s="94"/>
-      <c r="CJ86" s="95"/>
-      <c r="CK86" s="91"/>
-      <c r="CL86" s="91"/>
-      <c r="CM86" s="91"/>
-      <c r="CN86" s="91"/>
-      <c r="CO86" s="92"/>
-      <c r="CP86" s="93"/>
-      <c r="CQ86" s="90"/>
-      <c r="CR86" s="91"/>
-      <c r="CS86" s="91"/>
-      <c r="CT86" s="91"/>
-      <c r="CU86" s="91"/>
-      <c r="CV86" s="92"/>
-      <c r="CW86" s="93"/>
-      <c r="CX86" s="90"/>
-      <c r="CY86" s="91"/>
-      <c r="CZ86" s="91"/>
-      <c r="DA86" s="91"/>
-      <c r="DB86" s="91"/>
-      <c r="DC86" s="92"/>
-      <c r="DD86" s="93"/>
-      <c r="DE86" s="90"/>
-      <c r="DF86" s="91"/>
     </row>
     <row r="87" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="96"/>
@@ -13630,45 +10526,6 @@
       <c r="BQ87" s="91"/>
       <c r="BR87" s="91"/>
       <c r="BS87" s="91"/>
-      <c r="BT87" s="92"/>
-      <c r="BU87" s="93"/>
-      <c r="BV87" s="90"/>
-      <c r="BW87" s="91"/>
-      <c r="BX87" s="91"/>
-      <c r="BY87" s="91"/>
-      <c r="BZ87" s="91"/>
-      <c r="CA87" s="92"/>
-      <c r="CB87" s="93"/>
-      <c r="CC87" s="90"/>
-      <c r="CD87" s="91"/>
-      <c r="CE87" s="91"/>
-      <c r="CF87" s="91"/>
-      <c r="CG87" s="91"/>
-      <c r="CH87" s="92"/>
-      <c r="CI87" s="94"/>
-      <c r="CJ87" s="95"/>
-      <c r="CK87" s="91"/>
-      <c r="CL87" s="91"/>
-      <c r="CM87" s="91"/>
-      <c r="CN87" s="91"/>
-      <c r="CO87" s="92"/>
-      <c r="CP87" s="93"/>
-      <c r="CQ87" s="90"/>
-      <c r="CR87" s="91"/>
-      <c r="CS87" s="91"/>
-      <c r="CT87" s="91"/>
-      <c r="CU87" s="91"/>
-      <c r="CV87" s="92"/>
-      <c r="CW87" s="93"/>
-      <c r="CX87" s="90"/>
-      <c r="CY87" s="91"/>
-      <c r="CZ87" s="91"/>
-      <c r="DA87" s="91"/>
-      <c r="DB87" s="91"/>
-      <c r="DC87" s="92"/>
-      <c r="DD87" s="93"/>
-      <c r="DE87" s="90"/>
-      <c r="DF87" s="91"/>
     </row>
     <row r="88" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="96"/>
@@ -13742,45 +10599,6 @@
       <c r="BQ88" s="91"/>
       <c r="BR88" s="91"/>
       <c r="BS88" s="91"/>
-      <c r="BT88" s="92"/>
-      <c r="BU88" s="93"/>
-      <c r="BV88" s="90"/>
-      <c r="BW88" s="91"/>
-      <c r="BX88" s="91"/>
-      <c r="BY88" s="91"/>
-      <c r="BZ88" s="91"/>
-      <c r="CA88" s="92"/>
-      <c r="CB88" s="93"/>
-      <c r="CC88" s="90"/>
-      <c r="CD88" s="91"/>
-      <c r="CE88" s="91"/>
-      <c r="CF88" s="91"/>
-      <c r="CG88" s="91"/>
-      <c r="CH88" s="92"/>
-      <c r="CI88" s="94"/>
-      <c r="CJ88" s="95"/>
-      <c r="CK88" s="91"/>
-      <c r="CL88" s="91"/>
-      <c r="CM88" s="91"/>
-      <c r="CN88" s="91"/>
-      <c r="CO88" s="92"/>
-      <c r="CP88" s="93"/>
-      <c r="CQ88" s="90"/>
-      <c r="CR88" s="91"/>
-      <c r="CS88" s="91"/>
-      <c r="CT88" s="91"/>
-      <c r="CU88" s="91"/>
-      <c r="CV88" s="92"/>
-      <c r="CW88" s="93"/>
-      <c r="CX88" s="90"/>
-      <c r="CY88" s="91"/>
-      <c r="CZ88" s="91"/>
-      <c r="DA88" s="91"/>
-      <c r="DB88" s="91"/>
-      <c r="DC88" s="92"/>
-      <c r="DD88" s="93"/>
-      <c r="DE88" s="90"/>
-      <c r="DF88" s="91"/>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="96"/>
@@ -13854,45 +10672,6 @@
       <c r="BQ89" s="91"/>
       <c r="BR89" s="91"/>
       <c r="BS89" s="91"/>
-      <c r="BT89" s="92"/>
-      <c r="BU89" s="93"/>
-      <c r="BV89" s="90"/>
-      <c r="BW89" s="91"/>
-      <c r="BX89" s="91"/>
-      <c r="BY89" s="91"/>
-      <c r="BZ89" s="91"/>
-      <c r="CA89" s="92"/>
-      <c r="CB89" s="93"/>
-      <c r="CC89" s="90"/>
-      <c r="CD89" s="91"/>
-      <c r="CE89" s="91"/>
-      <c r="CF89" s="91"/>
-      <c r="CG89" s="91"/>
-      <c r="CH89" s="92"/>
-      <c r="CI89" s="94"/>
-      <c r="CJ89" s="95"/>
-      <c r="CK89" s="91"/>
-      <c r="CL89" s="91"/>
-      <c r="CM89" s="91"/>
-      <c r="CN89" s="91"/>
-      <c r="CO89" s="92"/>
-      <c r="CP89" s="93"/>
-      <c r="CQ89" s="90"/>
-      <c r="CR89" s="91"/>
-      <c r="CS89" s="91"/>
-      <c r="CT89" s="91"/>
-      <c r="CU89" s="91"/>
-      <c r="CV89" s="92"/>
-      <c r="CW89" s="93"/>
-      <c r="CX89" s="90"/>
-      <c r="CY89" s="91"/>
-      <c r="CZ89" s="91"/>
-      <c r="DA89" s="91"/>
-      <c r="DB89" s="91"/>
-      <c r="DC89" s="92"/>
-      <c r="DD89" s="93"/>
-      <c r="DE89" s="90"/>
-      <c r="DF89" s="91"/>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="96"/>
@@ -13966,45 +10745,6 @@
       <c r="BQ90" s="91"/>
       <c r="BR90" s="91"/>
       <c r="BS90" s="91"/>
-      <c r="BT90" s="92"/>
-      <c r="BU90" s="93"/>
-      <c r="BV90" s="90"/>
-      <c r="BW90" s="91"/>
-      <c r="BX90" s="91"/>
-      <c r="BY90" s="91"/>
-      <c r="BZ90" s="91"/>
-      <c r="CA90" s="92"/>
-      <c r="CB90" s="93"/>
-      <c r="CC90" s="90"/>
-      <c r="CD90" s="91"/>
-      <c r="CE90" s="91"/>
-      <c r="CF90" s="91"/>
-      <c r="CG90" s="91"/>
-      <c r="CH90" s="92"/>
-      <c r="CI90" s="94"/>
-      <c r="CJ90" s="95"/>
-      <c r="CK90" s="91"/>
-      <c r="CL90" s="91"/>
-      <c r="CM90" s="91"/>
-      <c r="CN90" s="91"/>
-      <c r="CO90" s="92"/>
-      <c r="CP90" s="93"/>
-      <c r="CQ90" s="90"/>
-      <c r="CR90" s="91"/>
-      <c r="CS90" s="91"/>
-      <c r="CT90" s="91"/>
-      <c r="CU90" s="91"/>
-      <c r="CV90" s="92"/>
-      <c r="CW90" s="93"/>
-      <c r="CX90" s="90"/>
-      <c r="CY90" s="91"/>
-      <c r="CZ90" s="91"/>
-      <c r="DA90" s="91"/>
-      <c r="DB90" s="91"/>
-      <c r="DC90" s="92"/>
-      <c r="DD90" s="93"/>
-      <c r="DE90" s="90"/>
-      <c r="DF90" s="91"/>
     </row>
     <row r="91" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="117"/>
@@ -14078,45 +10818,6 @@
       <c r="BQ91" s="91"/>
       <c r="BR91" s="91"/>
       <c r="BS91" s="91"/>
-      <c r="BT91" s="92"/>
-      <c r="BU91" s="93"/>
-      <c r="BV91" s="90"/>
-      <c r="BW91" s="91"/>
-      <c r="BX91" s="91"/>
-      <c r="BY91" s="91"/>
-      <c r="BZ91" s="91"/>
-      <c r="CA91" s="92"/>
-      <c r="CB91" s="93"/>
-      <c r="CC91" s="90"/>
-      <c r="CD91" s="91"/>
-      <c r="CE91" s="91"/>
-      <c r="CF91" s="91"/>
-      <c r="CG91" s="91"/>
-      <c r="CH91" s="92"/>
-      <c r="CI91" s="94"/>
-      <c r="CJ91" s="95"/>
-      <c r="CK91" s="91"/>
-      <c r="CL91" s="91"/>
-      <c r="CM91" s="91"/>
-      <c r="CN91" s="91"/>
-      <c r="CO91" s="92"/>
-      <c r="CP91" s="93"/>
-      <c r="CQ91" s="90"/>
-      <c r="CR91" s="91"/>
-      <c r="CS91" s="91"/>
-      <c r="CT91" s="91"/>
-      <c r="CU91" s="91"/>
-      <c r="CV91" s="92"/>
-      <c r="CW91" s="93"/>
-      <c r="CX91" s="90"/>
-      <c r="CY91" s="91"/>
-      <c r="CZ91" s="91"/>
-      <c r="DA91" s="91"/>
-      <c r="DB91" s="91"/>
-      <c r="DC91" s="92"/>
-      <c r="DD91" s="93"/>
-      <c r="DE91" s="90"/>
-      <c r="DF91" s="91"/>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="96"/>
@@ -14190,45 +10891,6 @@
       <c r="BQ92" s="91"/>
       <c r="BR92" s="91"/>
       <c r="BS92" s="91"/>
-      <c r="BT92" s="92"/>
-      <c r="BU92" s="93"/>
-      <c r="BV92" s="90"/>
-      <c r="BW92" s="91"/>
-      <c r="BX92" s="91"/>
-      <c r="BY92" s="91"/>
-      <c r="BZ92" s="91"/>
-      <c r="CA92" s="92"/>
-      <c r="CB92" s="93"/>
-      <c r="CC92" s="90"/>
-      <c r="CD92" s="91"/>
-      <c r="CE92" s="91"/>
-      <c r="CF92" s="91"/>
-      <c r="CG92" s="91"/>
-      <c r="CH92" s="92"/>
-      <c r="CI92" s="94"/>
-      <c r="CJ92" s="95"/>
-      <c r="CK92" s="91"/>
-      <c r="CL92" s="91"/>
-      <c r="CM92" s="91"/>
-      <c r="CN92" s="91"/>
-      <c r="CO92" s="92"/>
-      <c r="CP92" s="93"/>
-      <c r="CQ92" s="90"/>
-      <c r="CR92" s="91"/>
-      <c r="CS92" s="91"/>
-      <c r="CT92" s="91"/>
-      <c r="CU92" s="91"/>
-      <c r="CV92" s="92"/>
-      <c r="CW92" s="93"/>
-      <c r="CX92" s="90"/>
-      <c r="CY92" s="91"/>
-      <c r="CZ92" s="91"/>
-      <c r="DA92" s="91"/>
-      <c r="DB92" s="91"/>
-      <c r="DC92" s="92"/>
-      <c r="DD92" s="93"/>
-      <c r="DE92" s="90"/>
-      <c r="DF92" s="91"/>
     </row>
     <row r="93" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="96"/>
@@ -14302,45 +10964,6 @@
       <c r="BQ93" s="91"/>
       <c r="BR93" s="91"/>
       <c r="BS93" s="91"/>
-      <c r="BT93" s="92"/>
-      <c r="BU93" s="93"/>
-      <c r="BV93" s="90"/>
-      <c r="BW93" s="91"/>
-      <c r="BX93" s="91"/>
-      <c r="BY93" s="91"/>
-      <c r="BZ93" s="91"/>
-      <c r="CA93" s="92"/>
-      <c r="CB93" s="93"/>
-      <c r="CC93" s="90"/>
-      <c r="CD93" s="91"/>
-      <c r="CE93" s="91"/>
-      <c r="CF93" s="91"/>
-      <c r="CG93" s="91"/>
-      <c r="CH93" s="92"/>
-      <c r="CI93" s="94"/>
-      <c r="CJ93" s="95"/>
-      <c r="CK93" s="91"/>
-      <c r="CL93" s="91"/>
-      <c r="CM93" s="91"/>
-      <c r="CN93" s="91"/>
-      <c r="CO93" s="92"/>
-      <c r="CP93" s="93"/>
-      <c r="CQ93" s="90"/>
-      <c r="CR93" s="91"/>
-      <c r="CS93" s="91"/>
-      <c r="CT93" s="91"/>
-      <c r="CU93" s="91"/>
-      <c r="CV93" s="92"/>
-      <c r="CW93" s="93"/>
-      <c r="CX93" s="90"/>
-      <c r="CY93" s="91"/>
-      <c r="CZ93" s="91"/>
-      <c r="DA93" s="91"/>
-      <c r="DB93" s="91"/>
-      <c r="DC93" s="92"/>
-      <c r="DD93" s="93"/>
-      <c r="DE93" s="90"/>
-      <c r="DF93" s="91"/>
     </row>
     <row r="94" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="96"/>
@@ -14414,45 +11037,6 @@
       <c r="BQ94" s="91"/>
       <c r="BR94" s="91"/>
       <c r="BS94" s="91"/>
-      <c r="BT94" s="92"/>
-      <c r="BU94" s="93"/>
-      <c r="BV94" s="90"/>
-      <c r="BW94" s="91"/>
-      <c r="BX94" s="91"/>
-      <c r="BY94" s="91"/>
-      <c r="BZ94" s="91"/>
-      <c r="CA94" s="92"/>
-      <c r="CB94" s="93"/>
-      <c r="CC94" s="90"/>
-      <c r="CD94" s="91"/>
-      <c r="CE94" s="91"/>
-      <c r="CF94" s="91"/>
-      <c r="CG94" s="91"/>
-      <c r="CH94" s="92"/>
-      <c r="CI94" s="94"/>
-      <c r="CJ94" s="95"/>
-      <c r="CK94" s="91"/>
-      <c r="CL94" s="91"/>
-      <c r="CM94" s="91"/>
-      <c r="CN94" s="91"/>
-      <c r="CO94" s="92"/>
-      <c r="CP94" s="93"/>
-      <c r="CQ94" s="90"/>
-      <c r="CR94" s="91"/>
-      <c r="CS94" s="91"/>
-      <c r="CT94" s="91"/>
-      <c r="CU94" s="91"/>
-      <c r="CV94" s="92"/>
-      <c r="CW94" s="93"/>
-      <c r="CX94" s="90"/>
-      <c r="CY94" s="91"/>
-      <c r="CZ94" s="91"/>
-      <c r="DA94" s="91"/>
-      <c r="DB94" s="91"/>
-      <c r="DC94" s="92"/>
-      <c r="DD94" s="93"/>
-      <c r="DE94" s="90"/>
-      <c r="DF94" s="91"/>
     </row>
     <row r="95" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="96"/>
@@ -14526,45 +11110,6 @@
       <c r="BQ95" s="91"/>
       <c r="BR95" s="91"/>
       <c r="BS95" s="91"/>
-      <c r="BT95" s="92"/>
-      <c r="BU95" s="93"/>
-      <c r="BV95" s="90"/>
-      <c r="BW95" s="91"/>
-      <c r="BX95" s="91"/>
-      <c r="BY95" s="91"/>
-      <c r="BZ95" s="91"/>
-      <c r="CA95" s="92"/>
-      <c r="CB95" s="93"/>
-      <c r="CC95" s="90"/>
-      <c r="CD95" s="91"/>
-      <c r="CE95" s="91"/>
-      <c r="CF95" s="91"/>
-      <c r="CG95" s="91"/>
-      <c r="CH95" s="92"/>
-      <c r="CI95" s="94"/>
-      <c r="CJ95" s="95"/>
-      <c r="CK95" s="91"/>
-      <c r="CL95" s="91"/>
-      <c r="CM95" s="91"/>
-      <c r="CN95" s="91"/>
-      <c r="CO95" s="92"/>
-      <c r="CP95" s="93"/>
-      <c r="CQ95" s="90"/>
-      <c r="CR95" s="91"/>
-      <c r="CS95" s="91"/>
-      <c r="CT95" s="91"/>
-      <c r="CU95" s="91"/>
-      <c r="CV95" s="92"/>
-      <c r="CW95" s="93"/>
-      <c r="CX95" s="90"/>
-      <c r="CY95" s="91"/>
-      <c r="CZ95" s="91"/>
-      <c r="DA95" s="91"/>
-      <c r="DB95" s="91"/>
-      <c r="DC95" s="92"/>
-      <c r="DD95" s="93"/>
-      <c r="DE95" s="90"/>
-      <c r="DF95" s="91"/>
     </row>
     <row r="96" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="117"/>
@@ -14638,45 +11183,6 @@
       <c r="BQ96" s="91"/>
       <c r="BR96" s="91"/>
       <c r="BS96" s="91"/>
-      <c r="BT96" s="92"/>
-      <c r="BU96" s="93"/>
-      <c r="BV96" s="90"/>
-      <c r="BW96" s="91"/>
-      <c r="BX96" s="91"/>
-      <c r="BY96" s="91"/>
-      <c r="BZ96" s="91"/>
-      <c r="CA96" s="92"/>
-      <c r="CB96" s="93"/>
-      <c r="CC96" s="90"/>
-      <c r="CD96" s="91"/>
-      <c r="CE96" s="91"/>
-      <c r="CF96" s="91"/>
-      <c r="CG96" s="91"/>
-      <c r="CH96" s="92"/>
-      <c r="CI96" s="94"/>
-      <c r="CJ96" s="95"/>
-      <c r="CK96" s="91"/>
-      <c r="CL96" s="91"/>
-      <c r="CM96" s="91"/>
-      <c r="CN96" s="91"/>
-      <c r="CO96" s="92"/>
-      <c r="CP96" s="93"/>
-      <c r="CQ96" s="90"/>
-      <c r="CR96" s="91"/>
-      <c r="CS96" s="91"/>
-      <c r="CT96" s="91"/>
-      <c r="CU96" s="91"/>
-      <c r="CV96" s="92"/>
-      <c r="CW96" s="93"/>
-      <c r="CX96" s="90"/>
-      <c r="CY96" s="91"/>
-      <c r="CZ96" s="91"/>
-      <c r="DA96" s="91"/>
-      <c r="DB96" s="91"/>
-      <c r="DC96" s="92"/>
-      <c r="DD96" s="93"/>
-      <c r="DE96" s="90"/>
-      <c r="DF96" s="91"/>
     </row>
     <row r="97" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="96"/>
@@ -14750,45 +11256,6 @@
       <c r="BQ97" s="91"/>
       <c r="BR97" s="91"/>
       <c r="BS97" s="91"/>
-      <c r="BT97" s="92"/>
-      <c r="BU97" s="93"/>
-      <c r="BV97" s="90"/>
-      <c r="BW97" s="91"/>
-      <c r="BX97" s="91"/>
-      <c r="BY97" s="91"/>
-      <c r="BZ97" s="91"/>
-      <c r="CA97" s="92"/>
-      <c r="CB97" s="93"/>
-      <c r="CC97" s="90"/>
-      <c r="CD97" s="91"/>
-      <c r="CE97" s="91"/>
-      <c r="CF97" s="91"/>
-      <c r="CG97" s="91"/>
-      <c r="CH97" s="92"/>
-      <c r="CI97" s="94"/>
-      <c r="CJ97" s="95"/>
-      <c r="CK97" s="91"/>
-      <c r="CL97" s="91"/>
-      <c r="CM97" s="91"/>
-      <c r="CN97" s="91"/>
-      <c r="CO97" s="92"/>
-      <c r="CP97" s="93"/>
-      <c r="CQ97" s="90"/>
-      <c r="CR97" s="91"/>
-      <c r="CS97" s="91"/>
-      <c r="CT97" s="91"/>
-      <c r="CU97" s="91"/>
-      <c r="CV97" s="92"/>
-      <c r="CW97" s="93"/>
-      <c r="CX97" s="90"/>
-      <c r="CY97" s="91"/>
-      <c r="CZ97" s="91"/>
-      <c r="DA97" s="91"/>
-      <c r="DB97" s="91"/>
-      <c r="DC97" s="92"/>
-      <c r="DD97" s="93"/>
-      <c r="DE97" s="90"/>
-      <c r="DF97" s="91"/>
     </row>
     <row r="98" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="96"/>
@@ -14862,45 +11329,6 @@
       <c r="BQ98" s="91"/>
       <c r="BR98" s="91"/>
       <c r="BS98" s="91"/>
-      <c r="BT98" s="92"/>
-      <c r="BU98" s="93"/>
-      <c r="BV98" s="90"/>
-      <c r="BW98" s="91"/>
-      <c r="BX98" s="91"/>
-      <c r="BY98" s="91"/>
-      <c r="BZ98" s="91"/>
-      <c r="CA98" s="92"/>
-      <c r="CB98" s="93"/>
-      <c r="CC98" s="90"/>
-      <c r="CD98" s="91"/>
-      <c r="CE98" s="91"/>
-      <c r="CF98" s="91"/>
-      <c r="CG98" s="91"/>
-      <c r="CH98" s="92"/>
-      <c r="CI98" s="94"/>
-      <c r="CJ98" s="95"/>
-      <c r="CK98" s="91"/>
-      <c r="CL98" s="91"/>
-      <c r="CM98" s="91"/>
-      <c r="CN98" s="91"/>
-      <c r="CO98" s="92"/>
-      <c r="CP98" s="93"/>
-      <c r="CQ98" s="90"/>
-      <c r="CR98" s="91"/>
-      <c r="CS98" s="91"/>
-      <c r="CT98" s="91"/>
-      <c r="CU98" s="91"/>
-      <c r="CV98" s="92"/>
-      <c r="CW98" s="93"/>
-      <c r="CX98" s="90"/>
-      <c r="CY98" s="91"/>
-      <c r="CZ98" s="91"/>
-      <c r="DA98" s="91"/>
-      <c r="DB98" s="91"/>
-      <c r="DC98" s="92"/>
-      <c r="DD98" s="93"/>
-      <c r="DE98" s="90"/>
-      <c r="DF98" s="91"/>
     </row>
     <row r="99" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="96"/>
@@ -14974,45 +11402,6 @@
       <c r="BQ99" s="91"/>
       <c r="BR99" s="91"/>
       <c r="BS99" s="91"/>
-      <c r="BT99" s="92"/>
-      <c r="BU99" s="93"/>
-      <c r="BV99" s="90"/>
-      <c r="BW99" s="91"/>
-      <c r="BX99" s="91"/>
-      <c r="BY99" s="91"/>
-      <c r="BZ99" s="91"/>
-      <c r="CA99" s="92"/>
-      <c r="CB99" s="93"/>
-      <c r="CC99" s="90"/>
-      <c r="CD99" s="91"/>
-      <c r="CE99" s="91"/>
-      <c r="CF99" s="91"/>
-      <c r="CG99" s="91"/>
-      <c r="CH99" s="92"/>
-      <c r="CI99" s="94"/>
-      <c r="CJ99" s="95"/>
-      <c r="CK99" s="91"/>
-      <c r="CL99" s="91"/>
-      <c r="CM99" s="91"/>
-      <c r="CN99" s="91"/>
-      <c r="CO99" s="92"/>
-      <c r="CP99" s="93"/>
-      <c r="CQ99" s="90"/>
-      <c r="CR99" s="91"/>
-      <c r="CS99" s="91"/>
-      <c r="CT99" s="91"/>
-      <c r="CU99" s="91"/>
-      <c r="CV99" s="92"/>
-      <c r="CW99" s="93"/>
-      <c r="CX99" s="90"/>
-      <c r="CY99" s="91"/>
-      <c r="CZ99" s="91"/>
-      <c r="DA99" s="91"/>
-      <c r="DB99" s="91"/>
-      <c r="DC99" s="92"/>
-      <c r="DD99" s="93"/>
-      <c r="DE99" s="90"/>
-      <c r="DF99" s="91"/>
     </row>
     <row r="100" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="96"/>
@@ -15086,45 +11475,6 @@
       <c r="BQ100" s="91"/>
       <c r="BR100" s="91"/>
       <c r="BS100" s="91"/>
-      <c r="BT100" s="92"/>
-      <c r="BU100" s="93"/>
-      <c r="BV100" s="90"/>
-      <c r="BW100" s="91"/>
-      <c r="BX100" s="91"/>
-      <c r="BY100" s="91"/>
-      <c r="BZ100" s="91"/>
-      <c r="CA100" s="92"/>
-      <c r="CB100" s="93"/>
-      <c r="CC100" s="90"/>
-      <c r="CD100" s="91"/>
-      <c r="CE100" s="91"/>
-      <c r="CF100" s="91"/>
-      <c r="CG100" s="91"/>
-      <c r="CH100" s="92"/>
-      <c r="CI100" s="94"/>
-      <c r="CJ100" s="95"/>
-      <c r="CK100" s="91"/>
-      <c r="CL100" s="91"/>
-      <c r="CM100" s="91"/>
-      <c r="CN100" s="91"/>
-      <c r="CO100" s="92"/>
-      <c r="CP100" s="93"/>
-      <c r="CQ100" s="90"/>
-      <c r="CR100" s="91"/>
-      <c r="CS100" s="91"/>
-      <c r="CT100" s="91"/>
-      <c r="CU100" s="91"/>
-      <c r="CV100" s="92"/>
-      <c r="CW100" s="93"/>
-      <c r="CX100" s="90"/>
-      <c r="CY100" s="91"/>
-      <c r="CZ100" s="91"/>
-      <c r="DA100" s="91"/>
-      <c r="DB100" s="91"/>
-      <c r="DC100" s="92"/>
-      <c r="DD100" s="93"/>
-      <c r="DE100" s="90"/>
-      <c r="DF100" s="91"/>
     </row>
     <row r="101" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="83"/>
@@ -15198,45 +11548,6 @@
       <c r="BQ101" s="91"/>
       <c r="BR101" s="91"/>
       <c r="BS101" s="91"/>
-      <c r="BT101" s="92"/>
-      <c r="BU101" s="93"/>
-      <c r="BV101" s="90"/>
-      <c r="BW101" s="91"/>
-      <c r="BX101" s="91"/>
-      <c r="BY101" s="91"/>
-      <c r="BZ101" s="91"/>
-      <c r="CA101" s="92"/>
-      <c r="CB101" s="93"/>
-      <c r="CC101" s="90"/>
-      <c r="CD101" s="91"/>
-      <c r="CE101" s="91"/>
-      <c r="CF101" s="91"/>
-      <c r="CG101" s="91"/>
-      <c r="CH101" s="92"/>
-      <c r="CI101" s="94"/>
-      <c r="CJ101" s="95"/>
-      <c r="CK101" s="91"/>
-      <c r="CL101" s="91"/>
-      <c r="CM101" s="91"/>
-      <c r="CN101" s="91"/>
-      <c r="CO101" s="92"/>
-      <c r="CP101" s="93"/>
-      <c r="CQ101" s="90"/>
-      <c r="CR101" s="91"/>
-      <c r="CS101" s="91"/>
-      <c r="CT101" s="91"/>
-      <c r="CU101" s="91"/>
-      <c r="CV101" s="92"/>
-      <c r="CW101" s="93"/>
-      <c r="CX101" s="90"/>
-      <c r="CY101" s="91"/>
-      <c r="CZ101" s="91"/>
-      <c r="DA101" s="91"/>
-      <c r="DB101" s="91"/>
-      <c r="DC101" s="92"/>
-      <c r="DD101" s="93"/>
-      <c r="DE101" s="90"/>
-      <c r="DF101" s="91"/>
     </row>
     <row r="102" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="96"/>
@@ -15310,45 +11621,6 @@
       <c r="BQ102" s="91"/>
       <c r="BR102" s="91"/>
       <c r="BS102" s="91"/>
-      <c r="BT102" s="92"/>
-      <c r="BU102" s="93"/>
-      <c r="BV102" s="90"/>
-      <c r="BW102" s="91"/>
-      <c r="BX102" s="91"/>
-      <c r="BY102" s="91"/>
-      <c r="BZ102" s="91"/>
-      <c r="CA102" s="92"/>
-      <c r="CB102" s="93"/>
-      <c r="CC102" s="90"/>
-      <c r="CD102" s="91"/>
-      <c r="CE102" s="91"/>
-      <c r="CF102" s="91"/>
-      <c r="CG102" s="91"/>
-      <c r="CH102" s="92"/>
-      <c r="CI102" s="94"/>
-      <c r="CJ102" s="95"/>
-      <c r="CK102" s="91"/>
-      <c r="CL102" s="91"/>
-      <c r="CM102" s="91"/>
-      <c r="CN102" s="91"/>
-      <c r="CO102" s="92"/>
-      <c r="CP102" s="93"/>
-      <c r="CQ102" s="90"/>
-      <c r="CR102" s="91"/>
-      <c r="CS102" s="91"/>
-      <c r="CT102" s="91"/>
-      <c r="CU102" s="91"/>
-      <c r="CV102" s="92"/>
-      <c r="CW102" s="93"/>
-      <c r="CX102" s="90"/>
-      <c r="CY102" s="91"/>
-      <c r="CZ102" s="91"/>
-      <c r="DA102" s="91"/>
-      <c r="DB102" s="91"/>
-      <c r="DC102" s="92"/>
-      <c r="DD102" s="93"/>
-      <c r="DE102" s="90"/>
-      <c r="DF102" s="91"/>
     </row>
     <row r="103" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="96"/>
@@ -15422,45 +11694,6 @@
       <c r="BQ103" s="91"/>
       <c r="BR103" s="91"/>
       <c r="BS103" s="91"/>
-      <c r="BT103" s="92"/>
-      <c r="BU103" s="93"/>
-      <c r="BV103" s="90"/>
-      <c r="BW103" s="91"/>
-      <c r="BX103" s="91"/>
-      <c r="BY103" s="91"/>
-      <c r="BZ103" s="91"/>
-      <c r="CA103" s="92"/>
-      <c r="CB103" s="93"/>
-      <c r="CC103" s="90"/>
-      <c r="CD103" s="91"/>
-      <c r="CE103" s="91"/>
-      <c r="CF103" s="91"/>
-      <c r="CG103" s="91"/>
-      <c r="CH103" s="92"/>
-      <c r="CI103" s="94"/>
-      <c r="CJ103" s="95"/>
-      <c r="CK103" s="91"/>
-      <c r="CL103" s="91"/>
-      <c r="CM103" s="91"/>
-      <c r="CN103" s="91"/>
-      <c r="CO103" s="92"/>
-      <c r="CP103" s="93"/>
-      <c r="CQ103" s="90"/>
-      <c r="CR103" s="91"/>
-      <c r="CS103" s="91"/>
-      <c r="CT103" s="91"/>
-      <c r="CU103" s="91"/>
-      <c r="CV103" s="92"/>
-      <c r="CW103" s="93"/>
-      <c r="CX103" s="90"/>
-      <c r="CY103" s="91"/>
-      <c r="CZ103" s="91"/>
-      <c r="DA103" s="91"/>
-      <c r="DB103" s="91"/>
-      <c r="DC103" s="92"/>
-      <c r="DD103" s="93"/>
-      <c r="DE103" s="90"/>
-      <c r="DF103" s="91"/>
     </row>
     <row r="104" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="102"/>
@@ -15534,45 +11767,6 @@
       <c r="BQ104" s="110"/>
       <c r="BR104" s="110"/>
       <c r="BS104" s="110"/>
-      <c r="BT104" s="111"/>
-      <c r="BU104" s="112"/>
-      <c r="BV104" s="109"/>
-      <c r="BW104" s="110"/>
-      <c r="BX104" s="110"/>
-      <c r="BY104" s="110"/>
-      <c r="BZ104" s="110"/>
-      <c r="CA104" s="111"/>
-      <c r="CB104" s="112"/>
-      <c r="CC104" s="109"/>
-      <c r="CD104" s="110"/>
-      <c r="CE104" s="110"/>
-      <c r="CF104" s="110"/>
-      <c r="CG104" s="110"/>
-      <c r="CH104" s="111"/>
-      <c r="CI104" s="113"/>
-      <c r="CJ104" s="114"/>
-      <c r="CK104" s="110"/>
-      <c r="CL104" s="110"/>
-      <c r="CM104" s="110"/>
-      <c r="CN104" s="110"/>
-      <c r="CO104" s="111"/>
-      <c r="CP104" s="112"/>
-      <c r="CQ104" s="109"/>
-      <c r="CR104" s="110"/>
-      <c r="CS104" s="110"/>
-      <c r="CT104" s="110"/>
-      <c r="CU104" s="110"/>
-      <c r="CV104" s="111"/>
-      <c r="CW104" s="112"/>
-      <c r="CX104" s="109"/>
-      <c r="CY104" s="110"/>
-      <c r="CZ104" s="110"/>
-      <c r="DA104" s="110"/>
-      <c r="DB104" s="110"/>
-      <c r="DC104" s="111"/>
-      <c r="DD104" s="112"/>
-      <c r="DE104" s="109"/>
-      <c r="DF104" s="110"/>
     </row>
     <row r="105" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="83"/>
@@ -15646,45 +11840,6 @@
       <c r="BQ105" s="91"/>
       <c r="BR105" s="91"/>
       <c r="BS105" s="91"/>
-      <c r="BT105" s="92"/>
-      <c r="BU105" s="93"/>
-      <c r="BV105" s="90"/>
-      <c r="BW105" s="91"/>
-      <c r="BX105" s="91"/>
-      <c r="BY105" s="91"/>
-      <c r="BZ105" s="91"/>
-      <c r="CA105" s="92"/>
-      <c r="CB105" s="93"/>
-      <c r="CC105" s="90"/>
-      <c r="CD105" s="91"/>
-      <c r="CE105" s="91"/>
-      <c r="CF105" s="91"/>
-      <c r="CG105" s="91"/>
-      <c r="CH105" s="92"/>
-      <c r="CI105" s="94"/>
-      <c r="CJ105" s="95"/>
-      <c r="CK105" s="91"/>
-      <c r="CL105" s="91"/>
-      <c r="CM105" s="91"/>
-      <c r="CN105" s="91"/>
-      <c r="CO105" s="92"/>
-      <c r="CP105" s="93"/>
-      <c r="CQ105" s="90"/>
-      <c r="CR105" s="91"/>
-      <c r="CS105" s="91"/>
-      <c r="CT105" s="91"/>
-      <c r="CU105" s="91"/>
-      <c r="CV105" s="92"/>
-      <c r="CW105" s="93"/>
-      <c r="CX105" s="90"/>
-      <c r="CY105" s="91"/>
-      <c r="CZ105" s="91"/>
-      <c r="DA105" s="91"/>
-      <c r="DB105" s="91"/>
-      <c r="DC105" s="92"/>
-      <c r="DD105" s="93"/>
-      <c r="DE105" s="90"/>
-      <c r="DF105" s="91"/>
     </row>
     <row r="106" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="83"/>
@@ -15758,45 +11913,6 @@
       <c r="BQ106" s="91"/>
       <c r="BR106" s="91"/>
       <c r="BS106" s="91"/>
-      <c r="BT106" s="92"/>
-      <c r="BU106" s="93"/>
-      <c r="BV106" s="90"/>
-      <c r="BW106" s="91"/>
-      <c r="BX106" s="91"/>
-      <c r="BY106" s="91"/>
-      <c r="BZ106" s="91"/>
-      <c r="CA106" s="92"/>
-      <c r="CB106" s="93"/>
-      <c r="CC106" s="90"/>
-      <c r="CD106" s="91"/>
-      <c r="CE106" s="91"/>
-      <c r="CF106" s="91"/>
-      <c r="CG106" s="91"/>
-      <c r="CH106" s="92"/>
-      <c r="CI106" s="94"/>
-      <c r="CJ106" s="95"/>
-      <c r="CK106" s="91"/>
-      <c r="CL106" s="91"/>
-      <c r="CM106" s="91"/>
-      <c r="CN106" s="91"/>
-      <c r="CO106" s="92"/>
-      <c r="CP106" s="93"/>
-      <c r="CQ106" s="90"/>
-      <c r="CR106" s="91"/>
-      <c r="CS106" s="91"/>
-      <c r="CT106" s="91"/>
-      <c r="CU106" s="91"/>
-      <c r="CV106" s="92"/>
-      <c r="CW106" s="93"/>
-      <c r="CX106" s="90"/>
-      <c r="CY106" s="91"/>
-      <c r="CZ106" s="91"/>
-      <c r="DA106" s="91"/>
-      <c r="DB106" s="91"/>
-      <c r="DC106" s="92"/>
-      <c r="DD106" s="93"/>
-      <c r="DE106" s="90"/>
-      <c r="DF106" s="91"/>
     </row>
     <row r="107" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="96"/>
@@ -15870,45 +11986,6 @@
       <c r="BQ107" s="91"/>
       <c r="BR107" s="91"/>
       <c r="BS107" s="91"/>
-      <c r="BT107" s="92"/>
-      <c r="BU107" s="93"/>
-      <c r="BV107" s="90"/>
-      <c r="BW107" s="91"/>
-      <c r="BX107" s="91"/>
-      <c r="BY107" s="91"/>
-      <c r="BZ107" s="91"/>
-      <c r="CA107" s="92"/>
-      <c r="CB107" s="93"/>
-      <c r="CC107" s="90"/>
-      <c r="CD107" s="91"/>
-      <c r="CE107" s="91"/>
-      <c r="CF107" s="91"/>
-      <c r="CG107" s="91"/>
-      <c r="CH107" s="92"/>
-      <c r="CI107" s="94"/>
-      <c r="CJ107" s="95"/>
-      <c r="CK107" s="91"/>
-      <c r="CL107" s="91"/>
-      <c r="CM107" s="91"/>
-      <c r="CN107" s="91"/>
-      <c r="CO107" s="92"/>
-      <c r="CP107" s="93"/>
-      <c r="CQ107" s="90"/>
-      <c r="CR107" s="91"/>
-      <c r="CS107" s="91"/>
-      <c r="CT107" s="91"/>
-      <c r="CU107" s="91"/>
-      <c r="CV107" s="92"/>
-      <c r="CW107" s="93"/>
-      <c r="CX107" s="90"/>
-      <c r="CY107" s="91"/>
-      <c r="CZ107" s="91"/>
-      <c r="DA107" s="91"/>
-      <c r="DB107" s="91"/>
-      <c r="DC107" s="92"/>
-      <c r="DD107" s="93"/>
-      <c r="DE107" s="90"/>
-      <c r="DF107" s="91"/>
     </row>
     <row r="108" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="96"/>
@@ -15982,45 +12059,6 @@
       <c r="BQ108" s="91"/>
       <c r="BR108" s="91"/>
       <c r="BS108" s="91"/>
-      <c r="BT108" s="92"/>
-      <c r="BU108" s="93"/>
-      <c r="BV108" s="90"/>
-      <c r="BW108" s="91"/>
-      <c r="BX108" s="91"/>
-      <c r="BY108" s="91"/>
-      <c r="BZ108" s="91"/>
-      <c r="CA108" s="92"/>
-      <c r="CB108" s="93"/>
-      <c r="CC108" s="90"/>
-      <c r="CD108" s="91"/>
-      <c r="CE108" s="91"/>
-      <c r="CF108" s="91"/>
-      <c r="CG108" s="91"/>
-      <c r="CH108" s="92"/>
-      <c r="CI108" s="94"/>
-      <c r="CJ108" s="95"/>
-      <c r="CK108" s="91"/>
-      <c r="CL108" s="91"/>
-      <c r="CM108" s="91"/>
-      <c r="CN108" s="91"/>
-      <c r="CO108" s="92"/>
-      <c r="CP108" s="93"/>
-      <c r="CQ108" s="90"/>
-      <c r="CR108" s="91"/>
-      <c r="CS108" s="91"/>
-      <c r="CT108" s="91"/>
-      <c r="CU108" s="91"/>
-      <c r="CV108" s="92"/>
-      <c r="CW108" s="93"/>
-      <c r="CX108" s="90"/>
-      <c r="CY108" s="91"/>
-      <c r="CZ108" s="91"/>
-      <c r="DA108" s="91"/>
-      <c r="DB108" s="91"/>
-      <c r="DC108" s="92"/>
-      <c r="DD108" s="93"/>
-      <c r="DE108" s="90"/>
-      <c r="DF108" s="91"/>
     </row>
     <row r="109" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="96"/>
@@ -16094,45 +12132,6 @@
       <c r="BQ109" s="91"/>
       <c r="BR109" s="91"/>
       <c r="BS109" s="91"/>
-      <c r="BT109" s="92"/>
-      <c r="BU109" s="93"/>
-      <c r="BV109" s="90"/>
-      <c r="BW109" s="91"/>
-      <c r="BX109" s="91"/>
-      <c r="BY109" s="91"/>
-      <c r="BZ109" s="91"/>
-      <c r="CA109" s="92"/>
-      <c r="CB109" s="93"/>
-      <c r="CC109" s="90"/>
-      <c r="CD109" s="91"/>
-      <c r="CE109" s="91"/>
-      <c r="CF109" s="91"/>
-      <c r="CG109" s="91"/>
-      <c r="CH109" s="92"/>
-      <c r="CI109" s="94"/>
-      <c r="CJ109" s="95"/>
-      <c r="CK109" s="91"/>
-      <c r="CL109" s="91"/>
-      <c r="CM109" s="91"/>
-      <c r="CN109" s="91"/>
-      <c r="CO109" s="92"/>
-      <c r="CP109" s="93"/>
-      <c r="CQ109" s="90"/>
-      <c r="CR109" s="91"/>
-      <c r="CS109" s="91"/>
-      <c r="CT109" s="91"/>
-      <c r="CU109" s="91"/>
-      <c r="CV109" s="92"/>
-      <c r="CW109" s="93"/>
-      <c r="CX109" s="90"/>
-      <c r="CY109" s="91"/>
-      <c r="CZ109" s="91"/>
-      <c r="DA109" s="91"/>
-      <c r="DB109" s="91"/>
-      <c r="DC109" s="92"/>
-      <c r="DD109" s="93"/>
-      <c r="DE109" s="90"/>
-      <c r="DF109" s="91"/>
     </row>
     <row r="110" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="96"/>
@@ -16206,45 +12205,6 @@
       <c r="BQ110" s="91"/>
       <c r="BR110" s="91"/>
       <c r="BS110" s="91"/>
-      <c r="BT110" s="92"/>
-      <c r="BU110" s="93"/>
-      <c r="BV110" s="90"/>
-      <c r="BW110" s="91"/>
-      <c r="BX110" s="91"/>
-      <c r="BY110" s="91"/>
-      <c r="BZ110" s="91"/>
-      <c r="CA110" s="92"/>
-      <c r="CB110" s="93"/>
-      <c r="CC110" s="90"/>
-      <c r="CD110" s="91"/>
-      <c r="CE110" s="91"/>
-      <c r="CF110" s="91"/>
-      <c r="CG110" s="91"/>
-      <c r="CH110" s="92"/>
-      <c r="CI110" s="94"/>
-      <c r="CJ110" s="95"/>
-      <c r="CK110" s="91"/>
-      <c r="CL110" s="91"/>
-      <c r="CM110" s="91"/>
-      <c r="CN110" s="91"/>
-      <c r="CO110" s="92"/>
-      <c r="CP110" s="93"/>
-      <c r="CQ110" s="90"/>
-      <c r="CR110" s="91"/>
-      <c r="CS110" s="91"/>
-      <c r="CT110" s="91"/>
-      <c r="CU110" s="91"/>
-      <c r="CV110" s="92"/>
-      <c r="CW110" s="93"/>
-      <c r="CX110" s="90"/>
-      <c r="CY110" s="91"/>
-      <c r="CZ110" s="91"/>
-      <c r="DA110" s="91"/>
-      <c r="DB110" s="91"/>
-      <c r="DC110" s="92"/>
-      <c r="DD110" s="93"/>
-      <c r="DE110" s="90"/>
-      <c r="DF110" s="91"/>
     </row>
     <row r="111" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="83"/>
@@ -16318,45 +12278,6 @@
       <c r="BQ111" s="91"/>
       <c r="BR111" s="91"/>
       <c r="BS111" s="91"/>
-      <c r="BT111" s="92"/>
-      <c r="BU111" s="93"/>
-      <c r="BV111" s="90"/>
-      <c r="BW111" s="91"/>
-      <c r="BX111" s="91"/>
-      <c r="BY111" s="91"/>
-      <c r="BZ111" s="91"/>
-      <c r="CA111" s="92"/>
-      <c r="CB111" s="93"/>
-      <c r="CC111" s="90"/>
-      <c r="CD111" s="91"/>
-      <c r="CE111" s="91"/>
-      <c r="CF111" s="91"/>
-      <c r="CG111" s="91"/>
-      <c r="CH111" s="92"/>
-      <c r="CI111" s="94"/>
-      <c r="CJ111" s="95"/>
-      <c r="CK111" s="91"/>
-      <c r="CL111" s="91"/>
-      <c r="CM111" s="91"/>
-      <c r="CN111" s="91"/>
-      <c r="CO111" s="92"/>
-      <c r="CP111" s="93"/>
-      <c r="CQ111" s="90"/>
-      <c r="CR111" s="91"/>
-      <c r="CS111" s="91"/>
-      <c r="CT111" s="91"/>
-      <c r="CU111" s="91"/>
-      <c r="CV111" s="92"/>
-      <c r="CW111" s="93"/>
-      <c r="CX111" s="90"/>
-      <c r="CY111" s="91"/>
-      <c r="CZ111" s="91"/>
-      <c r="DA111" s="91"/>
-      <c r="DB111" s="91"/>
-      <c r="DC111" s="92"/>
-      <c r="DD111" s="93"/>
-      <c r="DE111" s="90"/>
-      <c r="DF111" s="91"/>
     </row>
     <row r="112" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="96"/>
@@ -16430,45 +12351,6 @@
       <c r="BQ112" s="91"/>
       <c r="BR112" s="91"/>
       <c r="BS112" s="91"/>
-      <c r="BT112" s="92"/>
-      <c r="BU112" s="93"/>
-      <c r="BV112" s="90"/>
-      <c r="BW112" s="91"/>
-      <c r="BX112" s="91"/>
-      <c r="BY112" s="91"/>
-      <c r="BZ112" s="91"/>
-      <c r="CA112" s="92"/>
-      <c r="CB112" s="93"/>
-      <c r="CC112" s="90"/>
-      <c r="CD112" s="91"/>
-      <c r="CE112" s="91"/>
-      <c r="CF112" s="91"/>
-      <c r="CG112" s="91"/>
-      <c r="CH112" s="92"/>
-      <c r="CI112" s="94"/>
-      <c r="CJ112" s="95"/>
-      <c r="CK112" s="91"/>
-      <c r="CL112" s="91"/>
-      <c r="CM112" s="91"/>
-      <c r="CN112" s="91"/>
-      <c r="CO112" s="92"/>
-      <c r="CP112" s="93"/>
-      <c r="CQ112" s="90"/>
-      <c r="CR112" s="91"/>
-      <c r="CS112" s="91"/>
-      <c r="CT112" s="91"/>
-      <c r="CU112" s="91"/>
-      <c r="CV112" s="92"/>
-      <c r="CW112" s="93"/>
-      <c r="CX112" s="90"/>
-      <c r="CY112" s="91"/>
-      <c r="CZ112" s="91"/>
-      <c r="DA112" s="91"/>
-      <c r="DB112" s="91"/>
-      <c r="DC112" s="92"/>
-      <c r="DD112" s="93"/>
-      <c r="DE112" s="90"/>
-      <c r="DF112" s="91"/>
     </row>
     <row r="113" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="96"/>
@@ -16542,45 +12424,6 @@
       <c r="BQ113" s="91"/>
       <c r="BR113" s="91"/>
       <c r="BS113" s="91"/>
-      <c r="BT113" s="92"/>
-      <c r="BU113" s="93"/>
-      <c r="BV113" s="90"/>
-      <c r="BW113" s="91"/>
-      <c r="BX113" s="91"/>
-      <c r="BY113" s="91"/>
-      <c r="BZ113" s="91"/>
-      <c r="CA113" s="92"/>
-      <c r="CB113" s="93"/>
-      <c r="CC113" s="90"/>
-      <c r="CD113" s="91"/>
-      <c r="CE113" s="91"/>
-      <c r="CF113" s="91"/>
-      <c r="CG113" s="91"/>
-      <c r="CH113" s="92"/>
-      <c r="CI113" s="94"/>
-      <c r="CJ113" s="95"/>
-      <c r="CK113" s="91"/>
-      <c r="CL113" s="91"/>
-      <c r="CM113" s="91"/>
-      <c r="CN113" s="91"/>
-      <c r="CO113" s="92"/>
-      <c r="CP113" s="93"/>
-      <c r="CQ113" s="90"/>
-      <c r="CR113" s="91"/>
-      <c r="CS113" s="91"/>
-      <c r="CT113" s="91"/>
-      <c r="CU113" s="91"/>
-      <c r="CV113" s="92"/>
-      <c r="CW113" s="93"/>
-      <c r="CX113" s="90"/>
-      <c r="CY113" s="91"/>
-      <c r="CZ113" s="91"/>
-      <c r="DA113" s="91"/>
-      <c r="DB113" s="91"/>
-      <c r="DC113" s="92"/>
-      <c r="DD113" s="93"/>
-      <c r="DE113" s="90"/>
-      <c r="DF113" s="91"/>
     </row>
     <row r="114" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="96"/>
@@ -16654,45 +12497,6 @@
       <c r="BQ114" s="91"/>
       <c r="BR114" s="91"/>
       <c r="BS114" s="91"/>
-      <c r="BT114" s="92"/>
-      <c r="BU114" s="93"/>
-      <c r="BV114" s="90"/>
-      <c r="BW114" s="91"/>
-      <c r="BX114" s="91"/>
-      <c r="BY114" s="91"/>
-      <c r="BZ114" s="91"/>
-      <c r="CA114" s="92"/>
-      <c r="CB114" s="93"/>
-      <c r="CC114" s="90"/>
-      <c r="CD114" s="91"/>
-      <c r="CE114" s="91"/>
-      <c r="CF114" s="91"/>
-      <c r="CG114" s="91"/>
-      <c r="CH114" s="92"/>
-      <c r="CI114" s="94"/>
-      <c r="CJ114" s="95"/>
-      <c r="CK114" s="91"/>
-      <c r="CL114" s="91"/>
-      <c r="CM114" s="91"/>
-      <c r="CN114" s="91"/>
-      <c r="CO114" s="92"/>
-      <c r="CP114" s="93"/>
-      <c r="CQ114" s="90"/>
-      <c r="CR114" s="91"/>
-      <c r="CS114" s="91"/>
-      <c r="CT114" s="91"/>
-      <c r="CU114" s="91"/>
-      <c r="CV114" s="92"/>
-      <c r="CW114" s="93"/>
-      <c r="CX114" s="90"/>
-      <c r="CY114" s="91"/>
-      <c r="CZ114" s="91"/>
-      <c r="DA114" s="91"/>
-      <c r="DB114" s="91"/>
-      <c r="DC114" s="92"/>
-      <c r="DD114" s="93"/>
-      <c r="DE114" s="90"/>
-      <c r="DF114" s="91"/>
     </row>
     <row r="115" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="96"/>
@@ -16766,45 +12570,6 @@
       <c r="BQ115" s="91"/>
       <c r="BR115" s="91"/>
       <c r="BS115" s="91"/>
-      <c r="BT115" s="92"/>
-      <c r="BU115" s="93"/>
-      <c r="BV115" s="90"/>
-      <c r="BW115" s="91"/>
-      <c r="BX115" s="91"/>
-      <c r="BY115" s="91"/>
-      <c r="BZ115" s="91"/>
-      <c r="CA115" s="92"/>
-      <c r="CB115" s="93"/>
-      <c r="CC115" s="90"/>
-      <c r="CD115" s="91"/>
-      <c r="CE115" s="91"/>
-      <c r="CF115" s="91"/>
-      <c r="CG115" s="91"/>
-      <c r="CH115" s="92"/>
-      <c r="CI115" s="94"/>
-      <c r="CJ115" s="95"/>
-      <c r="CK115" s="91"/>
-      <c r="CL115" s="91"/>
-      <c r="CM115" s="91"/>
-      <c r="CN115" s="91"/>
-      <c r="CO115" s="92"/>
-      <c r="CP115" s="93"/>
-      <c r="CQ115" s="90"/>
-      <c r="CR115" s="91"/>
-      <c r="CS115" s="91"/>
-      <c r="CT115" s="91"/>
-      <c r="CU115" s="91"/>
-      <c r="CV115" s="92"/>
-      <c r="CW115" s="93"/>
-      <c r="CX115" s="90"/>
-      <c r="CY115" s="91"/>
-      <c r="CZ115" s="91"/>
-      <c r="DA115" s="91"/>
-      <c r="DB115" s="91"/>
-      <c r="DC115" s="92"/>
-      <c r="DD115" s="93"/>
-      <c r="DE115" s="90"/>
-      <c r="DF115" s="91"/>
     </row>
     <row r="116" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="96"/>
@@ -16878,45 +12643,6 @@
       <c r="BQ116" s="91"/>
       <c r="BR116" s="91"/>
       <c r="BS116" s="91"/>
-      <c r="BT116" s="92"/>
-      <c r="BU116" s="93"/>
-      <c r="BV116" s="90"/>
-      <c r="BW116" s="91"/>
-      <c r="BX116" s="91"/>
-      <c r="BY116" s="91"/>
-      <c r="BZ116" s="91"/>
-      <c r="CA116" s="92"/>
-      <c r="CB116" s="93"/>
-      <c r="CC116" s="90"/>
-      <c r="CD116" s="91"/>
-      <c r="CE116" s="91"/>
-      <c r="CF116" s="91"/>
-      <c r="CG116" s="91"/>
-      <c r="CH116" s="92"/>
-      <c r="CI116" s="94"/>
-      <c r="CJ116" s="95"/>
-      <c r="CK116" s="91"/>
-      <c r="CL116" s="91"/>
-      <c r="CM116" s="91"/>
-      <c r="CN116" s="91"/>
-      <c r="CO116" s="92"/>
-      <c r="CP116" s="93"/>
-      <c r="CQ116" s="90"/>
-      <c r="CR116" s="91"/>
-      <c r="CS116" s="91"/>
-      <c r="CT116" s="116"/>
-      <c r="CU116" s="91"/>
-      <c r="CV116" s="92"/>
-      <c r="CW116" s="93"/>
-      <c r="CX116" s="90"/>
-      <c r="CY116" s="91"/>
-      <c r="CZ116" s="91"/>
-      <c r="DA116" s="91"/>
-      <c r="DB116" s="91"/>
-      <c r="DC116" s="92"/>
-      <c r="DD116" s="93"/>
-      <c r="DE116" s="90"/>
-      <c r="DF116" s="91"/>
     </row>
     <row r="117" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="83"/>
@@ -16990,45 +12716,6 @@
       <c r="BQ117" s="91"/>
       <c r="BR117" s="91"/>
       <c r="BS117" s="91"/>
-      <c r="BT117" s="92"/>
-      <c r="BU117" s="93"/>
-      <c r="BV117" s="90"/>
-      <c r="BW117" s="91"/>
-      <c r="BX117" s="91"/>
-      <c r="BY117" s="91"/>
-      <c r="BZ117" s="91"/>
-      <c r="CA117" s="92"/>
-      <c r="CB117" s="93"/>
-      <c r="CC117" s="90"/>
-      <c r="CD117" s="91"/>
-      <c r="CE117" s="91"/>
-      <c r="CF117" s="91"/>
-      <c r="CG117" s="91"/>
-      <c r="CH117" s="92"/>
-      <c r="CI117" s="94"/>
-      <c r="CJ117" s="95"/>
-      <c r="CK117" s="91"/>
-      <c r="CL117" s="91"/>
-      <c r="CM117" s="91"/>
-      <c r="CN117" s="91"/>
-      <c r="CO117" s="92"/>
-      <c r="CP117" s="93"/>
-      <c r="CQ117" s="90"/>
-      <c r="CR117" s="91"/>
-      <c r="CS117" s="91"/>
-      <c r="CT117" s="91"/>
-      <c r="CU117" s="91"/>
-      <c r="CV117" s="92"/>
-      <c r="CW117" s="93"/>
-      <c r="CX117" s="90"/>
-      <c r="CY117" s="91"/>
-      <c r="CZ117" s="91"/>
-      <c r="DA117" s="91"/>
-      <c r="DB117" s="91"/>
-      <c r="DC117" s="92"/>
-      <c r="DD117" s="93"/>
-      <c r="DE117" s="90"/>
-      <c r="DF117" s="91"/>
     </row>
     <row r="118" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="96"/>
@@ -17102,45 +12789,6 @@
       <c r="BQ118" s="91"/>
       <c r="BR118" s="91"/>
       <c r="BS118" s="91"/>
-      <c r="BT118" s="92"/>
-      <c r="BU118" s="93"/>
-      <c r="BV118" s="90"/>
-      <c r="BW118" s="91"/>
-      <c r="BX118" s="91"/>
-      <c r="BY118" s="91"/>
-      <c r="BZ118" s="91"/>
-      <c r="CA118" s="92"/>
-      <c r="CB118" s="93"/>
-      <c r="CC118" s="90"/>
-      <c r="CD118" s="91"/>
-      <c r="CE118" s="91"/>
-      <c r="CF118" s="91"/>
-      <c r="CG118" s="91"/>
-      <c r="CH118" s="92"/>
-      <c r="CI118" s="94"/>
-      <c r="CJ118" s="95"/>
-      <c r="CK118" s="91"/>
-      <c r="CL118" s="91"/>
-      <c r="CM118" s="91"/>
-      <c r="CN118" s="91"/>
-      <c r="CO118" s="92"/>
-      <c r="CP118" s="93"/>
-      <c r="CQ118" s="90"/>
-      <c r="CR118" s="91"/>
-      <c r="CS118" s="91"/>
-      <c r="CT118" s="91"/>
-      <c r="CU118" s="91"/>
-      <c r="CV118" s="92"/>
-      <c r="CW118" s="93"/>
-      <c r="CX118" s="90"/>
-      <c r="CY118" s="91"/>
-      <c r="CZ118" s="91"/>
-      <c r="DA118" s="91"/>
-      <c r="DB118" s="91"/>
-      <c r="DC118" s="92"/>
-      <c r="DD118" s="93"/>
-      <c r="DE118" s="90"/>
-      <c r="DF118" s="91"/>
     </row>
     <row r="119" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="96"/>
@@ -17214,45 +12862,6 @@
       <c r="BQ119" s="91"/>
       <c r="BR119" s="91"/>
       <c r="BS119" s="91"/>
-      <c r="BT119" s="92"/>
-      <c r="BU119" s="93"/>
-      <c r="BV119" s="90"/>
-      <c r="BW119" s="91"/>
-      <c r="BX119" s="91"/>
-      <c r="BY119" s="91"/>
-      <c r="BZ119" s="91"/>
-      <c r="CA119" s="92"/>
-      <c r="CB119" s="93"/>
-      <c r="CC119" s="90"/>
-      <c r="CD119" s="91"/>
-      <c r="CE119" s="91"/>
-      <c r="CF119" s="91"/>
-      <c r="CG119" s="91"/>
-      <c r="CH119" s="92"/>
-      <c r="CI119" s="94"/>
-      <c r="CJ119" s="95"/>
-      <c r="CK119" s="91"/>
-      <c r="CL119" s="91"/>
-      <c r="CM119" s="91"/>
-      <c r="CN119" s="91"/>
-      <c r="CO119" s="92"/>
-      <c r="CP119" s="93"/>
-      <c r="CQ119" s="90"/>
-      <c r="CR119" s="91"/>
-      <c r="CS119" s="91"/>
-      <c r="CT119" s="91"/>
-      <c r="CU119" s="91"/>
-      <c r="CV119" s="92"/>
-      <c r="CW119" s="93"/>
-      <c r="CX119" s="90"/>
-      <c r="CY119" s="91"/>
-      <c r="CZ119" s="91"/>
-      <c r="DA119" s="91"/>
-      <c r="DB119" s="91"/>
-      <c r="DC119" s="92"/>
-      <c r="DD119" s="93"/>
-      <c r="DE119" s="90"/>
-      <c r="DF119" s="91"/>
     </row>
     <row r="120" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="102"/>
@@ -17326,45 +12935,6 @@
       <c r="BQ120" s="110"/>
       <c r="BR120" s="110"/>
       <c r="BS120" s="110"/>
-      <c r="BT120" s="111"/>
-      <c r="BU120" s="112"/>
-      <c r="BV120" s="109"/>
-      <c r="BW120" s="110"/>
-      <c r="BX120" s="110"/>
-      <c r="BY120" s="110"/>
-      <c r="BZ120" s="110"/>
-      <c r="CA120" s="111"/>
-      <c r="CB120" s="112"/>
-      <c r="CC120" s="109"/>
-      <c r="CD120" s="110"/>
-      <c r="CE120" s="110"/>
-      <c r="CF120" s="110"/>
-      <c r="CG120" s="110"/>
-      <c r="CH120" s="111"/>
-      <c r="CI120" s="113"/>
-      <c r="CJ120" s="114"/>
-      <c r="CK120" s="110"/>
-      <c r="CL120" s="110"/>
-      <c r="CM120" s="110"/>
-      <c r="CN120" s="110"/>
-      <c r="CO120" s="111"/>
-      <c r="CP120" s="112"/>
-      <c r="CQ120" s="109"/>
-      <c r="CR120" s="110"/>
-      <c r="CS120" s="110"/>
-      <c r="CT120" s="110"/>
-      <c r="CU120" s="110"/>
-      <c r="CV120" s="111"/>
-      <c r="CW120" s="112"/>
-      <c r="CX120" s="109"/>
-      <c r="CY120" s="110"/>
-      <c r="CZ120" s="110"/>
-      <c r="DA120" s="110"/>
-      <c r="DB120" s="110"/>
-      <c r="DC120" s="111"/>
-      <c r="DD120" s="112"/>
-      <c r="DE120" s="109"/>
-      <c r="DF120" s="110"/>
     </row>
     <row r="121" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="83"/>
@@ -17438,45 +13008,6 @@
       <c r="BQ121" s="91"/>
       <c r="BR121" s="91"/>
       <c r="BS121" s="91"/>
-      <c r="BT121" s="92"/>
-      <c r="BU121" s="93"/>
-      <c r="BV121" s="90"/>
-      <c r="BW121" s="91"/>
-      <c r="BX121" s="91"/>
-      <c r="BY121" s="91"/>
-      <c r="BZ121" s="91"/>
-      <c r="CA121" s="92"/>
-      <c r="CB121" s="93"/>
-      <c r="CC121" s="90"/>
-      <c r="CD121" s="91"/>
-      <c r="CE121" s="91"/>
-      <c r="CF121" s="91"/>
-      <c r="CG121" s="91"/>
-      <c r="CH121" s="92"/>
-      <c r="CI121" s="94"/>
-      <c r="CJ121" s="95"/>
-      <c r="CK121" s="91"/>
-      <c r="CL121" s="91"/>
-      <c r="CM121" s="91"/>
-      <c r="CN121" s="91"/>
-      <c r="CO121" s="92"/>
-      <c r="CP121" s="93"/>
-      <c r="CQ121" s="90"/>
-      <c r="CR121" s="91"/>
-      <c r="CS121" s="91"/>
-      <c r="CT121" s="91"/>
-      <c r="CU121" s="91"/>
-      <c r="CV121" s="92"/>
-      <c r="CW121" s="93"/>
-      <c r="CX121" s="90"/>
-      <c r="CY121" s="91"/>
-      <c r="CZ121" s="91"/>
-      <c r="DA121" s="91"/>
-      <c r="DB121" s="91"/>
-      <c r="DC121" s="92"/>
-      <c r="DD121" s="93"/>
-      <c r="DE121" s="90"/>
-      <c r="DF121" s="91"/>
     </row>
     <row r="122" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="83"/>
@@ -17550,45 +13081,6 @@
       <c r="BQ122" s="91"/>
       <c r="BR122" s="91"/>
       <c r="BS122" s="91"/>
-      <c r="BT122" s="92"/>
-      <c r="BU122" s="93"/>
-      <c r="BV122" s="90"/>
-      <c r="BW122" s="91"/>
-      <c r="BX122" s="91"/>
-      <c r="BY122" s="91"/>
-      <c r="BZ122" s="91"/>
-      <c r="CA122" s="92"/>
-      <c r="CB122" s="93"/>
-      <c r="CC122" s="90"/>
-      <c r="CD122" s="91"/>
-      <c r="CE122" s="91"/>
-      <c r="CF122" s="91"/>
-      <c r="CG122" s="91"/>
-      <c r="CH122" s="92"/>
-      <c r="CI122" s="94"/>
-      <c r="CJ122" s="95"/>
-      <c r="CK122" s="91"/>
-      <c r="CL122" s="91"/>
-      <c r="CM122" s="91"/>
-      <c r="CN122" s="91"/>
-      <c r="CO122" s="92"/>
-      <c r="CP122" s="93"/>
-      <c r="CQ122" s="90"/>
-      <c r="CR122" s="91"/>
-      <c r="CS122" s="91"/>
-      <c r="CT122" s="91"/>
-      <c r="CU122" s="91"/>
-      <c r="CV122" s="92"/>
-      <c r="CW122" s="93"/>
-      <c r="CX122" s="90"/>
-      <c r="CY122" s="91"/>
-      <c r="CZ122" s="91"/>
-      <c r="DA122" s="91"/>
-      <c r="DB122" s="91"/>
-      <c r="DC122" s="92"/>
-      <c r="DD122" s="93"/>
-      <c r="DE122" s="90"/>
-      <c r="DF122" s="91"/>
     </row>
     <row r="123" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="96"/>
@@ -17662,45 +13154,6 @@
       <c r="BQ123" s="91"/>
       <c r="BR123" s="91"/>
       <c r="BS123" s="91"/>
-      <c r="BT123" s="92"/>
-      <c r="BU123" s="93"/>
-      <c r="BV123" s="90"/>
-      <c r="BW123" s="91"/>
-      <c r="BX123" s="91"/>
-      <c r="BY123" s="91"/>
-      <c r="BZ123" s="91"/>
-      <c r="CA123" s="92"/>
-      <c r="CB123" s="93"/>
-      <c r="CC123" s="90"/>
-      <c r="CD123" s="91"/>
-      <c r="CE123" s="91"/>
-      <c r="CF123" s="91"/>
-      <c r="CG123" s="91"/>
-      <c r="CH123" s="92"/>
-      <c r="CI123" s="94"/>
-      <c r="CJ123" s="95"/>
-      <c r="CK123" s="91"/>
-      <c r="CL123" s="91"/>
-      <c r="CM123" s="91"/>
-      <c r="CN123" s="91"/>
-      <c r="CO123" s="92"/>
-      <c r="CP123" s="93"/>
-      <c r="CQ123" s="90"/>
-      <c r="CR123" s="91"/>
-      <c r="CS123" s="91"/>
-      <c r="CT123" s="91"/>
-      <c r="CU123" s="91"/>
-      <c r="CV123" s="92"/>
-      <c r="CW123" s="93"/>
-      <c r="CX123" s="90"/>
-      <c r="CY123" s="91"/>
-      <c r="CZ123" s="91"/>
-      <c r="DA123" s="91"/>
-      <c r="DB123" s="91"/>
-      <c r="DC123" s="92"/>
-      <c r="DD123" s="93"/>
-      <c r="DE123" s="90"/>
-      <c r="DF123" s="91"/>
     </row>
     <row r="124" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="96"/>
@@ -17774,45 +13227,6 @@
       <c r="BQ124" s="91"/>
       <c r="BR124" s="91"/>
       <c r="BS124" s="91"/>
-      <c r="BT124" s="92"/>
-      <c r="BU124" s="93"/>
-      <c r="BV124" s="90"/>
-      <c r="BW124" s="91"/>
-      <c r="BX124" s="91"/>
-      <c r="BY124" s="91"/>
-      <c r="BZ124" s="91"/>
-      <c r="CA124" s="92"/>
-      <c r="CB124" s="93"/>
-      <c r="CC124" s="90"/>
-      <c r="CD124" s="91"/>
-      <c r="CE124" s="91"/>
-      <c r="CF124" s="91"/>
-      <c r="CG124" s="91"/>
-      <c r="CH124" s="92"/>
-      <c r="CI124" s="94"/>
-      <c r="CJ124" s="95"/>
-      <c r="CK124" s="91"/>
-      <c r="CL124" s="91"/>
-      <c r="CM124" s="91"/>
-      <c r="CN124" s="91"/>
-      <c r="CO124" s="92"/>
-      <c r="CP124" s="93"/>
-      <c r="CQ124" s="90"/>
-      <c r="CR124" s="91"/>
-      <c r="CS124" s="91"/>
-      <c r="CT124" s="91"/>
-      <c r="CU124" s="91"/>
-      <c r="CV124" s="92"/>
-      <c r="CW124" s="93"/>
-      <c r="CX124" s="90"/>
-      <c r="CY124" s="91"/>
-      <c r="CZ124" s="91"/>
-      <c r="DA124" s="91"/>
-      <c r="DB124" s="91"/>
-      <c r="DC124" s="92"/>
-      <c r="DD124" s="93"/>
-      <c r="DE124" s="90"/>
-      <c r="DF124" s="91"/>
     </row>
     <row r="125" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="83"/>
@@ -17886,45 +13300,6 @@
       <c r="BQ125" s="91"/>
       <c r="BR125" s="91"/>
       <c r="BS125" s="91"/>
-      <c r="BT125" s="92"/>
-      <c r="BU125" s="93"/>
-      <c r="BV125" s="90"/>
-      <c r="BW125" s="91"/>
-      <c r="BX125" s="91"/>
-      <c r="BY125" s="91"/>
-      <c r="BZ125" s="91"/>
-      <c r="CA125" s="92"/>
-      <c r="CB125" s="93"/>
-      <c r="CC125" s="90"/>
-      <c r="CD125" s="91"/>
-      <c r="CE125" s="91"/>
-      <c r="CF125" s="91"/>
-      <c r="CG125" s="91"/>
-      <c r="CH125" s="92"/>
-      <c r="CI125" s="94"/>
-      <c r="CJ125" s="95"/>
-      <c r="CK125" s="91"/>
-      <c r="CL125" s="91"/>
-      <c r="CM125" s="91"/>
-      <c r="CN125" s="91"/>
-      <c r="CO125" s="92"/>
-      <c r="CP125" s="93"/>
-      <c r="CQ125" s="90"/>
-      <c r="CR125" s="91"/>
-      <c r="CS125" s="91"/>
-      <c r="CT125" s="91"/>
-      <c r="CU125" s="91"/>
-      <c r="CV125" s="92"/>
-      <c r="CW125" s="93"/>
-      <c r="CX125" s="90"/>
-      <c r="CY125" s="91"/>
-      <c r="CZ125" s="91"/>
-      <c r="DA125" s="91"/>
-      <c r="DB125" s="91"/>
-      <c r="DC125" s="92"/>
-      <c r="DD125" s="93"/>
-      <c r="DE125" s="90"/>
-      <c r="DF125" s="91"/>
     </row>
     <row r="126" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="96"/>
@@ -17998,45 +13373,6 @@
       <c r="BQ126" s="91"/>
       <c r="BR126" s="91"/>
       <c r="BS126" s="91"/>
-      <c r="BT126" s="92"/>
-      <c r="BU126" s="93"/>
-      <c r="BV126" s="90"/>
-      <c r="BW126" s="91"/>
-      <c r="BX126" s="91"/>
-      <c r="BY126" s="91"/>
-      <c r="BZ126" s="91"/>
-      <c r="CA126" s="92"/>
-      <c r="CB126" s="93"/>
-      <c r="CC126" s="90"/>
-      <c r="CD126" s="91"/>
-      <c r="CE126" s="91"/>
-      <c r="CF126" s="91"/>
-      <c r="CG126" s="91"/>
-      <c r="CH126" s="92"/>
-      <c r="CI126" s="94"/>
-      <c r="CJ126" s="95"/>
-      <c r="CK126" s="91"/>
-      <c r="CL126" s="91"/>
-      <c r="CM126" s="91"/>
-      <c r="CN126" s="91"/>
-      <c r="CO126" s="92"/>
-      <c r="CP126" s="93"/>
-      <c r="CQ126" s="90"/>
-      <c r="CR126" s="91"/>
-      <c r="CS126" s="91"/>
-      <c r="CT126" s="91"/>
-      <c r="CU126" s="91"/>
-      <c r="CV126" s="92"/>
-      <c r="CW126" s="93"/>
-      <c r="CX126" s="90"/>
-      <c r="CY126" s="91"/>
-      <c r="CZ126" s="91"/>
-      <c r="DA126" s="91"/>
-      <c r="DB126" s="91"/>
-      <c r="DC126" s="92"/>
-      <c r="DD126" s="93"/>
-      <c r="DE126" s="90"/>
-      <c r="DF126" s="91"/>
     </row>
     <row r="127" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="96"/>
@@ -18110,72 +13446,24 @@
       <c r="BQ127" s="91"/>
       <c r="BR127" s="91"/>
       <c r="BS127" s="91"/>
-      <c r="BT127" s="92"/>
-      <c r="BU127" s="93"/>
-      <c r="BV127" s="90"/>
-      <c r="BW127" s="91"/>
-      <c r="BX127" s="91"/>
-      <c r="BY127" s="91"/>
-      <c r="BZ127" s="91"/>
-      <c r="CA127" s="92"/>
-      <c r="CB127" s="93"/>
-      <c r="CC127" s="90"/>
-      <c r="CD127" s="91"/>
-      <c r="CE127" s="91"/>
-      <c r="CF127" s="91"/>
-      <c r="CG127" s="91"/>
-      <c r="CH127" s="92"/>
-      <c r="CI127" s="94"/>
-      <c r="CJ127" s="95"/>
-      <c r="CK127" s="91"/>
-      <c r="CL127" s="91"/>
-      <c r="CM127" s="91"/>
-      <c r="CN127" s="91"/>
-      <c r="CO127" s="92"/>
-      <c r="CP127" s="93"/>
-      <c r="CQ127" s="90"/>
-      <c r="CR127" s="91"/>
-      <c r="CS127" s="91"/>
-      <c r="CT127" s="91"/>
-      <c r="CU127" s="91"/>
-      <c r="CV127" s="92"/>
-      <c r="CW127" s="93"/>
-      <c r="CX127" s="90"/>
-      <c r="CY127" s="91"/>
-      <c r="CZ127" s="91"/>
-      <c r="DA127" s="91"/>
-      <c r="DB127" s="91"/>
-      <c r="DC127" s="92"/>
-      <c r="DD127" s="93"/>
-      <c r="DE127" s="90"/>
-      <c r="DF127" s="91"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="13">
     <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:AE8"/>
-    <mergeCell ref="AF8:AS8"/>
-    <mergeCell ref="AT8:CB8"/>
-    <mergeCell ref="CC8:CW8"/>
-    <mergeCell ref="CX8:DF8"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="R9:X9"/>
-    <mergeCell ref="Y9:AE9"/>
-    <mergeCell ref="AF9:AL9"/>
-    <mergeCell ref="AM9:AS9"/>
-    <mergeCell ref="AT9:AZ9"/>
-    <mergeCell ref="BA9:BG9"/>
-    <mergeCell ref="BH9:BN9"/>
-    <mergeCell ref="BO9:BU9"/>
-    <mergeCell ref="BV9:CB9"/>
-    <mergeCell ref="CC9:CI9"/>
-    <mergeCell ref="CJ9:CP9"/>
-    <mergeCell ref="CQ9:CW9"/>
-    <mergeCell ref="CX9:DD9"/>
-    <mergeCell ref="DE9:DF9"/>
+    <mergeCell ref="K8:AO8"/>
+    <mergeCell ref="AP8:BS8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AC9:AI9"/>
+    <mergeCell ref="AJ9:AP9"/>
+    <mergeCell ref="AQ9:AW9"/>
+    <mergeCell ref="AX9:BD9"/>
+    <mergeCell ref="BE9:BK9"/>
+    <mergeCell ref="BL9:BR9"/>
   </mergeCells>
-  <conditionalFormatting sqref="K11:DF31">
+  <conditionalFormatting sqref="K11:BS31">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND($J11&gt;0,$J11&lt;=0.2,K$6=1,K$7&gt;=$G11,K$7&lt;=$H11)</formula>
     </cfRule>
